--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734698</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>128736016</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734698</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>128736016</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734698</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>128736016</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,6 +1167,121 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129169945</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Konttjärnen, Näverberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628694</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6978257</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129169945</v>
+        <v>129181897</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,45 +1180,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Konttjärnen, Näverberget, Ång</t>
+          <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628694</v>
+        <v>628501</v>
       </c>
       <c r="R6" t="n">
-        <v>6978257</v>
+        <v>6978560</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,22 +1237,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,8 +1261,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1277,10 +1288,863 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129184366</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628737</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6978215</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Markus Borja</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129184816</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628736</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6978326</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129169945</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Konttjärnen, Näverberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628694</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6978257</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129185300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6978349</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129184595</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6978264</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129182054</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Djupbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>628509</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6978536</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129182187</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56297</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djupbäcken, Djupbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628495</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6978535</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -1903,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129182054</v>
+        <v>129182187</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>56297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,40 +1914,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628509</v>
+        <v>628495</v>
       </c>
       <c r="R12" t="n">
-        <v>6978536</v>
+        <v>6978535</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,7 +1985,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,7 +1995,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,24 +2004,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2029,10 +2022,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129182187</v>
+        <v>129182054</v>
       </c>
       <c r="B13" t="n">
-        <v>56297</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,49 +2033,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628495</v>
+        <v>628509</v>
       </c>
       <c r="R13" t="n">
-        <v>6978535</v>
+        <v>6978536</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2111,7 +2095,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2121,7 +2105,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2130,8 +2114,24 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,60 +1547,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129169945</v>
+        <v>129185300</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>80100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Konttjärnen, Näverberget, Ång</t>
+          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628694</v>
+        <v>628759</v>
       </c>
       <c r="R9" t="n">
-        <v>6978257</v>
+        <v>6978349</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,22 +1615,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,6 +1639,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1659,14 +1651,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129185300</v>
+        <v>129184595</v>
       </c>
       <c r="B10" t="n">
         <v>80100</v>
@@ -1707,7 +1699,7 @@
         <v>628759</v>
       </c>
       <c r="R10" t="n">
-        <v>6978349</v>
+        <v>6978264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1741,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,6 +1753,21 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1777,51 +1784,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129184595</v>
+        <v>129182187</v>
       </c>
       <c r="B11" t="n">
-        <v>80100</v>
+        <v>56297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628759</v>
+        <v>628495</v>
       </c>
       <c r="R11" t="n">
-        <v>6978264</v>
+        <v>6978535</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1850,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,24 +1885,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1903,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129182187</v>
+        <v>129182054</v>
       </c>
       <c r="B12" t="n">
-        <v>56297</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,49 +1914,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628495</v>
+        <v>628509</v>
       </c>
       <c r="R12" t="n">
-        <v>6978535</v>
+        <v>6978536</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1985,7 +1976,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1986,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,8 +1995,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2022,10 +2029,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129182054</v>
+        <v>129187222</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,40 +2040,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628509</v>
+        <v>628900</v>
       </c>
       <c r="R13" t="n">
-        <v>6978536</v>
+        <v>6978506</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2095,7 +2115,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2105,7 +2125,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,24 +2134,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2145,6 +2149,129 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129169945</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Seselmyrhöjden, Konttjärnen, Näverberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628694</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6978257</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -1784,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129182187</v>
+        <v>129182054</v>
       </c>
       <c r="B11" t="n">
-        <v>56297</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,49 +1795,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628495</v>
+        <v>628509</v>
       </c>
       <c r="R11" t="n">
-        <v>6978535</v>
+        <v>6978536</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,7 +1857,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1876,7 +1867,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,8 +1876,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1903,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129182054</v>
+        <v>129182187</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>56297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,40 +1921,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628509</v>
+        <v>628495</v>
       </c>
       <c r="R12" t="n">
-        <v>6978536</v>
+        <v>6978535</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,7 +1992,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,7 +2002,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,24 +2011,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734698</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>128736016</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129181897</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>129184366</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129184816</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129185300</v>
       </c>
       <c r="B9" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129184595</v>
       </c>
       <c r="B10" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129182054</v>
+        <v>129182187</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>56299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,40 +1795,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628509</v>
+        <v>628495</v>
       </c>
       <c r="R11" t="n">
-        <v>6978536</v>
+        <v>6978535</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1867,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,24 +1885,8 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1910,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129182187</v>
+        <v>129182054</v>
       </c>
       <c r="B12" t="n">
-        <v>56297</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,49 +1914,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628495</v>
+        <v>628509</v>
       </c>
       <c r="R12" t="n">
-        <v>6978535</v>
+        <v>6978536</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1992,7 +1976,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2002,7 +1986,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,8 +1995,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2032,7 +2032,7 @@
         <v>129187222</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129169945</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -1784,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129182187</v>
+        <v>129182054</v>
       </c>
       <c r="B11" t="n">
-        <v>56299</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,49 +1795,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628495</v>
+        <v>628509</v>
       </c>
       <c r="R11" t="n">
-        <v>6978535</v>
+        <v>6978536</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,7 +1857,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1876,7 +1867,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,8 +1876,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1903,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129182054</v>
+        <v>129182187</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>56299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,40 +1921,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupbäcken, Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628509</v>
+        <v>628495</v>
       </c>
       <c r="R12" t="n">
-        <v>6978536</v>
+        <v>6978535</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,7 +1992,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,7 +2002,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,24 +2011,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2275,45 +2275,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295766</v>
+        <v>129302283</v>
       </c>
       <c r="B15" t="n">
-        <v>80173</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628846</v>
+        <v>628664</v>
       </c>
       <c r="R15" t="n">
-        <v>6978364</v>
+        <v>6978446</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,6 +2346,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,32 +2377,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129292781</v>
+        <v>129302237</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628590</v>
+        <v>628766</v>
       </c>
       <c r="R16" t="n">
-        <v>6978436</v>
+        <v>6978173</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,6 +2448,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,32 +2479,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295830</v>
+        <v>129302245</v>
       </c>
       <c r="B17" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2504,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628896</v>
+        <v>628749</v>
       </c>
       <c r="R17" t="n">
-        <v>6978430</v>
+        <v>6978341</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,6 +2550,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,45 +2581,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302237</v>
+        <v>129295766</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>80173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628766</v>
+        <v>628846</v>
       </c>
       <c r="R18" t="n">
-        <v>6978173</v>
+        <v>6978364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,11 +2652,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,32 +2678,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302283</v>
+        <v>129292781</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>92240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2703,10 +2713,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628664</v>
+        <v>628590</v>
       </c>
       <c r="R19" t="n">
-        <v>6978446</v>
+        <v>6978436</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,11 +2749,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,32 +2775,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129302245</v>
+        <v>129295830</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>92240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2805,10 +2810,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628749</v>
+        <v>628896</v>
       </c>
       <c r="R20" t="n">
-        <v>6978341</v>
+        <v>6978430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,11 +2846,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,32 +2872,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302262</v>
+        <v>129302269</v>
       </c>
       <c r="B21" t="n">
-        <v>91818</v>
+        <v>97547</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628800</v>
+        <v>628792</v>
       </c>
       <c r="R21" t="n">
-        <v>6978306</v>
+        <v>6978309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,32 +2969,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302269</v>
+        <v>129302284</v>
       </c>
       <c r="B22" t="n">
-        <v>97540</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628792</v>
+        <v>628667</v>
       </c>
       <c r="R22" t="n">
-        <v>6978309</v>
+        <v>6978461</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,6 +3040,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,32 +3071,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302243</v>
+        <v>129302278</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628743</v>
+        <v>628894</v>
       </c>
       <c r="R23" t="n">
-        <v>6978315</v>
+        <v>6978483</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3146,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302284</v>
+        <v>129293584</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>91995</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3179,21 +3184,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3203,10 +3208,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628667</v>
+        <v>628624</v>
       </c>
       <c r="R24" t="n">
-        <v>6978461</v>
+        <v>6978328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3239,11 +3244,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302265</v>
+        <v>129294036</v>
       </c>
       <c r="B25" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3301,14 +3301,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628772</v>
+        <v>628728</v>
       </c>
       <c r="R25" t="n">
-        <v>6978157</v>
+        <v>6978173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3367,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302240</v>
+        <v>129290628</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628764</v>
+        <v>628499</v>
       </c>
       <c r="R26" t="n">
-        <v>6978279</v>
+        <v>6978448</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,11 +3438,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,45 +3464,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302278</v>
+        <v>129294050</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628894</v>
+        <v>628728</v>
       </c>
       <c r="R27" t="n">
-        <v>6978483</v>
+        <v>6978173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,45 +3571,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129290628</v>
+        <v>129292558</v>
       </c>
       <c r="B28" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628499</v>
+        <v>628589</v>
       </c>
       <c r="R28" t="n">
-        <v>6978448</v>
+        <v>6978414</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3668,49 +3672,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129292558</v>
+        <v>129302262</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628589</v>
+        <v>628800</v>
       </c>
       <c r="R29" t="n">
-        <v>6978414</v>
+        <v>6978306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,32 +3769,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129293584</v>
+        <v>129302243</v>
       </c>
       <c r="B30" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628624</v>
+        <v>628743</v>
       </c>
       <c r="R30" t="n">
-        <v>6978328</v>
+        <v>6978315</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,6 +3840,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,10 +3871,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129294050</v>
+        <v>129302265</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,39 +3882,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628728</v>
+        <v>628772</v>
       </c>
       <c r="R31" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,11 +3942,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,10 +3968,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294036</v>
+        <v>129302240</v>
       </c>
       <c r="B32" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,34 +3979,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628728</v>
+        <v>628764</v>
       </c>
       <c r="R32" t="n">
-        <v>6978173</v>
+        <v>6978279</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129290118</v>
+        <v>129302293</v>
       </c>
       <c r="B33" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628453</v>
+        <v>628737</v>
       </c>
       <c r="R33" t="n">
-        <v>6978518</v>
+        <v>6978300</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129293171</v>
+        <v>129302235</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4178,43 +4178,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628702</v>
+        <v>628629</v>
       </c>
       <c r="R34" t="n">
-        <v>6978339</v>
+        <v>6978532</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,45 +4264,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129296183</v>
+        <v>129302277</v>
       </c>
       <c r="B35" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>629055</v>
+        <v>628899</v>
       </c>
       <c r="R35" t="n">
-        <v>6978511</v>
+        <v>6978480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4344,6 +4335,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4370,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129295187</v>
+        <v>129296183</v>
       </c>
       <c r="B36" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,34 +4377,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628834</v>
+        <v>629055</v>
       </c>
       <c r="R36" t="n">
-        <v>6978251</v>
+        <v>6978511</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129302293</v>
+        <v>129295187</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4478,34 +4474,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628737</v>
+        <v>628834</v>
       </c>
       <c r="R37" t="n">
-        <v>6978300</v>
+        <v>6978251</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4564,32 +4560,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302277</v>
+        <v>129290118</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4599,10 +4595,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628899</v>
+        <v>628453</v>
       </c>
       <c r="R38" t="n">
-        <v>6978480</v>
+        <v>6978518</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4635,11 +4631,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,45 +4657,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302235</v>
+        <v>129294218</v>
       </c>
       <c r="B39" t="n">
-        <v>91533</v>
+        <v>96010</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628629</v>
+        <v>628798</v>
       </c>
       <c r="R39" t="n">
-        <v>6978532</v>
+        <v>6978072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4737,6 +4728,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,45 +4759,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129294218</v>
+        <v>129293171</v>
       </c>
       <c r="B40" t="n">
-        <v>96003</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628798</v>
+        <v>628702</v>
       </c>
       <c r="R40" t="n">
-        <v>6978072</v>
+        <v>6978339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4834,11 +4839,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,49 +4865,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290183</v>
+        <v>129302248</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628436</v>
+        <v>628679</v>
       </c>
       <c r="R41" t="n">
-        <v>6978498</v>
+        <v>6978469</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4940,6 +4936,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4966,10 +4967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129291502</v>
+        <v>129294028</v>
       </c>
       <c r="B42" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4977,34 +4978,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628564</v>
+        <v>628728</v>
       </c>
       <c r="R42" t="n">
-        <v>6978436</v>
+        <v>6978173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,7 +5067,7 @@
         <v>129293533</v>
       </c>
       <c r="B43" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5160,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129294028</v>
+        <v>129291502</v>
       </c>
       <c r="B44" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5171,34 +5172,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628728</v>
+        <v>628564</v>
       </c>
       <c r="R44" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5363,45 +5364,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129302248</v>
+        <v>129290183</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628679</v>
+        <v>628436</v>
       </c>
       <c r="R46" t="n">
-        <v>6978469</v>
+        <v>6978498</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5434,11 +5439,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290361</v>
+        <v>129290169</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,34 +5476,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628465</v>
+        <v>628453</v>
       </c>
       <c r="R47" t="n">
-        <v>6978491</v>
+        <v>6978518</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5536,6 +5541,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,10 +5572,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290084</v>
+        <v>129302275</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5590,21 +5600,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628475</v>
+        <v>628663</v>
       </c>
       <c r="R48" t="n">
-        <v>6978540</v>
+        <v>6978428</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,6 +5643,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5663,50 +5674,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290169</v>
+        <v>129302276</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628453</v>
+        <v>628648</v>
       </c>
       <c r="R49" t="n">
-        <v>6978518</v>
+        <v>6978420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5743,7 +5749,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5770,10 +5776,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290616</v>
+        <v>129302231</v>
       </c>
       <c r="B50" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5805,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628499</v>
+        <v>628752</v>
       </c>
       <c r="R50" t="n">
-        <v>6978448</v>
+        <v>6978198</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5867,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296084</v>
+        <v>129302233</v>
       </c>
       <c r="B51" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5878,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5902,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628959</v>
+        <v>628759</v>
       </c>
       <c r="R51" t="n">
-        <v>6978530</v>
+        <v>6978233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302231</v>
+        <v>129302294</v>
       </c>
       <c r="B52" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5975,21 +5981,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5999,10 +6005,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628752</v>
+        <v>628661</v>
       </c>
       <c r="R52" t="n">
-        <v>6978198</v>
+        <v>6978421</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6061,10 +6067,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129302233</v>
+        <v>129296084</v>
       </c>
       <c r="B53" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6072,21 +6078,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6096,10 +6102,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628759</v>
+        <v>628959</v>
       </c>
       <c r="R53" t="n">
-        <v>6978233</v>
+        <v>6978530</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6158,10 +6164,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129302294</v>
+        <v>129290616</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6169,21 +6175,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6193,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628661</v>
+        <v>628499</v>
       </c>
       <c r="R54" t="n">
-        <v>6978421</v>
+        <v>6978448</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6255,32 +6261,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129302275</v>
+        <v>129290361</v>
       </c>
       <c r="B55" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6290,10 +6296,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628663</v>
+        <v>628465</v>
       </c>
       <c r="R55" t="n">
-        <v>6978428</v>
+        <v>6978491</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6326,11 +6332,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6357,10 +6358,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302276</v>
+        <v>129290084</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6385,17 +6386,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628648</v>
+        <v>628475</v>
       </c>
       <c r="R56" t="n">
-        <v>6978420</v>
+        <v>6978540</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6428,11 +6433,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6459,7 +6459,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129302274</v>
+        <v>129294015</v>
       </c>
       <c r="B57" t="n">
         <v>80144</v>
@@ -6490,14 +6490,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628659</v>
+        <v>628728</v>
       </c>
       <c r="R57" t="n">
-        <v>6978419</v>
+        <v>6978173</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6559,7 +6559,7 @@
         <v>129302271</v>
       </c>
       <c r="B58" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302241</v>
+        <v>129302252</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57885</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628741</v>
+        <v>628837</v>
       </c>
       <c r="R59" t="n">
-        <v>6978271</v>
+        <v>6978500</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6755,10 +6755,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302252</v>
+        <v>129302274</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>80144</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6766,21 +6766,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628837</v>
+        <v>628659</v>
       </c>
       <c r="R60" t="n">
-        <v>6978500</v>
+        <v>6978419</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6826,11 +6826,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6857,10 +6852,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302229</v>
+        <v>129302241</v>
       </c>
       <c r="B61" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6868,21 +6863,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628761</v>
+        <v>628741</v>
       </c>
       <c r="R61" t="n">
-        <v>6978157</v>
+        <v>6978271</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6928,6 +6923,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6954,10 +6954,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129294015</v>
+        <v>129302229</v>
       </c>
       <c r="B62" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6965,34 +6965,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628728</v>
+        <v>628761</v>
       </c>
       <c r="R62" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7051,54 +7051,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129293780</v>
+        <v>129295935</v>
       </c>
       <c r="B63" t="n">
-        <v>57717</v>
+        <v>91554</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100110</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628680</v>
+        <v>628907</v>
       </c>
       <c r="R63" t="n">
-        <v>6978235</v>
+        <v>6978423</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7157,45 +7148,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129295935</v>
+        <v>129293780</v>
       </c>
       <c r="B64" t="n">
-        <v>91547</v>
+        <v>57717</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1204</v>
+        <v>100110</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628907</v>
+        <v>628680</v>
       </c>
       <c r="R64" t="n">
-        <v>6978423</v>
+        <v>6978235</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7254,10 +7254,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129295162</v>
+        <v>129302280</v>
       </c>
       <c r="B65" t="n">
-        <v>91988</v>
+        <v>98676</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,34 +7265,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628834</v>
+        <v>628692</v>
       </c>
       <c r="R65" t="n">
-        <v>6978251</v>
+        <v>6978432</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,6 +7325,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7351,49 +7356,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129290108</v>
+        <v>129302254</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628447</v>
+        <v>628894</v>
       </c>
       <c r="R66" t="n">
-        <v>6978522</v>
+        <v>6978096</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,6 +7427,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7452,32 +7458,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129292729</v>
+        <v>129302250</v>
       </c>
       <c r="B67" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7487,10 +7493,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628599</v>
+        <v>628495</v>
       </c>
       <c r="R67" t="n">
-        <v>6978448</v>
+        <v>6978647</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7523,6 +7529,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7549,49 +7560,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129291473</v>
+        <v>129302244</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628549</v>
+        <v>628756</v>
       </c>
       <c r="R68" t="n">
-        <v>6978449</v>
+        <v>6978337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7624,6 +7631,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7650,32 +7662,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129294000</v>
+        <v>129302259</v>
       </c>
       <c r="B69" t="n">
-        <v>91533</v>
+        <v>91995</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7685,10 +7697,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628687</v>
+        <v>628771</v>
       </c>
       <c r="R69" t="n">
-        <v>6978194</v>
+        <v>6978154</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7747,54 +7759,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129297292</v>
+        <v>129295162</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>91995</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628429</v>
+        <v>628834</v>
       </c>
       <c r="R70" t="n">
-        <v>6978625</v>
+        <v>6978251</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7853,32 +7856,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129302254</v>
+        <v>129292729</v>
       </c>
       <c r="B71" t="n">
-        <v>57722</v>
+        <v>91995</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7888,10 +7891,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628894</v>
+        <v>628599</v>
       </c>
       <c r="R71" t="n">
-        <v>6978096</v>
+        <v>6978448</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7924,11 +7927,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7955,10 +7953,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302280</v>
+        <v>129291635</v>
       </c>
       <c r="B72" t="n">
-        <v>98669</v>
+        <v>96010</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7966,21 +7964,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7990,10 +7988,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628692</v>
+        <v>628573</v>
       </c>
       <c r="R72" t="n">
-        <v>6978432</v>
+        <v>6978423</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8026,11 +8024,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8057,10 +8050,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302250</v>
+        <v>129294000</v>
       </c>
       <c r="B73" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8068,21 +8061,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8092,10 +8085,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628495</v>
+        <v>628687</v>
       </c>
       <c r="R73" t="n">
-        <v>6978647</v>
+        <v>6978194</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8128,11 +8121,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8159,45 +8147,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302244</v>
+        <v>129291473</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628756</v>
+        <v>628549</v>
       </c>
       <c r="R74" t="n">
-        <v>6978337</v>
+        <v>6978449</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8230,11 +8222,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8261,10 +8248,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302259</v>
+        <v>129290108</v>
       </c>
       <c r="B75" t="n">
-        <v>91988</v>
+        <v>98676</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8272,34 +8259,38 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628771</v>
+        <v>628447</v>
       </c>
       <c r="R75" t="n">
-        <v>6978154</v>
+        <v>6978522</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8358,45 +8349,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129291635</v>
+        <v>129297292</v>
       </c>
       <c r="B76" t="n">
-        <v>96003</v>
+        <v>57725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628573</v>
+        <v>628429</v>
       </c>
       <c r="R76" t="n">
-        <v>6978423</v>
+        <v>6978625</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8455,45 +8455,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129290447</v>
+        <v>129295124</v>
       </c>
       <c r="B77" t="n">
-        <v>97540</v>
+        <v>91825</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628494</v>
+        <v>628788</v>
       </c>
       <c r="R77" t="n">
-        <v>6978496</v>
+        <v>6978227</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8552,10 +8552,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129295124</v>
+        <v>129289501</v>
       </c>
       <c r="B78" t="n">
-        <v>91818</v>
+        <v>57725</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8563,34 +8563,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628788</v>
+        <v>628451</v>
       </c>
       <c r="R78" t="n">
-        <v>6978227</v>
+        <v>6978596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,6 +8628,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8649,50 +8659,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129289501</v>
+        <v>129290447</v>
       </c>
       <c r="B79" t="n">
-        <v>57725</v>
+        <v>97547</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628451</v>
+        <v>628494</v>
       </c>
       <c r="R79" t="n">
-        <v>6978596</v>
+        <v>6978496</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8725,11 +8730,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8756,45 +8756,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302227</v>
+        <v>129302281</v>
       </c>
       <c r="B80" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628851</v>
+        <v>628688</v>
       </c>
       <c r="R80" t="n">
-        <v>6978504</v>
+        <v>6978441</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8829,12 +8833,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8853,10 +8863,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302255</v>
+        <v>129302227</v>
       </c>
       <c r="B81" t="n">
-        <v>57722</v>
+        <v>91540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8864,21 +8874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8888,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628712</v>
+        <v>628851</v>
       </c>
       <c r="R81" t="n">
-        <v>6978376</v>
+        <v>6978504</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,11 +8934,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8955,49 +8960,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B82" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R82" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,7 +9035,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9043,7 +9044,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9256,45 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129302232</v>
+        <v>129294276</v>
       </c>
       <c r="B85" t="n">
-        <v>91533</v>
+        <v>91741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628742</v>
+        <v>628790</v>
       </c>
       <c r="R85" t="n">
-        <v>6978216</v>
+        <v>6978034</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,32 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302267</v>
+        <v>129296097</v>
       </c>
       <c r="B86" t="n">
-        <v>91818</v>
+        <v>80173</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628603</v>
+        <v>628959</v>
       </c>
       <c r="R86" t="n">
-        <v>6978502</v>
+        <v>6978530</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302264</v>
+        <v>129293914</v>
       </c>
       <c r="B87" t="n">
-        <v>91818</v>
+        <v>57885</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9461,34 +9461,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628796</v>
+        <v>628690</v>
       </c>
       <c r="R87" t="n">
-        <v>6978261</v>
+        <v>6978221</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,32 +9552,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129302260</v>
+        <v>129302232</v>
       </c>
       <c r="B88" t="n">
-        <v>91988</v>
+        <v>91540</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9587,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628641</v>
+        <v>628742</v>
       </c>
       <c r="R88" t="n">
-        <v>6978450</v>
+        <v>6978216</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,10 +9649,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302291</v>
+        <v>129302267</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>91825</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9655,21 +9660,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9684,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628794</v>
+        <v>628603</v>
       </c>
       <c r="R89" t="n">
-        <v>6978373</v>
+        <v>6978502</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,32 +9746,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302258</v>
+        <v>129302264</v>
       </c>
       <c r="B90" t="n">
-        <v>91988</v>
+        <v>91825</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9776,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628851</v>
+        <v>628796</v>
       </c>
       <c r="R90" t="n">
-        <v>6978502</v>
+        <v>6978261</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129294276</v>
+        <v>129302260</v>
       </c>
       <c r="B91" t="n">
-        <v>91734</v>
+        <v>91995</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9849,34 +9854,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628790</v>
+        <v>628641</v>
       </c>
       <c r="R91" t="n">
-        <v>6978034</v>
+        <v>6978450</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,10 +9940,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129290229</v>
+        <v>129302291</v>
       </c>
       <c r="B92" t="n">
-        <v>91818</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9946,21 +9951,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9970,10 +9975,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628436</v>
+        <v>628794</v>
       </c>
       <c r="R92" t="n">
-        <v>6978498</v>
+        <v>6978373</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10032,32 +10037,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129296097</v>
+        <v>129302258</v>
       </c>
       <c r="B93" t="n">
-        <v>80173</v>
+        <v>91995</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10067,10 +10072,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628959</v>
+        <v>628851</v>
       </c>
       <c r="R93" t="n">
-        <v>6978530</v>
+        <v>6978502</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,32 +10134,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129292746</v>
+        <v>129289873</v>
       </c>
       <c r="B94" t="n">
-        <v>91818</v>
+        <v>91504</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10164,10 +10169,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628586</v>
+        <v>628447</v>
       </c>
       <c r="R94" t="n">
-        <v>6978451</v>
+        <v>6978522</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10226,32 +10231,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129289873</v>
+        <v>129292746</v>
       </c>
       <c r="B95" t="n">
-        <v>91497</v>
+        <v>91825</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10261,10 +10266,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628447</v>
+        <v>628586</v>
       </c>
       <c r="R95" t="n">
-        <v>6978522</v>
+        <v>6978451</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10323,10 +10328,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129293890</v>
+        <v>129290229</v>
       </c>
       <c r="B96" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10334,39 +10339,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628691</v>
+        <v>628436</v>
       </c>
       <c r="R96" t="n">
-        <v>6978242</v>
+        <v>6978498</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10399,11 +10399,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10430,10 +10425,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129293914</v>
+        <v>129293890</v>
       </c>
       <c r="B97" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10441,27 +10436,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10470,10 +10465,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628690</v>
+        <v>628691</v>
       </c>
       <c r="R97" t="n">
-        <v>6978221</v>
+        <v>6978242</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10506,6 +10501,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10532,49 +10532,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129293044</v>
+        <v>129302295</v>
       </c>
       <c r="B98" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628662</v>
+        <v>628463</v>
       </c>
       <c r="R98" t="n">
-        <v>6978408</v>
+        <v>6978635</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10633,10 +10629,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129302295</v>
+        <v>129295410</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10644,34 +10640,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628463</v>
+        <v>628767</v>
       </c>
       <c r="R99" t="n">
-        <v>6978635</v>
+        <v>6978383</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10730,54 +10735,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129295410</v>
+        <v>129293044</v>
       </c>
       <c r="B100" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>628767</v>
+        <v>628662</v>
       </c>
       <c r="R100" t="n">
-        <v>6978383</v>
+        <v>6978408</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10836,10 +10836,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129295020</v>
+        <v>129302268</v>
       </c>
       <c r="B101" t="n">
-        <v>80179</v>
+        <v>97547</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10847,34 +10847,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628826</v>
+        <v>628719</v>
       </c>
       <c r="R101" t="n">
-        <v>6978150</v>
+        <v>6978594</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129295651</v>
+        <v>129302287</v>
       </c>
       <c r="B102" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10961,21 +10961,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628796</v>
+        <v>628649</v>
       </c>
       <c r="R102" t="n">
-        <v>6978373</v>
+        <v>6978449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11008,6 +11004,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11037,7 +11038,7 @@
         <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11131,10 +11132,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302268</v>
+        <v>129295020</v>
       </c>
       <c r="B104" t="n">
-        <v>97540</v>
+        <v>80179</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11142,34 +11143,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628719</v>
+        <v>628826</v>
       </c>
       <c r="R104" t="n">
-        <v>6978594</v>
+        <v>6978150</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11231,7 +11232,7 @@
         <v>129302282</v>
       </c>
       <c r="B105" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11330,10 +11331,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302287</v>
+        <v>129295651</v>
       </c>
       <c r="B106" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11358,17 +11359,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628649</v>
+        <v>628796</v>
       </c>
       <c r="R106" t="n">
-        <v>6978449</v>
+        <v>6978373</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11401,11 +11406,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129293395</v>
+        <v>129302246</v>
       </c>
       <c r="B107" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,21 +11443,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11467,10 +11467,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628616</v>
+        <v>628750</v>
       </c>
       <c r="R107" t="n">
-        <v>6978368</v>
+        <v>6978346</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11503,6 +11503,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11529,7 +11534,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129293300</v>
+        <v>129302251</v>
       </c>
       <c r="B108" t="n">
         <v>57725</v>
@@ -11558,21 +11563,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628665</v>
+        <v>628425</v>
       </c>
       <c r="R108" t="n">
-        <v>6978376</v>
+        <v>6978621</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11636,10 +11636,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129289885</v>
+        <v>129293395</v>
       </c>
       <c r="B109" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628447</v>
+        <v>628616</v>
       </c>
       <c r="R109" t="n">
-        <v>6978522</v>
+        <v>6978368</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11733,10 +11733,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129302246</v>
+        <v>129289885</v>
       </c>
       <c r="B110" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11744,21 +11744,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11768,10 +11768,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>628750</v>
+        <v>628447</v>
       </c>
       <c r="R110" t="n">
-        <v>6978346</v>
+        <v>6978522</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11804,11 +11804,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11835,7 +11830,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129302251</v>
+        <v>129293300</v>
       </c>
       <c r="B111" t="n">
         <v>57725</v>
@@ -11864,16 +11859,21 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628425</v>
+        <v>628665</v>
       </c>
       <c r="R111" t="n">
-        <v>6978621</v>
+        <v>6978376</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11937,32 +11937,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129295820</v>
+        <v>129302247</v>
       </c>
       <c r="B112" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628889</v>
+        <v>628749</v>
       </c>
       <c r="R112" t="n">
-        <v>6978417</v>
+        <v>6978349</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,6 +12008,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12034,10 +12039,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302247</v>
+        <v>129302290</v>
       </c>
       <c r="B113" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12045,21 +12050,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12069,10 +12074,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628749</v>
+        <v>628712</v>
       </c>
       <c r="R113" t="n">
-        <v>6978349</v>
+        <v>6978591</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12105,11 +12110,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12136,10 +12136,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302290</v>
+        <v>129302225</v>
       </c>
       <c r="B114" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12147,21 +12147,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628712</v>
+        <v>628856</v>
       </c>
       <c r="R114" t="n">
-        <v>6978591</v>
+        <v>6978527</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12233,32 +12233,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302225</v>
+        <v>129302289</v>
       </c>
       <c r="B115" t="n">
-        <v>91533</v>
+        <v>57717</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12268,10 +12268,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628856</v>
+        <v>628493</v>
       </c>
       <c r="R115" t="n">
-        <v>6978527</v>
+        <v>6978648</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,6 +12304,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12333,7 +12338,7 @@
         <v>129302256</v>
       </c>
       <c r="B116" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12432,32 +12437,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302289</v>
+        <v>129295820</v>
       </c>
       <c r="B117" t="n">
-        <v>57717</v>
+        <v>91995</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100110</v>
+        <v>1209</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12467,10 +12472,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628493</v>
+        <v>628889</v>
       </c>
       <c r="R117" t="n">
-        <v>6978648</v>
+        <v>6978417</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12503,11 +12508,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12537,7 +12537,7 @@
         <v>129293475</v>
       </c>
       <c r="B118" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,10 +12631,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129293329</v>
+        <v>129302242</v>
       </c>
       <c r="B119" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12642,16 +12642,16 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -12659,26 +12659,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628640</v>
+        <v>628750</v>
       </c>
       <c r="R119" t="n">
-        <v>6978364</v>
+        <v>6978284</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12711,6 +12702,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12737,45 +12733,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129294695</v>
+        <v>129302273</v>
       </c>
       <c r="B120" t="n">
-        <v>91988</v>
+        <v>80144</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628831</v>
+        <v>628878</v>
       </c>
       <c r="R120" t="n">
-        <v>6978180</v>
+        <v>6978535</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12834,50 +12830,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129294983</v>
+        <v>129302257</v>
       </c>
       <c r="B121" t="n">
-        <v>57725</v>
+        <v>91995</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628826</v>
+        <v>628794</v>
       </c>
       <c r="R121" t="n">
-        <v>6978150</v>
+        <v>6978311</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12910,11 +12901,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Sannolikt bohål av tretåig hackspett. I gran. Omkring 6 meter upp. Klättrade upp i trädet och bohålet stämmer mycket väl in på tretå. Prydligt uthackat och relativt litet.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12941,45 +12927,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129297070</v>
+        <v>129293329</v>
       </c>
       <c r="B122" t="n">
-        <v>91988</v>
+        <v>57722</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628764</v>
+        <v>628640</v>
       </c>
       <c r="R122" t="n">
-        <v>6978591</v>
+        <v>6978364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13038,10 +13033,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129295812</v>
+        <v>129294983</v>
       </c>
       <c r="B123" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13049,34 +13044,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628900</v>
+        <v>628826</v>
       </c>
       <c r="R123" t="n">
-        <v>6978416</v>
+        <v>6978150</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13109,6 +13109,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Sannolikt bohål av tretåig hackspett. I gran. Omkring 6 meter upp. Klättrade upp i trädet och bohålet stämmer mycket väl in på tretå. Prydligt uthackat och relativt litet.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13135,45 +13140,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302242</v>
+        <v>129294695</v>
       </c>
       <c r="B124" t="n">
-        <v>57725</v>
+        <v>91995</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628750</v>
+        <v>628831</v>
       </c>
       <c r="R124" t="n">
-        <v>6978284</v>
+        <v>6978180</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13206,11 +13211,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13237,32 +13237,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302273</v>
+        <v>129297070</v>
       </c>
       <c r="B125" t="n">
-        <v>80144</v>
+        <v>91995</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628878</v>
+        <v>628764</v>
       </c>
       <c r="R125" t="n">
-        <v>6978535</v>
+        <v>6978591</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13334,45 +13334,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129302257</v>
+        <v>129295812</v>
       </c>
       <c r="B126" t="n">
-        <v>91988</v>
+        <v>91540</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628794</v>
+        <v>628900</v>
       </c>
       <c r="R126" t="n">
-        <v>6978311</v>
+        <v>6978416</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13431,50 +13431,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129289677</v>
+        <v>129302270</v>
       </c>
       <c r="B127" t="n">
-        <v>57722</v>
+        <v>97547</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628484</v>
+        <v>628812</v>
       </c>
       <c r="R127" t="n">
-        <v>6978568</v>
+        <v>6978062</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13533,32 +13528,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290692</v>
+        <v>129302296</v>
       </c>
       <c r="B128" t="n">
-        <v>80104</v>
+        <v>79039</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13568,10 +13563,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628515</v>
+        <v>628449</v>
       </c>
       <c r="R128" t="n">
-        <v>6978451</v>
+        <v>6978612</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13630,45 +13625,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129294090</v>
+        <v>129302239</v>
       </c>
       <c r="B129" t="n">
-        <v>80104</v>
+        <v>57725</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628743</v>
+        <v>628747</v>
       </c>
       <c r="R129" t="n">
-        <v>6978155</v>
+        <v>6978218</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13701,6 +13696,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13727,38 +13727,37 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129290523</v>
+        <v>129291461</v>
       </c>
       <c r="B130" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -13767,10 +13766,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628509</v>
+        <v>628547</v>
       </c>
       <c r="R130" t="n">
-        <v>6978510</v>
+        <v>6978457</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13803,11 +13802,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13834,45 +13828,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129291548</v>
+        <v>129289677</v>
       </c>
       <c r="B131" t="n">
-        <v>80048</v>
+        <v>57722</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628549</v>
+        <v>628484</v>
       </c>
       <c r="R131" t="n">
-        <v>6978433</v>
+        <v>6978568</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13931,37 +13930,38 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129291461</v>
+        <v>129290523</v>
       </c>
       <c r="B132" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13970,10 +13970,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628547</v>
+        <v>628509</v>
       </c>
       <c r="R132" t="n">
-        <v>6978457</v>
+        <v>6978510</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14006,6 +14006,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14032,32 +14037,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129302296</v>
+        <v>129290692</v>
       </c>
       <c r="B133" t="n">
-        <v>79039</v>
+        <v>80104</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14067,10 +14072,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628449</v>
+        <v>628515</v>
       </c>
       <c r="R133" t="n">
-        <v>6978612</v>
+        <v>6978451</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14129,45 +14134,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129302239</v>
+        <v>129294090</v>
       </c>
       <c r="B134" t="n">
-        <v>57725</v>
+        <v>80104</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628747</v>
+        <v>628743</v>
       </c>
       <c r="R134" t="n">
-        <v>6978218</v>
+        <v>6978155</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14200,11 +14205,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14231,10 +14231,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129302270</v>
+        <v>129291548</v>
       </c>
       <c r="B135" t="n">
-        <v>97540</v>
+        <v>80048</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14242,21 +14242,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628812</v>
+        <v>628549</v>
       </c>
       <c r="R135" t="n">
-        <v>6978062</v>
+        <v>6978433</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14328,10 +14328,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129294072</v>
+        <v>129302228</v>
       </c>
       <c r="B136" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14339,34 +14339,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628731</v>
+        <v>628870</v>
       </c>
       <c r="R136" t="n">
-        <v>6978165</v>
+        <v>6978469</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14425,10 +14425,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293275</v>
+        <v>129294072</v>
       </c>
       <c r="B137" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14436,39 +14436,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628693</v>
+        <v>628731</v>
       </c>
       <c r="R137" t="n">
-        <v>6978372</v>
+        <v>6978165</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14501,11 +14496,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14532,10 +14522,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293208</v>
+        <v>129295655</v>
       </c>
       <c r="B138" t="n">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14543,16 +14533,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14560,22 +14550,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628695</v>
+        <v>628796</v>
       </c>
       <c r="R138" t="n">
-        <v>6978356</v>
+        <v>6978373</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14608,11 +14602,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14639,10 +14628,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B139" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14650,16 +14639,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -14667,26 +14656,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R139" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14719,6 +14704,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14745,10 +14735,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129302228</v>
+        <v>129293275</v>
       </c>
       <c r="B140" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14756,34 +14746,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628870</v>
+        <v>628693</v>
       </c>
       <c r="R140" t="n">
-        <v>6978469</v>
+        <v>6978372</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14816,6 +14811,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14845,7 +14845,7 @@
         <v>129302266</v>
       </c>
       <c r="B141" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15041,32 +15041,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129302272</v>
+        <v>129291606</v>
       </c>
       <c r="B143" t="n">
-        <v>97540</v>
+        <v>80144</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15076,10 +15076,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628641</v>
+        <v>628564</v>
       </c>
       <c r="R143" t="n">
-        <v>6978450</v>
+        <v>6978436</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15138,32 +15138,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129302288</v>
+        <v>129290695</v>
       </c>
       <c r="B144" t="n">
-        <v>98669</v>
+        <v>80180</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15173,10 +15173,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628636</v>
+        <v>628509</v>
       </c>
       <c r="R144" t="n">
-        <v>6978511</v>
+        <v>6978440</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15209,11 +15209,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15347,10 +15342,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129290695</v>
+        <v>129302272</v>
       </c>
       <c r="B146" t="n">
-        <v>80180</v>
+        <v>97547</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15358,21 +15353,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15382,10 +15377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628509</v>
+        <v>628641</v>
       </c>
       <c r="R146" t="n">
-        <v>6978440</v>
+        <v>6978450</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15444,32 +15439,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129291606</v>
+        <v>129302288</v>
       </c>
       <c r="B147" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15479,10 +15474,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628564</v>
+        <v>628636</v>
       </c>
       <c r="R147" t="n">
-        <v>6978436</v>
+        <v>6978511</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15515,6 +15510,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15541,49 +15541,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129290760</v>
+        <v>129302292</v>
       </c>
       <c r="B148" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628499</v>
+        <v>628819</v>
       </c>
       <c r="R148" t="n">
-        <v>6978448</v>
+        <v>6978067</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15616,6 +15612,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15642,10 +15643,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129295133</v>
+        <v>129302249</v>
       </c>
       <c r="B149" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15653,34 +15654,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628788</v>
+        <v>628539</v>
       </c>
       <c r="R149" t="n">
-        <v>6978227</v>
+        <v>6978526</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15713,6 +15714,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15739,10 +15745,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129295136</v>
+        <v>129302230</v>
       </c>
       <c r="B150" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15750,34 +15756,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628799</v>
+        <v>628766</v>
       </c>
       <c r="R150" t="n">
-        <v>6978234</v>
+        <v>6978195</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15836,32 +15842,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129295841</v>
+        <v>129302261</v>
       </c>
       <c r="B151" t="n">
-        <v>91734</v>
+        <v>91825</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15871,10 +15877,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628889</v>
+        <v>628794</v>
       </c>
       <c r="R151" t="n">
-        <v>6978417</v>
+        <v>6978311</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15933,10 +15939,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129295719</v>
+        <v>129302238</v>
       </c>
       <c r="B152" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15944,34 +15950,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628846</v>
+        <v>628757</v>
       </c>
       <c r="R152" t="n">
-        <v>6978364</v>
+        <v>6978192</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16004,6 +16010,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16030,10 +16041,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302292</v>
+        <v>129302226</v>
       </c>
       <c r="B153" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16041,21 +16052,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16065,10 +16076,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628819</v>
+        <v>628849</v>
       </c>
       <c r="R153" t="n">
-        <v>6978067</v>
+        <v>6978507</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16101,11 +16112,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16135,7 +16141,7 @@
         <v>129302297</v>
       </c>
       <c r="B154" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16229,32 +16235,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302249</v>
+        <v>129302285</v>
       </c>
       <c r="B155" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16264,10 +16270,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628539</v>
+        <v>628656</v>
       </c>
       <c r="R155" t="n">
-        <v>6978526</v>
+        <v>6978459</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16304,7 +16310,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16331,10 +16337,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B156" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16342,34 +16348,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R156" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16428,10 +16434,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302261</v>
+        <v>129295133</v>
       </c>
       <c r="B157" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16439,34 +16445,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628794</v>
+        <v>628788</v>
       </c>
       <c r="R157" t="n">
-        <v>6978311</v>
+        <v>6978227</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16525,32 +16531,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302238</v>
+        <v>129295841</v>
       </c>
       <c r="B158" t="n">
-        <v>57725</v>
+        <v>91741</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16560,10 +16566,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628757</v>
+        <v>628889</v>
       </c>
       <c r="R158" t="n">
-        <v>6978192</v>
+        <v>6978417</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16596,11 +16602,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16627,45 +16628,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129302285</v>
+        <v>129295719</v>
       </c>
       <c r="B159" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628656</v>
+        <v>628846</v>
       </c>
       <c r="R159" t="n">
-        <v>6978459</v>
+        <v>6978364</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16698,11 +16699,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16729,45 +16725,49 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129302226</v>
+        <v>129290760</v>
       </c>
       <c r="B160" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628849</v>
+        <v>628499</v>
       </c>
       <c r="R160" t="n">
-        <v>6978507</v>
+        <v>6978448</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16826,10 +16826,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129289808</v>
+        <v>129302253</v>
       </c>
       <c r="B161" t="n">
-        <v>79039</v>
+        <v>57885</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16837,21 +16837,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16861,10 +16861,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628421</v>
+        <v>628759</v>
       </c>
       <c r="R161" t="n">
-        <v>6978541</v>
+        <v>6978235</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16923,45 +16923,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129295735</v>
+        <v>129302279</v>
       </c>
       <c r="B162" t="n">
-        <v>80179</v>
+        <v>98676</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628841</v>
+        <v>628884</v>
       </c>
       <c r="R162" t="n">
-        <v>6978384</v>
+        <v>6978488</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16994,6 +16994,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17020,10 +17025,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129295515</v>
+        <v>129302234</v>
       </c>
       <c r="B163" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17031,39 +17036,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628796</v>
+        <v>628641</v>
       </c>
       <c r="R163" t="n">
-        <v>6978384</v>
+        <v>6978450</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17096,11 +17096,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Sannolikt bohål av tretåig hackspett. Drygt två meter ovan mark i död gran. Bohålets diameter omkring 4,5 - 5 cm.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17130,7 +17125,7 @@
         <v>129290278</v>
       </c>
       <c r="B164" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17224,10 +17219,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129302253</v>
+        <v>129295515</v>
       </c>
       <c r="B165" t="n">
-        <v>57885</v>
+        <v>57725</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17235,34 +17230,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>628759</v>
+        <v>628796</v>
       </c>
       <c r="R165" t="n">
-        <v>6978235</v>
+        <v>6978384</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17295,6 +17295,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Sannolikt bohål av tretåig hackspett. Drygt två meter ovan mark i död gran. Bohålets diameter omkring 4,5 - 5 cm.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17321,10 +17326,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129302234</v>
+        <v>129289808</v>
       </c>
       <c r="B166" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17332,21 +17337,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17356,10 +17361,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>628641</v>
+        <v>628421</v>
       </c>
       <c r="R166" t="n">
-        <v>6978450</v>
+        <v>6978541</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17418,45 +17423,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129302279</v>
+        <v>129295735</v>
       </c>
       <c r="B167" t="n">
-        <v>98669</v>
+        <v>80179</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>628884</v>
+        <v>628841</v>
       </c>
       <c r="R167" t="n">
-        <v>6978488</v>
+        <v>6978384</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17489,11 +17494,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128734698</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128735541</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>128736016</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>128732126</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129181897</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>129184366</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129184816</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129185300</v>
       </c>
       <c r="B9" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129184595</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>129182054</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>129182187</v>
       </c>
       <c r="B12" t="n">
-        <v>56299</v>
+        <v>56301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>129187222</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>129169945</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2275,32 +2275,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129302283</v>
+        <v>129302237</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628664</v>
+        <v>628766</v>
       </c>
       <c r="R15" t="n">
-        <v>6978446</v>
+        <v>6978173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>60 stycken kan finnas mer gömda i mossan</t>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129302237</v>
+        <v>129302245</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628766</v>
+        <v>628749</v>
       </c>
       <c r="R16" t="n">
-        <v>6978173</v>
+        <v>6978341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,32 +2479,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129302245</v>
+        <v>129302283</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628749</v>
+        <v>628664</v>
       </c>
       <c r="R17" t="n">
-        <v>6978341</v>
+        <v>6978446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2584,7 +2584,7 @@
         <v>129295766</v>
       </c>
       <c r="B18" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>129292781</v>
       </c>
       <c r="B19" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>129295830</v>
       </c>
       <c r="B20" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,32 +2872,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302269</v>
+        <v>129302284</v>
       </c>
       <c r="B21" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628792</v>
+        <v>628667</v>
       </c>
       <c r="R21" t="n">
-        <v>6978309</v>
+        <v>6978461</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,6 +2943,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302284</v>
+        <v>129302278</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3004,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628667</v>
+        <v>628894</v>
       </c>
       <c r="R22" t="n">
-        <v>6978461</v>
+        <v>6978483</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,7 +3049,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,32 +3076,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302278</v>
+        <v>129302262</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3111,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628894</v>
+        <v>628800</v>
       </c>
       <c r="R23" t="n">
-        <v>6978483</v>
+        <v>6978306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3142,11 +3147,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,32 +3173,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129293584</v>
+        <v>129302265</v>
       </c>
       <c r="B24" t="n">
-        <v>91995</v>
+        <v>91827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628624</v>
+        <v>628772</v>
       </c>
       <c r="R24" t="n">
-        <v>6978328</v>
+        <v>6978157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3270,10 +3270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294036</v>
+        <v>129302240</v>
       </c>
       <c r="B25" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,34 +3281,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628728</v>
+        <v>628764</v>
       </c>
       <c r="R25" t="n">
-        <v>6978173</v>
+        <v>6978279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,6 +3341,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290628</v>
+        <v>129302243</v>
       </c>
       <c r="B26" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,21 +3383,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628499</v>
+        <v>628743</v>
       </c>
       <c r="R26" t="n">
-        <v>6978448</v>
+        <v>6978315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,6 +3443,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,50 +3474,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294050</v>
+        <v>129302269</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628728</v>
+        <v>628792</v>
       </c>
       <c r="R27" t="n">
-        <v>6978173</v>
+        <v>6978309</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,11 +3545,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129292558</v>
+        <v>129293584</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>91997</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,38 +3582,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628589</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6978414</v>
+        <v>6978328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302262</v>
+        <v>129294036</v>
       </c>
       <c r="B29" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,14 +3699,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628800</v>
+        <v>628728</v>
       </c>
       <c r="R29" t="n">
-        <v>6978306</v>
+        <v>6978173</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,10 +3765,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302243</v>
+        <v>129290628</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>91827</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,21 +3776,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628743</v>
+        <v>628499</v>
       </c>
       <c r="R30" t="n">
-        <v>6978315</v>
+        <v>6978448</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,11 +3836,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3871,10 +3862,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302265</v>
+        <v>129294050</v>
       </c>
       <c r="B31" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3882,34 +3873,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628772</v>
+        <v>628728</v>
       </c>
       <c r="R31" t="n">
-        <v>6978157</v>
+        <v>6978173</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3942,6 +3938,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,45 +3969,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302240</v>
+        <v>129292558</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628764</v>
+        <v>628589</v>
       </c>
       <c r="R32" t="n">
-        <v>6978279</v>
+        <v>6978414</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,11 +4044,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129302293</v>
+        <v>129295187</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628737</v>
+        <v>628834</v>
       </c>
       <c r="R33" t="n">
-        <v>6978300</v>
+        <v>6978251</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129302235</v>
+        <v>129290118</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628629</v>
+        <v>628453</v>
       </c>
       <c r="R34" t="n">
-        <v>6978532</v>
+        <v>6978518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129302277</v>
+        <v>129294218</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>96012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,34 +4275,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628899</v>
+        <v>628798</v>
       </c>
       <c r="R35" t="n">
-        <v>6978480</v>
+        <v>6978072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>150, finns troligtvis mer i mossan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4369,7 +4369,7 @@
         <v>129296183</v>
       </c>
       <c r="B36" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4463,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129295187</v>
+        <v>129293171</v>
       </c>
       <c r="B37" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,34 +4474,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628834</v>
+        <v>628702</v>
       </c>
       <c r="R37" t="n">
-        <v>6978251</v>
+        <v>6978339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4560,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129290118</v>
+        <v>129302293</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4571,21 +4580,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4595,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628453</v>
+        <v>628737</v>
       </c>
       <c r="R38" t="n">
-        <v>6978518</v>
+        <v>6978300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4657,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294218</v>
+        <v>129302277</v>
       </c>
       <c r="B39" t="n">
-        <v>96010</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,34 +4677,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1079</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628798</v>
+        <v>628899</v>
       </c>
       <c r="R39" t="n">
-        <v>6978072</v>
+        <v>6978480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4732,7 +4741,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4759,10 +4768,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293171</v>
+        <v>129302235</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,43 +4779,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628702</v>
+        <v>628629</v>
       </c>
       <c r="R40" t="n">
-        <v>6978339</v>
+        <v>6978532</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4868,7 +4868,7 @@
         <v>129302248</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>129294028</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>129293533</v>
       </c>
       <c r="B43" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>129291502</v>
       </c>
       <c r="B44" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>129296072</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>129290183</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>129290169</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129302275</v>
+        <v>129290084</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5600,17 +5600,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628663</v>
+        <v>628475</v>
       </c>
       <c r="R48" t="n">
-        <v>6978428</v>
+        <v>6978540</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5643,11 +5647,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5674,32 +5673,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129302276</v>
+        <v>129302294</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5709,10 +5708,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628648</v>
+        <v>628661</v>
       </c>
       <c r="R49" t="n">
-        <v>6978420</v>
+        <v>6978421</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5745,11 +5744,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5776,32 +5770,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129302231</v>
+        <v>129302275</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5811,10 +5805,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628752</v>
+        <v>628663</v>
       </c>
       <c r="R50" t="n">
-        <v>6978198</v>
+        <v>6978428</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,6 +5841,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,32 +5872,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302233</v>
+        <v>129302276</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5907,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628759</v>
+        <v>628648</v>
       </c>
       <c r="R51" t="n">
-        <v>6978233</v>
+        <v>6978420</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,6 +5943,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302294</v>
+        <v>129302231</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5981,21 +5985,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6005,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628661</v>
+        <v>628752</v>
       </c>
       <c r="R52" t="n">
-        <v>6978421</v>
+        <v>6978198</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129296084</v>
+        <v>129302233</v>
       </c>
       <c r="B53" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6078,21 +6082,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6102,10 +6106,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628959</v>
+        <v>628759</v>
       </c>
       <c r="R53" t="n">
-        <v>6978530</v>
+        <v>6978233</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6167,7 +6171,7 @@
         <v>129290616</v>
       </c>
       <c r="B54" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6264,7 +6268,7 @@
         <v>129290361</v>
       </c>
       <c r="B55" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6358,49 +6362,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129290084</v>
+        <v>129296084</v>
       </c>
       <c r="B56" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628475</v>
+        <v>628959</v>
       </c>
       <c r="R56" t="n">
-        <v>6978540</v>
+        <v>6978530</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129294015</v>
+        <v>129302274</v>
       </c>
       <c r="B57" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6490,14 +6490,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628728</v>
+        <v>628659</v>
       </c>
       <c r="R57" t="n">
-        <v>6978173</v>
+        <v>6978419</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6556,32 +6556,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129302271</v>
+        <v>129302252</v>
       </c>
       <c r="B58" t="n">
-        <v>97547</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628763</v>
+        <v>628837</v>
       </c>
       <c r="R58" t="n">
-        <v>6978273</v>
+        <v>6978500</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6627,6 +6627,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6653,10 +6658,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302252</v>
+        <v>129302229</v>
       </c>
       <c r="B59" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6664,21 +6669,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6688,10 +6693,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628837</v>
+        <v>628761</v>
       </c>
       <c r="R59" t="n">
-        <v>6978500</v>
+        <v>6978157</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6724,11 +6729,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6755,32 +6755,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302274</v>
+        <v>129302271</v>
       </c>
       <c r="B60" t="n">
-        <v>80144</v>
+        <v>97549</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628659</v>
+        <v>628763</v>
       </c>
       <c r="R60" t="n">
-        <v>6978419</v>
+        <v>6978273</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6855,7 +6855,7 @@
         <v>129302241</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6954,10 +6954,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302229</v>
+        <v>129295935</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>91556</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6965,21 +6965,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6989,10 +6989,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628761</v>
+        <v>628907</v>
       </c>
       <c r="R62" t="n">
-        <v>6978157</v>
+        <v>6978423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7051,45 +7051,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129295935</v>
+        <v>129293780</v>
       </c>
       <c r="B63" t="n">
-        <v>91554</v>
+        <v>57719</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>100110</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628907</v>
+        <v>628680</v>
       </c>
       <c r="R63" t="n">
-        <v>6978423</v>
+        <v>6978235</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7148,54 +7157,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B64" t="n">
-        <v>57717</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R64" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7254,32 +7254,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129302280</v>
+        <v>129302250</v>
       </c>
       <c r="B65" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628692</v>
+        <v>628495</v>
       </c>
       <c r="R65" t="n">
-        <v>6978432</v>
+        <v>6978647</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>200 ( ca) några blommande</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7356,10 +7356,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129302254</v>
+        <v>129302244</v>
       </c>
       <c r="B66" t="n">
-        <v>57722</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628894</v>
+        <v>628756</v>
       </c>
       <c r="R66" t="n">
-        <v>6978096</v>
+        <v>6978337</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7458,32 +7458,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129302250</v>
+        <v>129302259</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628495</v>
+        <v>628771</v>
       </c>
       <c r="R67" t="n">
-        <v>6978647</v>
+        <v>6978154</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7529,11 +7529,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7560,45 +7555,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129302244</v>
+        <v>129291473</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628756</v>
+        <v>628549</v>
       </c>
       <c r="R68" t="n">
-        <v>6978337</v>
+        <v>6978449</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7631,11 +7630,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7662,10 +7656,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129302259</v>
+        <v>129290108</v>
       </c>
       <c r="B69" t="n">
-        <v>91995</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7673,34 +7667,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628771</v>
+        <v>628447</v>
       </c>
       <c r="R69" t="n">
-        <v>6978154</v>
+        <v>6978522</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,45 +7757,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129295162</v>
+        <v>129302254</v>
       </c>
       <c r="B70" t="n">
-        <v>91995</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628834</v>
+        <v>628894</v>
       </c>
       <c r="R70" t="n">
-        <v>6978251</v>
+        <v>6978096</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7830,6 +7828,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7856,10 +7859,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129292729</v>
+        <v>129302280</v>
       </c>
       <c r="B71" t="n">
-        <v>91995</v>
+        <v>98678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7867,21 +7870,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7891,10 +7894,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628599</v>
+        <v>628692</v>
       </c>
       <c r="R71" t="n">
-        <v>6978448</v>
+        <v>6978432</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7927,6 +7930,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7953,10 +7961,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129291635</v>
+        <v>129295162</v>
       </c>
       <c r="B72" t="n">
-        <v>96010</v>
+        <v>91997</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7964,34 +7972,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1079</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628573</v>
+        <v>628834</v>
       </c>
       <c r="R72" t="n">
-        <v>6978423</v>
+        <v>6978251</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8050,32 +8058,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129294000</v>
+        <v>129292729</v>
       </c>
       <c r="B73" t="n">
-        <v>91540</v>
+        <v>91997</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8085,10 +8093,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628687</v>
+        <v>628599</v>
       </c>
       <c r="R73" t="n">
-        <v>6978194</v>
+        <v>6978448</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8147,10 +8155,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129291473</v>
+        <v>129291635</v>
       </c>
       <c r="B74" t="n">
-        <v>98676</v>
+        <v>96012</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8158,38 +8166,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628549</v>
+        <v>628573</v>
       </c>
       <c r="R74" t="n">
-        <v>6978449</v>
+        <v>6978423</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8248,49 +8252,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129290108</v>
+        <v>129294000</v>
       </c>
       <c r="B75" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628447</v>
+        <v>628687</v>
       </c>
       <c r="R75" t="n">
-        <v>6978522</v>
+        <v>6978194</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8352,7 +8352,7 @@
         <v>129297292</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>129295124</v>
       </c>
       <c r="B77" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8552,50 +8552,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129289501</v>
+        <v>129290447</v>
       </c>
       <c r="B78" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628451</v>
+        <v>628494</v>
       </c>
       <c r="R78" t="n">
-        <v>6978596</v>
+        <v>6978496</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8628,11 +8623,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8659,45 +8649,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129290447</v>
+        <v>129302281</v>
       </c>
       <c r="B79" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628494</v>
+        <v>628688</v>
       </c>
       <c r="R79" t="n">
-        <v>6978496</v>
+        <v>6978441</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8732,12 +8726,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8756,49 +8756,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302281</v>
+        <v>129302227</v>
       </c>
       <c r="B80" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628688</v>
+        <v>628851</v>
       </c>
       <c r="R80" t="n">
-        <v>6978441</v>
+        <v>6978504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8833,18 +8829,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8863,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302227</v>
+        <v>129289501</v>
       </c>
       <c r="B81" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8874,34 +8864,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628851</v>
+        <v>628451</v>
       </c>
       <c r="R81" t="n">
-        <v>6978504</v>
+        <v>6978596</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8934,6 +8929,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8963,7 +8963,7 @@
         <v>129302255</v>
       </c>
       <c r="B82" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>129296224</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,45 +9256,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129294276</v>
+        <v>129293890</v>
       </c>
       <c r="B85" t="n">
-        <v>91741</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628790</v>
+        <v>628691</v>
       </c>
       <c r="R85" t="n">
-        <v>6978034</v>
+        <v>6978242</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9327,6 +9332,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9353,32 +9363,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129296097</v>
+        <v>129302291</v>
       </c>
       <c r="B86" t="n">
-        <v>80173</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9398,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628959</v>
+        <v>628794</v>
       </c>
       <c r="R86" t="n">
-        <v>6978530</v>
+        <v>6978373</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,10 +9460,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129293914</v>
+        <v>129302232</v>
       </c>
       <c r="B87" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9461,39 +9471,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628690</v>
+        <v>628742</v>
       </c>
       <c r="R87" t="n">
-        <v>6978221</v>
+        <v>6978216</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9552,10 +9557,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129302232</v>
+        <v>129302267</v>
       </c>
       <c r="B88" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,21 +9568,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9587,10 +9592,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628742</v>
+        <v>628603</v>
       </c>
       <c r="R88" t="n">
-        <v>6978216</v>
+        <v>6978502</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9649,10 +9654,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302267</v>
+        <v>129302264</v>
       </c>
       <c r="B89" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9684,10 +9689,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628603</v>
+        <v>628796</v>
       </c>
       <c r="R89" t="n">
-        <v>6978502</v>
+        <v>6978261</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9746,32 +9751,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302264</v>
+        <v>129302260</v>
       </c>
       <c r="B90" t="n">
-        <v>91825</v>
+        <v>91997</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9786,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628796</v>
+        <v>628641</v>
       </c>
       <c r="R90" t="n">
-        <v>6978261</v>
+        <v>6978450</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,10 +9848,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302260</v>
+        <v>129302258</v>
       </c>
       <c r="B91" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9878,10 +9883,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628641</v>
+        <v>628851</v>
       </c>
       <c r="R91" t="n">
-        <v>6978450</v>
+        <v>6978502</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9940,32 +9945,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129302291</v>
+        <v>129289873</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>91506</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9975,10 +9980,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628794</v>
+        <v>628447</v>
       </c>
       <c r="R92" t="n">
-        <v>6978373</v>
+        <v>6978522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10037,32 +10042,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129302258</v>
+        <v>129296097</v>
       </c>
       <c r="B93" t="n">
-        <v>91995</v>
+        <v>80175</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10072,10 +10077,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628851</v>
+        <v>628959</v>
       </c>
       <c r="R93" t="n">
-        <v>6978502</v>
+        <v>6978530</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10134,45 +10139,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129289873</v>
+        <v>129294276</v>
       </c>
       <c r="B94" t="n">
-        <v>91504</v>
+        <v>91743</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>48</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628447</v>
+        <v>628790</v>
       </c>
       <c r="R94" t="n">
-        <v>6978522</v>
+        <v>6978034</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10234,7 +10239,7 @@
         <v>129292746</v>
       </c>
       <c r="B95" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10331,7 +10336,7 @@
         <v>129290229</v>
       </c>
       <c r="B96" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10425,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129293890</v>
+        <v>129293914</v>
       </c>
       <c r="B97" t="n">
-        <v>57725</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10436,27 +10441,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10465,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628691</v>
+        <v>628690</v>
       </c>
       <c r="R97" t="n">
-        <v>6978242</v>
+        <v>6978221</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10501,11 +10506,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129302295</v>
+        <v>129295410</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10543,34 +10543,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628463</v>
+        <v>628767</v>
       </c>
       <c r="R98" t="n">
-        <v>6978635</v>
+        <v>6978383</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,10 +10638,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129295410</v>
+        <v>129302295</v>
       </c>
       <c r="B99" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10640,43 +10649,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628767</v>
+        <v>628463</v>
       </c>
       <c r="R99" t="n">
-        <v>6978383</v>
+        <v>6978635</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10738,7 +10738,7 @@
         <v>129293044</v>
       </c>
       <c r="B100" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10836,32 +10836,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129302268</v>
+        <v>129302282</v>
       </c>
       <c r="B101" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628719</v>
+        <v>628654</v>
       </c>
       <c r="R101" t="n">
-        <v>6978594</v>
+        <v>6978418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,6 +10907,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10936,7 +10941,7 @@
         <v>129302287</v>
       </c>
       <c r="B102" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11038,7 +11043,7 @@
         <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11132,10 +11137,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129295020</v>
+        <v>129302268</v>
       </c>
       <c r="B104" t="n">
-        <v>80179</v>
+        <v>97549</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11143,34 +11148,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628826</v>
+        <v>628719</v>
       </c>
       <c r="R104" t="n">
-        <v>6978150</v>
+        <v>6978594</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11229,45 +11234,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302282</v>
+        <v>129295020</v>
       </c>
       <c r="B105" t="n">
-        <v>98676</v>
+        <v>80181</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628654</v>
+        <v>628826</v>
       </c>
       <c r="R105" t="n">
-        <v>6978418</v>
+        <v>6978150</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11300,11 +11305,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11334,7 +11334,7 @@
         <v>129295651</v>
       </c>
       <c r="B106" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129302246</v>
+        <v>129293300</v>
       </c>
       <c r="B107" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11461,16 +11461,21 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628750</v>
+        <v>628665</v>
       </c>
       <c r="R107" t="n">
-        <v>6978346</v>
+        <v>6978376</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11507,7 +11512,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11537,7 +11542,7 @@
         <v>129302251</v>
       </c>
       <c r="B108" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11636,10 +11641,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129293395</v>
+        <v>129302246</v>
       </c>
       <c r="B109" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11647,21 +11652,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11671,10 +11676,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628616</v>
+        <v>628750</v>
       </c>
       <c r="R109" t="n">
-        <v>6978368</v>
+        <v>6978346</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,6 +11712,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11733,10 +11743,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129289885</v>
+        <v>129293395</v>
       </c>
       <c r="B110" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11768,10 +11778,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>628447</v>
+        <v>628616</v>
       </c>
       <c r="R110" t="n">
-        <v>6978522</v>
+        <v>6978368</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11830,10 +11840,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129293300</v>
+        <v>129289885</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11841,39 +11851,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628665</v>
+        <v>628447</v>
       </c>
       <c r="R111" t="n">
-        <v>6978376</v>
+        <v>6978522</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11906,11 +11911,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302247</v>
+        <v>129302290</v>
       </c>
       <c r="B112" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628749</v>
+        <v>628712</v>
       </c>
       <c r="R112" t="n">
-        <v>6978349</v>
+        <v>6978591</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,11 +12008,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12039,32 +12034,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302290</v>
+        <v>129302289</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>57719</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12074,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628712</v>
+        <v>628493</v>
       </c>
       <c r="R113" t="n">
-        <v>6978591</v>
+        <v>6978648</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,6 +12105,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12136,10 +12136,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302225</v>
+        <v>129302247</v>
       </c>
       <c r="B114" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12147,21 +12147,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628856</v>
+        <v>628749</v>
       </c>
       <c r="R114" t="n">
-        <v>6978527</v>
+        <v>6978349</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12207,6 +12207,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12233,32 +12238,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302289</v>
+        <v>129302225</v>
       </c>
       <c r="B115" t="n">
-        <v>57717</v>
+        <v>91542</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12268,10 +12273,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628493</v>
+        <v>628856</v>
       </c>
       <c r="R115" t="n">
-        <v>6978648</v>
+        <v>6978527</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12304,11 +12309,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12338,7 +12338,7 @@
         <v>129302256</v>
       </c>
       <c r="B116" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12437,32 +12437,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129295820</v>
+        <v>129293475</v>
       </c>
       <c r="B117" t="n">
-        <v>91995</v>
+        <v>91827</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628889</v>
+        <v>628623</v>
       </c>
       <c r="R117" t="n">
-        <v>6978417</v>
+        <v>6978341</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12534,32 +12534,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129293475</v>
+        <v>129295820</v>
       </c>
       <c r="B118" t="n">
-        <v>91825</v>
+        <v>91997</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628623</v>
+        <v>628889</v>
       </c>
       <c r="R118" t="n">
-        <v>6978341</v>
+        <v>6978417</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12631,45 +12631,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129302242</v>
+        <v>129294695</v>
       </c>
       <c r="B119" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628750</v>
+        <v>628831</v>
       </c>
       <c r="R119" t="n">
-        <v>6978284</v>
+        <v>6978180</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12702,11 +12702,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12733,32 +12728,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129302273</v>
+        <v>129297070</v>
       </c>
       <c r="B120" t="n">
-        <v>80144</v>
+        <v>91997</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12768,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628878</v>
+        <v>628764</v>
       </c>
       <c r="R120" t="n">
-        <v>6978535</v>
+        <v>6978591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12830,45 +12825,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129302257</v>
+        <v>129295812</v>
       </c>
       <c r="B121" t="n">
-        <v>91995</v>
+        <v>91542</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628794</v>
+        <v>628900</v>
       </c>
       <c r="R121" t="n">
-        <v>6978311</v>
+        <v>6978416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12927,10 +12922,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129293329</v>
+        <v>129302273</v>
       </c>
       <c r="B122" t="n">
-        <v>57722</v>
+        <v>80146</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12938,43 +12933,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628640</v>
+        <v>628878</v>
       </c>
       <c r="R122" t="n">
-        <v>6978364</v>
+        <v>6978535</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13033,50 +13019,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129294983</v>
+        <v>129302257</v>
       </c>
       <c r="B123" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628826</v>
+        <v>628794</v>
       </c>
       <c r="R123" t="n">
-        <v>6978150</v>
+        <v>6978311</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13109,11 +13090,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Sannolikt bohål av tretåig hackspett. I gran. Omkring 6 meter upp. Klättrade upp i trädet och bohålet stämmer mycket väl in på tretå. Prydligt uthackat och relativt litet.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13140,45 +13116,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129294695</v>
+        <v>129302242</v>
       </c>
       <c r="B124" t="n">
-        <v>91995</v>
+        <v>57727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628831</v>
+        <v>628750</v>
       </c>
       <c r="R124" t="n">
-        <v>6978180</v>
+        <v>6978284</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13211,6 +13187,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13237,45 +13218,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129297070</v>
+        <v>129293329</v>
       </c>
       <c r="B125" t="n">
-        <v>91995</v>
+        <v>57724</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628764</v>
+        <v>628640</v>
       </c>
       <c r="R125" t="n">
-        <v>6978591</v>
+        <v>6978364</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13334,45 +13324,49 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129295812</v>
+        <v>129291461</v>
       </c>
       <c r="B126" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628900</v>
+        <v>628547</v>
       </c>
       <c r="R126" t="n">
-        <v>6978416</v>
+        <v>6978457</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13431,10 +13425,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129302270</v>
+        <v>129290692</v>
       </c>
       <c r="B127" t="n">
-        <v>97547</v>
+        <v>80106</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13442,21 +13436,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13466,10 +13460,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628812</v>
+        <v>628515</v>
       </c>
       <c r="R127" t="n">
-        <v>6978062</v>
+        <v>6978451</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13528,45 +13522,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129302296</v>
+        <v>129294090</v>
       </c>
       <c r="B128" t="n">
-        <v>79039</v>
+        <v>80106</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628449</v>
+        <v>628743</v>
       </c>
       <c r="R128" t="n">
-        <v>6978612</v>
+        <v>6978155</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13628,7 +13622,7 @@
         <v>129302239</v>
       </c>
       <c r="B129" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13727,49 +13721,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129291461</v>
+        <v>129291548</v>
       </c>
       <c r="B130" t="n">
-        <v>98676</v>
+        <v>80050</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628547</v>
+        <v>628549</v>
       </c>
       <c r="R130" t="n">
-        <v>6978457</v>
+        <v>6978433</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13831,7 +13821,7 @@
         <v>129289677</v>
       </c>
       <c r="B131" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13933,7 +13923,7 @@
         <v>129290523</v>
       </c>
       <c r="B132" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14037,32 +14027,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129290692</v>
+        <v>129302296</v>
       </c>
       <c r="B133" t="n">
-        <v>80104</v>
+        <v>79041</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14072,10 +14062,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628515</v>
+        <v>628449</v>
       </c>
       <c r="R133" t="n">
-        <v>6978451</v>
+        <v>6978612</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14134,10 +14124,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129294090</v>
+        <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>80104</v>
+        <v>97549</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14145,34 +14135,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628743</v>
+        <v>628812</v>
       </c>
       <c r="R134" t="n">
-        <v>6978155</v>
+        <v>6978062</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14231,32 +14221,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129291548</v>
+        <v>129302228</v>
       </c>
       <c r="B135" t="n">
-        <v>80048</v>
+        <v>91542</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14266,10 +14256,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628549</v>
+        <v>628870</v>
       </c>
       <c r="R135" t="n">
-        <v>6978433</v>
+        <v>6978469</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14328,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129302228</v>
+        <v>129294072</v>
       </c>
       <c r="B136" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14339,34 +14329,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628870</v>
+        <v>628731</v>
       </c>
       <c r="R136" t="n">
-        <v>6978469</v>
+        <v>6978165</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14425,10 +14415,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294072</v>
+        <v>129295655</v>
       </c>
       <c r="B137" t="n">
-        <v>80144</v>
+        <v>57724</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14436,34 +14426,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628731</v>
+        <v>628796</v>
       </c>
       <c r="R137" t="n">
-        <v>6978165</v>
+        <v>6978373</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14522,10 +14521,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B138" t="n">
-        <v>57722</v>
+        <v>57727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14533,16 +14532,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14550,26 +14549,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R138" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14602,6 +14597,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14628,10 +14628,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129293208</v>
+        <v>129293275</v>
       </c>
       <c r="B139" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14668,10 +14668,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628695</v>
+        <v>628693</v>
       </c>
       <c r="R139" t="n">
-        <v>6978356</v>
+        <v>6978372</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14735,10 +14735,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129293275</v>
+        <v>129291606</v>
       </c>
       <c r="B140" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14746,39 +14746,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628693</v>
+        <v>628564</v>
       </c>
       <c r="R140" t="n">
-        <v>6978372</v>
+        <v>6978436</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14811,11 +14806,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14842,32 +14832,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129302266</v>
+        <v>129290695</v>
       </c>
       <c r="B141" t="n">
-        <v>91825</v>
+        <v>80182</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14877,10 +14867,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628639</v>
+        <v>628509</v>
       </c>
       <c r="R141" t="n">
-        <v>6978441</v>
+        <v>6978440</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14939,10 +14929,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129302236</v>
+        <v>129293977</v>
       </c>
       <c r="B142" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14968,16 +14958,21 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628854</v>
+        <v>628687</v>
       </c>
       <c r="R142" t="n">
-        <v>6978069</v>
+        <v>6978194</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15014,7 +15009,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Födosökande tretåig hackspett observerad, kön hona.</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15041,10 +15036,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129291606</v>
+        <v>129302266</v>
       </c>
       <c r="B143" t="n">
-        <v>80144</v>
+        <v>91827</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15052,21 +15047,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15076,10 +15071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628564</v>
+        <v>628639</v>
       </c>
       <c r="R143" t="n">
-        <v>6978436</v>
+        <v>6978441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15138,32 +15133,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129290695</v>
+        <v>129302288</v>
       </c>
       <c r="B144" t="n">
-        <v>80180</v>
+        <v>98678</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15173,10 +15168,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628509</v>
+        <v>628636</v>
       </c>
       <c r="R144" t="n">
-        <v>6978440</v>
+        <v>6978511</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15209,6 +15204,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15235,50 +15235,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129293977</v>
+        <v>129302272</v>
       </c>
       <c r="B145" t="n">
-        <v>57725</v>
+        <v>97549</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628687</v>
+        <v>628641</v>
       </c>
       <c r="R145" t="n">
-        <v>6978194</v>
+        <v>6978450</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15311,11 +15306,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15342,45 +15332,49 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129302272</v>
+        <v>129290760</v>
       </c>
       <c r="B146" t="n">
-        <v>97547</v>
+        <v>98678</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628641</v>
+        <v>628499</v>
       </c>
       <c r="R146" t="n">
-        <v>6978450</v>
+        <v>6978448</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15439,32 +15433,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302288</v>
+        <v>129302292</v>
       </c>
       <c r="B147" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15474,10 +15468,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628636</v>
+        <v>628819</v>
       </c>
       <c r="R147" t="n">
-        <v>6978511</v>
+        <v>6978067</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15514,7 +15508,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15541,10 +15535,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129302292</v>
+        <v>129302238</v>
       </c>
       <c r="B148" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15552,21 +15546,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15576,10 +15570,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628819</v>
+        <v>628757</v>
       </c>
       <c r="R148" t="n">
-        <v>6978067</v>
+        <v>6978192</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15616,7 +15610,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15646,7 +15640,7 @@
         <v>129302249</v>
       </c>
       <c r="B149" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15748,7 +15742,7 @@
         <v>129302230</v>
       </c>
       <c r="B150" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15845,7 +15839,7 @@
         <v>129302261</v>
       </c>
       <c r="B151" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15939,10 +15933,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302238</v>
+        <v>129302226</v>
       </c>
       <c r="B152" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15950,21 +15944,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15974,10 +15968,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628757</v>
+        <v>628849</v>
       </c>
       <c r="R152" t="n">
-        <v>6978192</v>
+        <v>6978507</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16010,11 +16004,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16041,32 +16030,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302226</v>
+        <v>129302285</v>
       </c>
       <c r="B153" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16076,10 +16065,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628849</v>
+        <v>628656</v>
       </c>
       <c r="R153" t="n">
-        <v>6978507</v>
+        <v>6978459</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16112,6 +16101,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16141,7 +16135,7 @@
         <v>129302297</v>
       </c>
       <c r="B154" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16235,45 +16229,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302285</v>
+        <v>129295136</v>
       </c>
       <c r="B155" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628656</v>
+        <v>628799</v>
       </c>
       <c r="R155" t="n">
-        <v>6978459</v>
+        <v>6978234</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16306,11 +16300,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16337,10 +16326,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129295136</v>
+        <v>129295133</v>
       </c>
       <c r="B156" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16348,21 +16337,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16372,10 +16361,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628799</v>
+        <v>628788</v>
       </c>
       <c r="R156" t="n">
-        <v>6978234</v>
+        <v>6978227</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16434,10 +16423,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129295133</v>
+        <v>129295719</v>
       </c>
       <c r="B157" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16445,21 +16434,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16469,10 +16458,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628788</v>
+        <v>628846</v>
       </c>
       <c r="R157" t="n">
-        <v>6978227</v>
+        <v>6978364</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16534,7 +16523,7 @@
         <v>129295841</v>
       </c>
       <c r="B158" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16628,10 +16617,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129295719</v>
+        <v>129302234</v>
       </c>
       <c r="B159" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16639,34 +16628,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628846</v>
+        <v>628641</v>
       </c>
       <c r="R159" t="n">
-        <v>6978364</v>
+        <v>6978450</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16725,49 +16714,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129290760</v>
+        <v>129302253</v>
       </c>
       <c r="B160" t="n">
-        <v>98676</v>
+        <v>57887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628499</v>
+        <v>628759</v>
       </c>
       <c r="R160" t="n">
-        <v>6978448</v>
+        <v>6978235</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16826,32 +16811,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129302253</v>
+        <v>129302279</v>
       </c>
       <c r="B161" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16861,10 +16846,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628759</v>
+        <v>628884</v>
       </c>
       <c r="R161" t="n">
-        <v>6978235</v>
+        <v>6978488</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16897,6 +16882,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16923,32 +16913,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129302279</v>
+        <v>129289808</v>
       </c>
       <c r="B162" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16958,10 +16948,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628884</v>
+        <v>628421</v>
       </c>
       <c r="R162" t="n">
-        <v>6978488</v>
+        <v>6978541</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16994,11 +16984,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17025,45 +17010,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129302234</v>
+        <v>129295735</v>
       </c>
       <c r="B163" t="n">
-        <v>91540</v>
+        <v>80181</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628641</v>
+        <v>628841</v>
       </c>
       <c r="R163" t="n">
-        <v>6978450</v>
+        <v>6978384</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17125,7 +17110,7 @@
         <v>129290278</v>
       </c>
       <c r="B164" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17219,10 +17204,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129295515</v>
+        <v>129294983</v>
       </c>
       <c r="B165" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17259,10 +17244,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>628796</v>
+        <v>628826</v>
       </c>
       <c r="R165" t="n">
-        <v>6978384</v>
+        <v>6978150</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17299,7 +17284,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Sannolikt bohål av tretåig hackspett. Drygt två meter ovan mark i död gran. Bohålets diameter omkring 4,5 - 5 cm.</t>
+          <t>Sannolikt bohål av tretåig hackspett. I gran. Omkring 6 meter upp. Klättrade upp i trädet och bohålet stämmer mycket väl in på tretå. Prydligt uthackat och relativt litet.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17326,10 +17311,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129289808</v>
+        <v>129302236</v>
       </c>
       <c r="B166" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17337,21 +17322,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17361,10 +17346,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>628421</v>
+        <v>628854</v>
       </c>
       <c r="R166" t="n">
-        <v>6978541</v>
+        <v>6978069</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17397,6 +17382,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Födosökande tretåig hackspett observerad, kön hona.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17423,42 +17413,50 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129295735</v>
+        <v>129295515</v>
       </c>
       <c r="B167" t="n">
-        <v>80179</v>
+        <v>57727</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>628841</v>
+        <v>628796</v>
       </c>
       <c r="R167" t="n">
         <v>6978384</v>
@@ -17494,6 +17492,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Sannolikt bohål av tretåig hackspett. Drygt två meter ovan mark i död gran. Bohålets innerdiameter omkring 4,5 - 5 cm.</t>
         </is>
       </c>
       <c r="AD167" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,45 +2275,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129302237</v>
+        <v>129295766</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628766</v>
+        <v>628846</v>
       </c>
       <c r="R15" t="n">
-        <v>6978173</v>
+        <v>6978364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,11 +2346,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,32 +2372,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129302245</v>
+        <v>129292781</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>92242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628749</v>
+        <v>628590</v>
       </c>
       <c r="R16" t="n">
-        <v>6978341</v>
+        <v>6978436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,11 +2443,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,32 +2469,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129302283</v>
+        <v>129295830</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>92242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2514,10 +2504,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628664</v>
+        <v>628896</v>
       </c>
       <c r="R17" t="n">
-        <v>6978446</v>
+        <v>6978430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,11 +2540,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,45 +2566,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129295766</v>
+        <v>129302237</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628846</v>
+        <v>628766</v>
       </c>
       <c r="R18" t="n">
-        <v>6978364</v>
+        <v>6978173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,6 +2637,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,32 +2668,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129292781</v>
+        <v>129302245</v>
       </c>
       <c r="B19" t="n">
-        <v>92242</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2713,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628590</v>
+        <v>628749</v>
       </c>
       <c r="R19" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2749,6 +2739,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,32 +2770,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129295830</v>
+        <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>92242</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2810,10 +2805,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628896</v>
+        <v>628664</v>
       </c>
       <c r="R20" t="n">
-        <v>6978430</v>
+        <v>6978446</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,6 +2841,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,45 +2872,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302284</v>
+        <v>129294050</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628667</v>
+        <v>628728</v>
       </c>
       <c r="R21" t="n">
-        <v>6978461</v>
+        <v>6978173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2952,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,45 +2979,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302278</v>
+        <v>129294036</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628894</v>
+        <v>628728</v>
       </c>
       <c r="R22" t="n">
-        <v>6978483</v>
+        <v>6978173</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,11 +3050,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,7 +3076,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302262</v>
+        <v>129290628</v>
       </c>
       <c r="B23" t="n">
         <v>91827</v>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628800</v>
+        <v>628499</v>
       </c>
       <c r="R23" t="n">
-        <v>6978306</v>
+        <v>6978448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,45 +3173,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302265</v>
+        <v>129292558</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628772</v>
+        <v>628589</v>
       </c>
       <c r="R24" t="n">
-        <v>6978157</v>
+        <v>6978414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3270,10 +3274,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302240</v>
+        <v>129302262</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3305,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628764</v>
+        <v>628800</v>
       </c>
       <c r="R25" t="n">
-        <v>6978279</v>
+        <v>6978306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,11 +3345,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302243</v>
+        <v>129302265</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3383,21 +3382,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3407,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628743</v>
+        <v>628772</v>
       </c>
       <c r="R26" t="n">
-        <v>6978315</v>
+        <v>6978157</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,11 +3442,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,32 +3468,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302269</v>
+        <v>129302284</v>
       </c>
       <c r="B27" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628792</v>
+        <v>628667</v>
       </c>
       <c r="R27" t="n">
-        <v>6978309</v>
+        <v>6978461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3545,6 +3539,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129293584</v>
+        <v>129302278</v>
       </c>
       <c r="B28" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,21 +3581,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628894</v>
       </c>
       <c r="R28" t="n">
-        <v>6978328</v>
+        <v>6978483</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,6 +3641,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294036</v>
+        <v>129302243</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3679,34 +3683,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628728</v>
+        <v>628743</v>
       </c>
       <c r="R29" t="n">
-        <v>6978173</v>
+        <v>6978315</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3739,6 +3743,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3765,10 +3774,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290628</v>
+        <v>129302240</v>
       </c>
       <c r="B30" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,21 +3785,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628499</v>
+        <v>628764</v>
       </c>
       <c r="R30" t="n">
-        <v>6978448</v>
+        <v>6978279</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3836,6 +3845,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3862,50 +3876,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129294050</v>
+        <v>129302269</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628728</v>
+        <v>628792</v>
       </c>
       <c r="R31" t="n">
-        <v>6978173</v>
+        <v>6978309</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,11 +3947,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3969,10 +3973,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129292558</v>
+        <v>129293584</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3980,38 +3984,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628589</v>
+        <v>628624</v>
       </c>
       <c r="R32" t="n">
-        <v>6978414</v>
+        <v>6978328</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129295187</v>
+        <v>129290118</v>
       </c>
       <c r="B33" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628834</v>
+        <v>628453</v>
       </c>
       <c r="R33" t="n">
-        <v>6978251</v>
+        <v>6978518</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,45 +4167,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129290118</v>
+        <v>129294218</v>
       </c>
       <c r="B34" t="n">
-        <v>91542</v>
+        <v>96012</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628453</v>
+        <v>628798</v>
       </c>
       <c r="R34" t="n">
-        <v>6978518</v>
+        <v>6978072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,6 +4238,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,45 +4269,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294218</v>
+        <v>129296183</v>
       </c>
       <c r="B35" t="n">
-        <v>96012</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628798</v>
+        <v>629055</v>
       </c>
       <c r="R35" t="n">
-        <v>6978072</v>
+        <v>6978511</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,11 +4340,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129296183</v>
+        <v>129293171</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,34 +4377,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>629055</v>
+        <v>628702</v>
       </c>
       <c r="R36" t="n">
-        <v>6978511</v>
+        <v>6978339</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293171</v>
+        <v>129295187</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,43 +4483,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628702</v>
+        <v>628834</v>
       </c>
       <c r="R37" t="n">
-        <v>6978339</v>
+        <v>6978251</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302293</v>
+        <v>129302235</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628737</v>
+        <v>628629</v>
       </c>
       <c r="R38" t="n">
-        <v>6978300</v>
+        <v>6978532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,32 +4666,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302277</v>
+        <v>129302293</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628899</v>
+        <v>628737</v>
       </c>
       <c r="R39" t="n">
-        <v>6978480</v>
+        <v>6978300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4737,11 +4737,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,32 +4763,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129302235</v>
+        <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4803,10 +4798,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628629</v>
+        <v>628899</v>
       </c>
       <c r="R40" t="n">
-        <v>6978532</v>
+        <v>6978480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,6 +4834,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,7 +4865,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129302248</v>
+        <v>129296072</v>
       </c>
       <c r="B41" t="n">
         <v>57727</v>
@@ -4893,17 +4893,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628679</v>
+        <v>628971</v>
       </c>
       <c r="R41" t="n">
-        <v>6978469</v>
+        <v>6978518</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,11 +4945,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,10 +4971,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129294028</v>
+        <v>129291502</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4978,34 +4982,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628728</v>
+        <v>628564</v>
       </c>
       <c r="R42" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5064,10 +5068,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293533</v>
+        <v>129290183</v>
       </c>
       <c r="B43" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5075,34 +5079,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628623</v>
+        <v>628436</v>
       </c>
       <c r="R43" t="n">
-        <v>6978341</v>
+        <v>6978498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129291502</v>
+        <v>129302248</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5196,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628564</v>
+        <v>628679</v>
       </c>
       <c r="R44" t="n">
-        <v>6978436</v>
+        <v>6978469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5232,6 +5240,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5258,10 +5271,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129296072</v>
+        <v>129294028</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5269,43 +5282,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628971</v>
+        <v>628728</v>
       </c>
       <c r="R45" t="n">
-        <v>6978518</v>
+        <v>6978173</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,10 +5368,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129290183</v>
+        <v>129293533</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5375,38 +5379,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628436</v>
+        <v>628623</v>
       </c>
       <c r="R46" t="n">
-        <v>6978498</v>
+        <v>6978341</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290169</v>
+        <v>129296084</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,39 +5476,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628453</v>
+        <v>628959</v>
       </c>
       <c r="R47" t="n">
-        <v>6978518</v>
+        <v>6978530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5541,11 +5536,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5572,49 +5562,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290084</v>
+        <v>129290616</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628475</v>
+        <v>628499</v>
       </c>
       <c r="R48" t="n">
-        <v>6978540</v>
+        <v>6978448</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5673,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129302294</v>
+        <v>129290361</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5684,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5708,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628661</v>
+        <v>628465</v>
       </c>
       <c r="R49" t="n">
-        <v>6978421</v>
+        <v>6978491</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5770,45 +5756,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129302275</v>
+        <v>129290169</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628663</v>
+        <v>628453</v>
       </c>
       <c r="R50" t="n">
-        <v>6978428</v>
+        <v>6978518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5845,7 +5836,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5872,7 +5863,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302276</v>
+        <v>129290084</v>
       </c>
       <c r="B51" t="n">
         <v>98678</v>
@@ -5900,17 +5891,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628648</v>
+        <v>628475</v>
       </c>
       <c r="R51" t="n">
-        <v>6978420</v>
+        <v>6978540</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,11 +5938,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6168,10 +6158,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129290616</v>
+        <v>129302294</v>
       </c>
       <c r="B54" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6179,21 +6169,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6203,10 +6193,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628499</v>
+        <v>628661</v>
       </c>
       <c r="R54" t="n">
-        <v>6978448</v>
+        <v>6978421</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,32 +6255,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129290361</v>
+        <v>129302275</v>
       </c>
       <c r="B55" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6300,10 +6290,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628465</v>
+        <v>628663</v>
       </c>
       <c r="R55" t="n">
-        <v>6978491</v>
+        <v>6978428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6336,6 +6326,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,32 +6357,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129296084</v>
+        <v>129302276</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6392,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628959</v>
+        <v>628648</v>
       </c>
       <c r="R56" t="n">
-        <v>6978530</v>
+        <v>6978420</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6433,6 +6428,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,32 +6658,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302229</v>
+        <v>129302271</v>
       </c>
       <c r="B59" t="n">
-        <v>91542</v>
+        <v>97549</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628761</v>
+        <v>628763</v>
       </c>
       <c r="R59" t="n">
-        <v>6978157</v>
+        <v>6978273</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302271</v>
+        <v>129295935</v>
       </c>
       <c r="B60" t="n">
-        <v>97549</v>
+        <v>91556</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628763</v>
+        <v>628907</v>
       </c>
       <c r="R60" t="n">
-        <v>6978273</v>
+        <v>6978423</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302241</v>
+        <v>129294015</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6863,34 +6863,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628741</v>
+        <v>628728</v>
       </c>
       <c r="R61" t="n">
-        <v>6978271</v>
+        <v>6978173</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,11 +6923,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6954,45 +6949,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129295935</v>
+        <v>129293780</v>
       </c>
       <c r="B62" t="n">
-        <v>91556</v>
+        <v>57719</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>100110</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628907</v>
+        <v>628680</v>
       </c>
       <c r="R62" t="n">
-        <v>6978423</v>
+        <v>6978235</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7051,54 +7055,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129293780</v>
+        <v>129302229</v>
       </c>
       <c r="B63" t="n">
-        <v>57719</v>
+        <v>91542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628680</v>
+        <v>628761</v>
       </c>
       <c r="R63" t="n">
-        <v>6978235</v>
+        <v>6978157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7157,10 +7152,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129294015</v>
+        <v>129302241</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7168,34 +7163,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628728</v>
+        <v>628741</v>
       </c>
       <c r="R64" t="n">
-        <v>6978173</v>
+        <v>6978271</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,6 +7223,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7254,45 +7254,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129302250</v>
+        <v>129295162</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91997</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628495</v>
+        <v>628834</v>
       </c>
       <c r="R65" t="n">
-        <v>6978647</v>
+        <v>6978251</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,11 +7325,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7356,32 +7351,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129302244</v>
+        <v>129292729</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91997</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7391,10 +7386,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628756</v>
+        <v>628599</v>
       </c>
       <c r="R66" t="n">
-        <v>6978337</v>
+        <v>6978448</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7427,11 +7422,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7458,10 +7448,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129302259</v>
+        <v>129291635</v>
       </c>
       <c r="B67" t="n">
-        <v>91997</v>
+        <v>96012</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7469,21 +7459,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>1079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7493,10 +7483,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628771</v>
+        <v>628573</v>
       </c>
       <c r="R67" t="n">
-        <v>6978154</v>
+        <v>6978423</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7555,49 +7545,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129291473</v>
+        <v>129294000</v>
       </c>
       <c r="B68" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628549</v>
+        <v>628687</v>
       </c>
       <c r="R68" t="n">
-        <v>6978449</v>
+        <v>6978194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7656,7 +7642,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129290108</v>
+        <v>129291473</v>
       </c>
       <c r="B69" t="n">
         <v>98678</v>
@@ -7686,7 +7672,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7695,10 +7681,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628447</v>
+        <v>628549</v>
       </c>
       <c r="R69" t="n">
-        <v>6978522</v>
+        <v>6978449</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7757,45 +7743,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129302254</v>
+        <v>129290108</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628894</v>
+        <v>628447</v>
       </c>
       <c r="R70" t="n">
-        <v>6978096</v>
+        <v>6978522</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7828,11 +7818,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7859,32 +7844,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129302280</v>
+        <v>129302250</v>
       </c>
       <c r="B71" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7894,10 +7879,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628692</v>
+        <v>628495</v>
       </c>
       <c r="R71" t="n">
-        <v>6978432</v>
+        <v>6978647</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7934,7 +7919,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>200 ( ca) några blommande</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7961,45 +7946,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129295162</v>
+        <v>129302244</v>
       </c>
       <c r="B72" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628834</v>
+        <v>628756</v>
       </c>
       <c r="R72" t="n">
-        <v>6978251</v>
+        <v>6978337</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8032,6 +8017,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8058,32 +8048,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129292729</v>
+        <v>129302254</v>
       </c>
       <c r="B73" t="n">
-        <v>91997</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8093,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628599</v>
+        <v>628894</v>
       </c>
       <c r="R73" t="n">
-        <v>6978448</v>
+        <v>6978096</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8129,6 +8119,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8155,10 +8150,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129291635</v>
+        <v>129302259</v>
       </c>
       <c r="B74" t="n">
-        <v>96012</v>
+        <v>91997</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8166,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1079</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8190,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628573</v>
+        <v>628771</v>
       </c>
       <c r="R74" t="n">
-        <v>6978423</v>
+        <v>6978154</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8252,10 +8247,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129294000</v>
+        <v>129297292</v>
       </c>
       <c r="B75" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,34 +8258,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628687</v>
+        <v>628429</v>
       </c>
       <c r="R75" t="n">
-        <v>6978194</v>
+        <v>6978625</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8349,54 +8353,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129297292</v>
+        <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628429</v>
+        <v>628692</v>
       </c>
       <c r="R76" t="n">
-        <v>6978625</v>
+        <v>6978432</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,6 +8424,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8552,45 +8552,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129290447</v>
+        <v>129289501</v>
       </c>
       <c r="B78" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628494</v>
+        <v>628451</v>
       </c>
       <c r="R78" t="n">
-        <v>6978496</v>
+        <v>6978596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,6 +8628,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8649,49 +8659,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129302281</v>
+        <v>129290447</v>
       </c>
       <c r="B79" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628688</v>
+        <v>628494</v>
       </c>
       <c r="R79" t="n">
-        <v>6978441</v>
+        <v>6978496</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8726,18 +8732,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129289501</v>
+        <v>129302255</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8864,16 +8864,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8882,21 +8882,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628451</v>
+        <v>628712</v>
       </c>
       <c r="R81" t="n">
-        <v>6978596</v>
+        <v>6978376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8933,7 +8928,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8960,45 +8955,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302255</v>
+        <v>129302281</v>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628712</v>
+        <v>628688</v>
       </c>
       <c r="R82" t="n">
-        <v>6978376</v>
+        <v>6978441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9035,7 +9034,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9044,6 +9043,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9256,50 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129293890</v>
+        <v>129296097</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628691</v>
+        <v>628959</v>
       </c>
       <c r="R85" t="n">
-        <v>6978242</v>
+        <v>6978530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9332,11 +9327,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9363,32 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302291</v>
+        <v>129289873</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>91506</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9398,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628794</v>
+        <v>628447</v>
       </c>
       <c r="R86" t="n">
-        <v>6978373</v>
+        <v>6978522</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9460,45 +9450,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302232</v>
+        <v>129294276</v>
       </c>
       <c r="B87" t="n">
-        <v>91542</v>
+        <v>91743</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628742</v>
+        <v>628790</v>
       </c>
       <c r="R87" t="n">
-        <v>6978216</v>
+        <v>6978034</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9557,7 +9547,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129302267</v>
+        <v>129292746</v>
       </c>
       <c r="B88" t="n">
         <v>91827</v>
@@ -9592,10 +9582,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628603</v>
+        <v>628586</v>
       </c>
       <c r="R88" t="n">
-        <v>6978502</v>
+        <v>6978451</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9654,7 +9644,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302264</v>
+        <v>129290229</v>
       </c>
       <c r="B89" t="n">
         <v>91827</v>
@@ -9689,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628796</v>
+        <v>628436</v>
       </c>
       <c r="R89" t="n">
-        <v>6978261</v>
+        <v>6978498</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9751,32 +9741,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302260</v>
+        <v>129302232</v>
       </c>
       <c r="B90" t="n">
-        <v>91997</v>
+        <v>91542</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9786,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628641</v>
+        <v>628742</v>
       </c>
       <c r="R90" t="n">
-        <v>6978450</v>
+        <v>6978216</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9848,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302258</v>
+        <v>129302267</v>
       </c>
       <c r="B91" t="n">
-        <v>91997</v>
+        <v>91827</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9883,7 +9873,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628851</v>
+        <v>628603</v>
       </c>
       <c r="R91" t="n">
         <v>6978502</v>
@@ -9945,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129289873</v>
+        <v>129302264</v>
       </c>
       <c r="B92" t="n">
-        <v>91506</v>
+        <v>91827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9980,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628447</v>
+        <v>628796</v>
       </c>
       <c r="R92" t="n">
-        <v>6978522</v>
+        <v>6978261</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10042,32 +10032,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129296097</v>
+        <v>129302260</v>
       </c>
       <c r="B93" t="n">
-        <v>80175</v>
+        <v>91997</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10077,10 +10067,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628959</v>
+        <v>628641</v>
       </c>
       <c r="R93" t="n">
-        <v>6978530</v>
+        <v>6978450</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10139,10 +10129,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129294276</v>
+        <v>129302258</v>
       </c>
       <c r="B94" t="n">
-        <v>91743</v>
+        <v>91997</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10150,34 +10140,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628790</v>
+        <v>628851</v>
       </c>
       <c r="R94" t="n">
-        <v>6978034</v>
+        <v>6978502</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10236,10 +10226,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129292746</v>
+        <v>129302291</v>
       </c>
       <c r="B95" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10247,21 +10237,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10271,10 +10261,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628586</v>
+        <v>628794</v>
       </c>
       <c r="R95" t="n">
-        <v>6978451</v>
+        <v>6978373</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10333,10 +10323,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129290229</v>
+        <v>129293890</v>
       </c>
       <c r="B96" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10344,34 +10334,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628436</v>
+        <v>628691</v>
       </c>
       <c r="R96" t="n">
-        <v>6978498</v>
+        <v>6978242</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10404,6 +10399,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10638,45 +10638,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129302295</v>
+        <v>129293044</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628463</v>
+        <v>628662</v>
       </c>
       <c r="R99" t="n">
-        <v>6978635</v>
+        <v>6978408</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10735,49 +10739,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129293044</v>
+        <v>129302295</v>
       </c>
       <c r="B100" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>628662</v>
+        <v>628463</v>
       </c>
       <c r="R100" t="n">
-        <v>6978408</v>
+        <v>6978635</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10836,32 +10836,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129302282</v>
+        <v>129302263</v>
       </c>
       <c r="B101" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628654</v>
+        <v>628810</v>
       </c>
       <c r="R101" t="n">
-        <v>6978418</v>
+        <v>6978299</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,11 +10907,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10938,7 +10933,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302287</v>
+        <v>129302282</v>
       </c>
       <c r="B102" t="n">
         <v>98678</v>
@@ -10973,10 +10968,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628649</v>
+        <v>628654</v>
       </c>
       <c r="R102" t="n">
-        <v>6978449</v>
+        <v>6978418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11013,7 +11008,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11040,32 +11035,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302263</v>
+        <v>129302287</v>
       </c>
       <c r="B103" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11075,10 +11070,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628810</v>
+        <v>628649</v>
       </c>
       <c r="R103" t="n">
-        <v>6978299</v>
+        <v>6978449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11111,6 +11106,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302268</v>
+        <v>129295020</v>
       </c>
       <c r="B104" t="n">
-        <v>97549</v>
+        <v>80181</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11148,34 +11148,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628719</v>
+        <v>628826</v>
       </c>
       <c r="R104" t="n">
-        <v>6978594</v>
+        <v>6978150</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11234,45 +11234,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129295020</v>
+        <v>129295651</v>
       </c>
       <c r="B105" t="n">
-        <v>80181</v>
+        <v>98678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628826</v>
+        <v>628796</v>
       </c>
       <c r="R105" t="n">
-        <v>6978150</v>
+        <v>6978373</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11331,49 +11335,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129295651</v>
+        <v>129302268</v>
       </c>
       <c r="B106" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628796</v>
+        <v>628719</v>
       </c>
       <c r="R106" t="n">
-        <v>6978373</v>
+        <v>6978594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11432,7 +11432,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129293300</v>
+        <v>129302246</v>
       </c>
       <c r="B107" t="n">
         <v>57727</v>
@@ -11461,21 +11461,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628665</v>
+        <v>628750</v>
       </c>
       <c r="R107" t="n">
-        <v>6978376</v>
+        <v>6978346</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11512,7 +11507,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11641,7 +11636,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129302246</v>
+        <v>129293300</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11670,16 +11665,21 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628750</v>
+        <v>628665</v>
       </c>
       <c r="R109" t="n">
-        <v>6978346</v>
+        <v>6978376</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302290</v>
+        <v>129302247</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628712</v>
+        <v>628749</v>
       </c>
       <c r="R112" t="n">
-        <v>6978591</v>
+        <v>6978349</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,6 +12008,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12136,32 +12141,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302247</v>
+        <v>129302256</v>
       </c>
       <c r="B114" t="n">
-        <v>57727</v>
+        <v>98595</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12171,10 +12176,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628749</v>
+        <v>628658</v>
       </c>
       <c r="R114" t="n">
-        <v>6978349</v>
+        <v>6978439</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12211,7 +12216,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12238,32 +12243,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302225</v>
+        <v>129295820</v>
       </c>
       <c r="B115" t="n">
-        <v>91542</v>
+        <v>91997</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12273,10 +12278,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628856</v>
+        <v>628889</v>
       </c>
       <c r="R115" t="n">
-        <v>6978527</v>
+        <v>6978417</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12335,32 +12340,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129302256</v>
+        <v>129293475</v>
       </c>
       <c r="B116" t="n">
-        <v>98595</v>
+        <v>91827</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219790</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12370,10 +12375,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628658</v>
+        <v>628623</v>
       </c>
       <c r="R116" t="n">
-        <v>6978439</v>
+        <v>6978341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12406,11 +12411,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12437,10 +12437,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129293475</v>
+        <v>129302290</v>
       </c>
       <c r="B117" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12448,21 +12448,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12472,10 +12472,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628623</v>
+        <v>628712</v>
       </c>
       <c r="R117" t="n">
-        <v>6978341</v>
+        <v>6978591</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12534,32 +12534,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129295820</v>
+        <v>129302225</v>
       </c>
       <c r="B118" t="n">
-        <v>91997</v>
+        <v>91542</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628889</v>
+        <v>628856</v>
       </c>
       <c r="R118" t="n">
-        <v>6978417</v>
+        <v>6978527</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12922,10 +12922,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129302273</v>
+        <v>129293329</v>
       </c>
       <c r="B122" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12933,34 +12933,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628878</v>
+        <v>628640</v>
       </c>
       <c r="R122" t="n">
-        <v>6978535</v>
+        <v>6978364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13116,10 +13125,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302242</v>
+        <v>129302273</v>
       </c>
       <c r="B124" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13127,21 +13136,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13151,10 +13160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628750</v>
+        <v>628878</v>
       </c>
       <c r="R124" t="n">
-        <v>6978284</v>
+        <v>6978535</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13187,11 +13196,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13218,10 +13222,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129293329</v>
+        <v>129302242</v>
       </c>
       <c r="B125" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13229,16 +13233,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -13246,26 +13250,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628640</v>
+        <v>628750</v>
       </c>
       <c r="R125" t="n">
-        <v>6978364</v>
+        <v>6978284</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13298,6 +13293,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13324,37 +13324,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129291461</v>
+        <v>129289677</v>
       </c>
       <c r="B126" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13363,10 +13364,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628547</v>
+        <v>628484</v>
       </c>
       <c r="R126" t="n">
-        <v>6978457</v>
+        <v>6978568</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13425,10 +13426,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129290692</v>
+        <v>129291548</v>
       </c>
       <c r="B127" t="n">
-        <v>80106</v>
+        <v>80050</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13436,21 +13437,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13460,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628515</v>
+        <v>628549</v>
       </c>
       <c r="R127" t="n">
-        <v>6978451</v>
+        <v>6978433</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13522,45 +13523,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129294090</v>
+        <v>129291461</v>
       </c>
       <c r="B128" t="n">
-        <v>80106</v>
+        <v>98678</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628743</v>
+        <v>628547</v>
       </c>
       <c r="R128" t="n">
-        <v>6978155</v>
+        <v>6978457</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13721,10 +13726,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129291548</v>
+        <v>129302270</v>
       </c>
       <c r="B130" t="n">
-        <v>80050</v>
+        <v>97549</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13732,21 +13737,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13756,10 +13761,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628549</v>
+        <v>628812</v>
       </c>
       <c r="R130" t="n">
-        <v>6978433</v>
+        <v>6978062</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13818,50 +13823,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129289677</v>
+        <v>129290692</v>
       </c>
       <c r="B131" t="n">
-        <v>57724</v>
+        <v>80106</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628484</v>
+        <v>628515</v>
       </c>
       <c r="R131" t="n">
-        <v>6978568</v>
+        <v>6978451</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13920,50 +13920,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129290523</v>
+        <v>129294090</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628509</v>
+        <v>628743</v>
       </c>
       <c r="R132" t="n">
-        <v>6978510</v>
+        <v>6978155</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13996,11 +13991,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14124,45 +14114,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129302270</v>
+        <v>129290523</v>
       </c>
       <c r="B134" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628812</v>
+        <v>628509</v>
       </c>
       <c r="R134" t="n">
-        <v>6978062</v>
+        <v>6978510</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14195,6 +14190,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129294072</v>
+        <v>129295655</v>
       </c>
       <c r="B136" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,34 +14329,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628731</v>
+        <v>628796</v>
       </c>
       <c r="R136" t="n">
-        <v>6978165</v>
+        <v>6978373</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14415,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129295655</v>
+        <v>129294072</v>
       </c>
       <c r="B137" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14426,43 +14435,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628796</v>
+        <v>628731</v>
       </c>
       <c r="R137" t="n">
-        <v>6978373</v>
+        <v>6978165</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14832,32 +14832,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129290695</v>
+        <v>129302266</v>
       </c>
       <c r="B141" t="n">
-        <v>80182</v>
+        <v>91827</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628509</v>
+        <v>628639</v>
       </c>
       <c r="R141" t="n">
-        <v>6978440</v>
+        <v>6978441</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14929,50 +14929,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129293977</v>
+        <v>129302288</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628687</v>
+        <v>628636</v>
       </c>
       <c r="R142" t="n">
-        <v>6978194</v>
+        <v>6978511</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15009,7 +15004,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15036,32 +15031,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129302266</v>
+        <v>129302272</v>
       </c>
       <c r="B143" t="n">
-        <v>91827</v>
+        <v>97549</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15071,10 +15066,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628639</v>
+        <v>628641</v>
       </c>
       <c r="R143" t="n">
-        <v>6978441</v>
+        <v>6978450</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15133,32 +15128,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129302288</v>
+        <v>129290695</v>
       </c>
       <c r="B144" t="n">
-        <v>98678</v>
+        <v>80182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15168,10 +15163,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628636</v>
+        <v>628509</v>
       </c>
       <c r="R144" t="n">
-        <v>6978511</v>
+        <v>6978440</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15204,11 +15199,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15235,45 +15225,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129302272</v>
+        <v>129293977</v>
       </c>
       <c r="B145" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628641</v>
+        <v>628687</v>
       </c>
       <c r="R145" t="n">
-        <v>6978450</v>
+        <v>6978194</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15306,6 +15301,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15332,10 +15332,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129290760</v>
+        <v>129295841</v>
       </c>
       <c r="B146" t="n">
-        <v>98678</v>
+        <v>91743</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15343,38 +15343,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628499</v>
+        <v>628889</v>
       </c>
       <c r="R146" t="n">
-        <v>6978448</v>
+        <v>6978417</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15433,10 +15429,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302292</v>
+        <v>129295133</v>
       </c>
       <c r="B147" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15444,34 +15440,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628819</v>
+        <v>628788</v>
       </c>
       <c r="R147" t="n">
-        <v>6978067</v>
+        <v>6978227</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15504,11 +15500,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15535,45 +15526,49 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129302238</v>
+        <v>129290760</v>
       </c>
       <c r="B148" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628757</v>
+        <v>628499</v>
       </c>
       <c r="R148" t="n">
-        <v>6978192</v>
+        <v>6978448</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15606,11 +15601,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15637,10 +15627,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129302249</v>
+        <v>129295719</v>
       </c>
       <c r="B149" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15648,34 +15638,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628539</v>
+        <v>628846</v>
       </c>
       <c r="R149" t="n">
-        <v>6978526</v>
+        <v>6978364</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15708,11 +15698,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15739,10 +15724,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B150" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15750,34 +15735,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R150" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15836,10 +15821,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302261</v>
+        <v>129302230</v>
       </c>
       <c r="B151" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15847,21 +15832,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15871,10 +15856,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628794</v>
+        <v>628766</v>
       </c>
       <c r="R151" t="n">
-        <v>6978311</v>
+        <v>6978195</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15933,10 +15918,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302226</v>
+        <v>129302261</v>
       </c>
       <c r="B152" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15944,21 +15929,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15968,10 +15953,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628849</v>
+        <v>628794</v>
       </c>
       <c r="R152" t="n">
-        <v>6978507</v>
+        <v>6978311</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16030,32 +16015,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302285</v>
+        <v>129302226</v>
       </c>
       <c r="B153" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16065,10 +16050,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628656</v>
+        <v>628849</v>
       </c>
       <c r="R153" t="n">
-        <v>6978459</v>
+        <v>6978507</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16101,11 +16086,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16132,32 +16112,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129302297</v>
+        <v>129302292</v>
       </c>
       <c r="B154" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16167,10 +16147,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628720</v>
+        <v>628819</v>
       </c>
       <c r="R154" t="n">
-        <v>6978591</v>
+        <v>6978067</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16203,6 +16183,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16229,10 +16214,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129295136</v>
+        <v>129302249</v>
       </c>
       <c r="B155" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16240,34 +16225,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628799</v>
+        <v>628539</v>
       </c>
       <c r="R155" t="n">
-        <v>6978234</v>
+        <v>6978526</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16300,6 +16285,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16326,10 +16316,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129295133</v>
+        <v>129302238</v>
       </c>
       <c r="B156" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16337,34 +16327,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628788</v>
+        <v>628757</v>
       </c>
       <c r="R156" t="n">
-        <v>6978227</v>
+        <v>6978192</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16397,6 +16387,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16423,45 +16418,45 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129295719</v>
+        <v>129302285</v>
       </c>
       <c r="B157" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628846</v>
+        <v>628656</v>
       </c>
       <c r="R157" t="n">
-        <v>6978364</v>
+        <v>6978459</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16494,6 +16489,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16520,32 +16520,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129295841</v>
+        <v>129302297</v>
       </c>
       <c r="B158" t="n">
-        <v>91743</v>
+        <v>100866</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>48</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16555,10 +16555,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628889</v>
+        <v>628720</v>
       </c>
       <c r="R158" t="n">
-        <v>6978417</v>
+        <v>6978591</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16617,32 +16617,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129302234</v>
+        <v>129290278</v>
       </c>
       <c r="B159" t="n">
-        <v>91542</v>
+        <v>91997</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16652,10 +16652,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628641</v>
+        <v>628451</v>
       </c>
       <c r="R159" t="n">
-        <v>6978450</v>
+        <v>6978495</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16714,45 +16714,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129302253</v>
+        <v>129295735</v>
       </c>
       <c r="B160" t="n">
-        <v>57887</v>
+        <v>80181</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628759</v>
+        <v>628841</v>
       </c>
       <c r="R160" t="n">
-        <v>6978235</v>
+        <v>6978384</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16811,32 +16811,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129302279</v>
+        <v>129289808</v>
       </c>
       <c r="B161" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628884</v>
+        <v>628421</v>
       </c>
       <c r="R161" t="n">
-        <v>6978488</v>
+        <v>6978541</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16882,11 +16882,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16913,10 +16908,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129289808</v>
+        <v>129302234</v>
       </c>
       <c r="B162" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16924,21 +16919,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16948,10 +16943,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628421</v>
+        <v>628641</v>
       </c>
       <c r="R162" t="n">
-        <v>6978541</v>
+        <v>6978450</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17010,45 +17005,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129295735</v>
+        <v>129302253</v>
       </c>
       <c r="B163" t="n">
-        <v>80181</v>
+        <v>57887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628841</v>
+        <v>628759</v>
       </c>
       <c r="R163" t="n">
-        <v>6978384</v>
+        <v>6978235</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17107,10 +17102,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129290278</v>
+        <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17118,21 +17113,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17142,10 +17137,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628451</v>
+        <v>628884</v>
       </c>
       <c r="R164" t="n">
-        <v>6978495</v>
+        <v>6978488</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17178,6 +17173,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -4070,7 +4070,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129290118</v>
+        <v>129302235</v>
       </c>
       <c r="B33" t="n">
         <v>91542</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628453</v>
+        <v>628629</v>
       </c>
       <c r="R33" t="n">
-        <v>6978518</v>
+        <v>6978532</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,45 +4167,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129294218</v>
+        <v>129302293</v>
       </c>
       <c r="B34" t="n">
-        <v>96012</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1079</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628798</v>
+        <v>628737</v>
       </c>
       <c r="R34" t="n">
-        <v>6978072</v>
+        <v>6978300</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,11 +4238,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4269,45 +4264,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129296183</v>
+        <v>129302277</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>629055</v>
+        <v>628899</v>
       </c>
       <c r="R35" t="n">
-        <v>6978511</v>
+        <v>6978480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4340,6 +4335,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129293171</v>
+        <v>129290118</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,43 +4377,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628702</v>
+        <v>628453</v>
       </c>
       <c r="R36" t="n">
-        <v>6978339</v>
+        <v>6978518</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129295187</v>
+        <v>129294218</v>
       </c>
       <c r="B37" t="n">
-        <v>91827</v>
+        <v>96012</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4507,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628834</v>
+        <v>628798</v>
       </c>
       <c r="R37" t="n">
-        <v>6978251</v>
+        <v>6978072</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4543,6 +4534,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,10 +4565,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302235</v>
+        <v>129296183</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,34 +4576,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628629</v>
+        <v>629055</v>
       </c>
       <c r="R38" t="n">
-        <v>6978532</v>
+        <v>6978511</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302293</v>
+        <v>129293171</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,34 +4673,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628737</v>
+        <v>628702</v>
       </c>
       <c r="R39" t="n">
-        <v>6978300</v>
+        <v>6978339</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,45 +4768,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129302277</v>
+        <v>129295187</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628899</v>
+        <v>628834</v>
       </c>
       <c r="R40" t="n">
-        <v>6978480</v>
+        <v>6978251</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4834,11 +4839,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129296072</v>
+        <v>129294028</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4876,43 +4876,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628971</v>
+        <v>628728</v>
       </c>
       <c r="R41" t="n">
-        <v>6978518</v>
+        <v>6978173</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4971,32 +4962,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B42" t="n">
-        <v>91827</v>
+        <v>91997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5006,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R42" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5068,37 +5059,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290183</v>
+        <v>129296072</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5107,10 +5103,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628436</v>
+        <v>628971</v>
       </c>
       <c r="R43" t="n">
-        <v>6978498</v>
+        <v>6978518</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5169,10 +5165,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129302248</v>
+        <v>129291502</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5176,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5200,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628679</v>
+        <v>628564</v>
       </c>
       <c r="R44" t="n">
-        <v>6978469</v>
+        <v>6978436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5240,11 +5236,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,45 +5262,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129294028</v>
+        <v>129290183</v>
       </c>
       <c r="B45" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628728</v>
+        <v>628436</v>
       </c>
       <c r="R45" t="n">
-        <v>6978173</v>
+        <v>6978498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5368,32 +5363,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129293533</v>
+        <v>129302248</v>
       </c>
       <c r="B46" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5403,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628623</v>
+        <v>628679</v>
       </c>
       <c r="R46" t="n">
-        <v>6978341</v>
+        <v>6978469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5439,6 +5434,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6459,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129302274</v>
+        <v>129295935</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>91556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6470,21 +6470,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628659</v>
+        <v>628907</v>
       </c>
       <c r="R57" t="n">
-        <v>6978419</v>
+        <v>6978423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129302252</v>
+        <v>129294015</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6567,34 +6567,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628837</v>
+        <v>628728</v>
       </c>
       <c r="R58" t="n">
-        <v>6978500</v>
+        <v>6978173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6627,11 +6627,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6658,10 +6653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302271</v>
+        <v>129293780</v>
       </c>
       <c r="B59" t="n">
-        <v>97549</v>
+        <v>57719</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6669,34 +6664,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>100110</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628763</v>
+        <v>628680</v>
       </c>
       <c r="R59" t="n">
-        <v>6978273</v>
+        <v>6978235</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6755,10 +6759,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129295935</v>
+        <v>129302229</v>
       </c>
       <c r="B60" t="n">
-        <v>91556</v>
+        <v>91542</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6766,21 +6770,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6794,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628907</v>
+        <v>628761</v>
       </c>
       <c r="R60" t="n">
-        <v>6978423</v>
+        <v>6978157</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129294015</v>
+        <v>129302241</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6863,34 +6867,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628728</v>
+        <v>628741</v>
       </c>
       <c r="R61" t="n">
-        <v>6978173</v>
+        <v>6978271</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,6 +6927,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6949,54 +6958,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129293780</v>
+        <v>129302274</v>
       </c>
       <c r="B62" t="n">
-        <v>57719</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628680</v>
+        <v>628659</v>
       </c>
       <c r="R62" t="n">
-        <v>6978235</v>
+        <v>6978419</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302229</v>
+        <v>129302252</v>
       </c>
       <c r="B63" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628761</v>
+        <v>628837</v>
       </c>
       <c r="R63" t="n">
-        <v>6978157</v>
+        <v>6978500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7126,6 +7126,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7152,32 +7157,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302241</v>
+        <v>129302271</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7187,10 +7192,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628741</v>
+        <v>628763</v>
       </c>
       <c r="R64" t="n">
-        <v>6978271</v>
+        <v>6978273</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7223,11 +7228,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7642,37 +7642,42 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129291473</v>
+        <v>129297292</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7681,10 +7686,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628549</v>
+        <v>628429</v>
       </c>
       <c r="R69" t="n">
-        <v>6978449</v>
+        <v>6978625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7743,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129290108</v>
+        <v>129302259</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7754,38 +7759,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628447</v>
+        <v>628771</v>
       </c>
       <c r="R70" t="n">
-        <v>6978522</v>
+        <v>6978154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8150,10 +8151,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302259</v>
+        <v>129302280</v>
       </c>
       <c r="B74" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8162,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8186,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628771</v>
+        <v>628692</v>
       </c>
       <c r="R74" t="n">
-        <v>6978154</v>
+        <v>6978432</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8221,6 +8222,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8247,42 +8253,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129297292</v>
+        <v>129291473</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8291,10 +8292,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628429</v>
+        <v>628549</v>
       </c>
       <c r="R75" t="n">
-        <v>6978625</v>
+        <v>6978449</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8353,7 +8354,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129302280</v>
+        <v>129290108</v>
       </c>
       <c r="B76" t="n">
         <v>98678</v>
@@ -8381,17 +8382,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628692</v>
+        <v>628447</v>
       </c>
       <c r="R76" t="n">
-        <v>6978432</v>
+        <v>6978522</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,11 +8429,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8455,10 +8455,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129295124</v>
+        <v>129289501</v>
       </c>
       <c r="B77" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,34 +8466,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628788</v>
+        <v>628451</v>
       </c>
       <c r="R77" t="n">
-        <v>6978227</v>
+        <v>6978596</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8526,6 +8531,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,10 +8562,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129289501</v>
+        <v>129295124</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8563,39 +8573,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628451</v>
+        <v>628788</v>
       </c>
       <c r="R78" t="n">
-        <v>6978596</v>
+        <v>6978227</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8756,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302227</v>
+        <v>129302255</v>
       </c>
       <c r="B80" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8767,21 +8767,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628851</v>
+        <v>628712</v>
       </c>
       <c r="R80" t="n">
-        <v>6978504</v>
+        <v>6978376</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8827,6 +8827,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8853,45 +8858,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302255</v>
+        <v>129302281</v>
       </c>
       <c r="B81" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628712</v>
+        <v>628688</v>
       </c>
       <c r="R81" t="n">
-        <v>6978376</v>
+        <v>6978441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8928,7 +8937,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8937,6 +8946,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8955,49 +8965,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302281</v>
+        <v>129302227</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628688</v>
+        <v>628851</v>
       </c>
       <c r="R82" t="n">
-        <v>6978441</v>
+        <v>6978504</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9032,18 +9038,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9256,45 +9256,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129296097</v>
+        <v>129293890</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628959</v>
+        <v>628691</v>
       </c>
       <c r="R85" t="n">
-        <v>6978530</v>
+        <v>6978242</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9327,6 +9332,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9353,45 +9363,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129289873</v>
+        <v>129293914</v>
       </c>
       <c r="B86" t="n">
-        <v>91506</v>
+        <v>57887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628447</v>
+        <v>628690</v>
       </c>
       <c r="R86" t="n">
-        <v>6978522</v>
+        <v>6978221</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,45 +9465,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129294276</v>
+        <v>129302291</v>
       </c>
       <c r="B87" t="n">
-        <v>91743</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628790</v>
+        <v>628794</v>
       </c>
       <c r="R87" t="n">
-        <v>6978034</v>
+        <v>6978373</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,32 +9562,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129292746</v>
+        <v>129296097</v>
       </c>
       <c r="B88" t="n">
-        <v>91827</v>
+        <v>80175</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9582,10 +9597,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628586</v>
+        <v>628959</v>
       </c>
       <c r="R88" t="n">
-        <v>6978451</v>
+        <v>6978530</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,32 +9659,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129290229</v>
+        <v>129289873</v>
       </c>
       <c r="B89" t="n">
-        <v>91827</v>
+        <v>91506</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9694,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628436</v>
+        <v>628447</v>
       </c>
       <c r="R89" t="n">
-        <v>6978498</v>
+        <v>6978522</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,45 +9756,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302232</v>
+        <v>129294276</v>
       </c>
       <c r="B90" t="n">
-        <v>91542</v>
+        <v>91743</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628742</v>
+        <v>628790</v>
       </c>
       <c r="R90" t="n">
-        <v>6978216</v>
+        <v>6978034</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,7 +9853,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302267</v>
+        <v>129292746</v>
       </c>
       <c r="B91" t="n">
         <v>91827</v>
@@ -9873,10 +9888,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628603</v>
+        <v>628586</v>
       </c>
       <c r="R91" t="n">
-        <v>6978502</v>
+        <v>6978451</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,7 +9950,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129302264</v>
+        <v>129290229</v>
       </c>
       <c r="B92" t="n">
         <v>91827</v>
@@ -9970,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628796</v>
+        <v>628436</v>
       </c>
       <c r="R92" t="n">
-        <v>6978261</v>
+        <v>6978498</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10032,32 +10047,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129302260</v>
+        <v>129302232</v>
       </c>
       <c r="B93" t="n">
-        <v>91997</v>
+        <v>91542</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10067,10 +10082,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628641</v>
+        <v>628742</v>
       </c>
       <c r="R93" t="n">
-        <v>6978450</v>
+        <v>6978216</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10129,32 +10144,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129302258</v>
+        <v>129302267</v>
       </c>
       <c r="B94" t="n">
-        <v>91997</v>
+        <v>91827</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10164,7 +10179,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628851</v>
+        <v>628603</v>
       </c>
       <c r="R94" t="n">
         <v>6978502</v>
@@ -10226,10 +10241,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302291</v>
+        <v>129302264</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10237,21 +10252,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10261,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628794</v>
+        <v>628796</v>
       </c>
       <c r="R95" t="n">
-        <v>6978373</v>
+        <v>6978261</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10323,50 +10338,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129293890</v>
+        <v>129302260</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>91997</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628691</v>
+        <v>628641</v>
       </c>
       <c r="R96" t="n">
-        <v>6978242</v>
+        <v>6978450</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10399,11 +10409,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10430,50 +10435,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129293914</v>
+        <v>129302258</v>
       </c>
       <c r="B97" t="n">
-        <v>57887</v>
+        <v>91997</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628690</v>
+        <v>628851</v>
       </c>
       <c r="R97" t="n">
-        <v>6978221</v>
+        <v>6978502</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12922,54 +12922,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129293329</v>
+        <v>129302257</v>
       </c>
       <c r="B122" t="n">
-        <v>57724</v>
+        <v>91997</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628640</v>
+        <v>628794</v>
       </c>
       <c r="R122" t="n">
-        <v>6978364</v>
+        <v>6978311</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13028,32 +13019,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129302257</v>
+        <v>129302273</v>
       </c>
       <c r="B123" t="n">
-        <v>91997</v>
+        <v>80146</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13063,10 +13054,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628794</v>
+        <v>628878</v>
       </c>
       <c r="R123" t="n">
-        <v>6978311</v>
+        <v>6978535</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13125,10 +13116,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302273</v>
+        <v>129293329</v>
       </c>
       <c r="B124" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13136,34 +13127,43 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628878</v>
+        <v>628640</v>
       </c>
       <c r="R124" t="n">
-        <v>6978535</v>
+        <v>6978364</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13324,50 +13324,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129289677</v>
+        <v>129291548</v>
       </c>
       <c r="B126" t="n">
-        <v>57724</v>
+        <v>80050</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628484</v>
+        <v>628549</v>
       </c>
       <c r="R126" t="n">
-        <v>6978568</v>
+        <v>6978433</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13426,45 +13421,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129291548</v>
+        <v>129290523</v>
       </c>
       <c r="B127" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628549</v>
+        <v>628509</v>
       </c>
       <c r="R127" t="n">
-        <v>6978433</v>
+        <v>6978510</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13497,6 +13497,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13523,37 +13528,38 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129291461</v>
+        <v>129289677</v>
       </c>
       <c r="B128" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -13562,10 +13568,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628547</v>
+        <v>628484</v>
       </c>
       <c r="R128" t="n">
-        <v>6978457</v>
+        <v>6978568</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13624,32 +13630,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129302239</v>
+        <v>129290692</v>
       </c>
       <c r="B129" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13659,10 +13665,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628747</v>
+        <v>628515</v>
       </c>
       <c r="R129" t="n">
-        <v>6978218</v>
+        <v>6978451</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13695,11 +13701,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13726,10 +13727,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129302270</v>
+        <v>129294090</v>
       </c>
       <c r="B130" t="n">
-        <v>97549</v>
+        <v>80106</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13737,34 +13738,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628812</v>
+        <v>628743</v>
       </c>
       <c r="R130" t="n">
-        <v>6978062</v>
+        <v>6978155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13823,45 +13824,49 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129290692</v>
+        <v>129291461</v>
       </c>
       <c r="B131" t="n">
-        <v>80106</v>
+        <v>98678</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628515</v>
+        <v>628547</v>
       </c>
       <c r="R131" t="n">
-        <v>6978451</v>
+        <v>6978457</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13920,45 +13925,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129294090</v>
+        <v>129302296</v>
       </c>
       <c r="B132" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628743</v>
+        <v>628449</v>
       </c>
       <c r="R132" t="n">
-        <v>6978155</v>
+        <v>6978612</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14017,10 +14022,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129302296</v>
+        <v>129302239</v>
       </c>
       <c r="B133" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14028,21 +14033,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14052,10 +14057,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628449</v>
+        <v>628747</v>
       </c>
       <c r="R133" t="n">
-        <v>6978612</v>
+        <v>6978218</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14088,6 +14093,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14114,50 +14124,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129290523</v>
+        <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>57727</v>
+        <v>97549</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628509</v>
+        <v>628812</v>
       </c>
       <c r="R134" t="n">
-        <v>6978510</v>
+        <v>6978062</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14190,11 +14195,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14221,10 +14221,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129302228</v>
+        <v>129294072</v>
       </c>
       <c r="B135" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14232,34 +14232,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628870</v>
+        <v>628731</v>
       </c>
       <c r="R135" t="n">
-        <v>6978469</v>
+        <v>6978165</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129295655</v>
+        <v>129302228</v>
       </c>
       <c r="B136" t="n">
-        <v>57724</v>
+        <v>91542</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,43 +14329,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628796</v>
+        <v>628870</v>
       </c>
       <c r="R136" t="n">
-        <v>6978373</v>
+        <v>6978469</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,10 +14415,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294072</v>
+        <v>129295655</v>
       </c>
       <c r="B137" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14435,34 +14426,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628731</v>
+        <v>628796</v>
       </c>
       <c r="R137" t="n">
-        <v>6978165</v>
+        <v>6978373</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,10 +2275,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295766</v>
+        <v>129292781</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>92257</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,34 +2286,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628846</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6978364</v>
+        <v>6978436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129292781</v>
+        <v>129295830</v>
       </c>
       <c r="B16" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628590</v>
+        <v>628896</v>
       </c>
       <c r="R16" t="n">
-        <v>6978436</v>
+        <v>6978430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295830</v>
+        <v>129295766</v>
       </c>
       <c r="B17" t="n">
-        <v>92242</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,34 +2480,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628896</v>
+        <v>628846</v>
       </c>
       <c r="R17" t="n">
-        <v>6978430</v>
+        <v>6978364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,45 +2979,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294036</v>
+        <v>129292558</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628728</v>
+        <v>628589</v>
       </c>
       <c r="R22" t="n">
-        <v>6978173</v>
+        <v>6978414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129290628</v>
+        <v>129294036</v>
       </c>
       <c r="B23" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3107,14 +3111,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628499</v>
+        <v>628728</v>
       </c>
       <c r="R23" t="n">
-        <v>6978448</v>
+        <v>6978173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,49 +3177,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129292558</v>
+        <v>129290628</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628589</v>
+        <v>628499</v>
       </c>
       <c r="R24" t="n">
-        <v>6978414</v>
+        <v>6978448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,32 +3274,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302262</v>
+        <v>129293584</v>
       </c>
       <c r="B25" t="n">
-        <v>91827</v>
+        <v>91992</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628800</v>
+        <v>628624</v>
       </c>
       <c r="R25" t="n">
-        <v>6978306</v>
+        <v>6978328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,32 +3371,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302265</v>
+        <v>129302278</v>
       </c>
       <c r="B26" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628772</v>
+        <v>628894</v>
       </c>
       <c r="R26" t="n">
-        <v>6978157</v>
+        <v>6978483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3442,6 +3442,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,7 +3476,7 @@
         <v>129302284</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3570,32 +3575,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302278</v>
+        <v>129302269</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>97575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3605,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628894</v>
+        <v>628792</v>
       </c>
       <c r="R28" t="n">
-        <v>6978483</v>
+        <v>6978309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,11 +3646,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302243</v>
+        <v>129302262</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,21 +3683,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628743</v>
+        <v>628800</v>
       </c>
       <c r="R29" t="n">
-        <v>6978315</v>
+        <v>6978306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3743,11 +3743,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3774,10 +3769,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302240</v>
+        <v>129302265</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,21 +3780,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628764</v>
+        <v>628772</v>
       </c>
       <c r="R30" t="n">
-        <v>6978279</v>
+        <v>6978157</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3845,11 +3840,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3876,32 +3866,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302269</v>
+        <v>129302243</v>
       </c>
       <c r="B31" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3911,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628792</v>
+        <v>628743</v>
       </c>
       <c r="R31" t="n">
-        <v>6978309</v>
+        <v>6978315</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,6 +3937,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,32 +3968,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129293584</v>
+        <v>129302240</v>
       </c>
       <c r="B32" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4008,10 +4003,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628624</v>
+        <v>628764</v>
       </c>
       <c r="R32" t="n">
-        <v>6978328</v>
+        <v>6978279</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129302235</v>
+        <v>129295187</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628629</v>
+        <v>628834</v>
       </c>
       <c r="R33" t="n">
-        <v>6978532</v>
+        <v>6978251</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129302293</v>
+        <v>129290118</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4178,21 +4178,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628737</v>
+        <v>628453</v>
       </c>
       <c r="R34" t="n">
-        <v>6978300</v>
+        <v>6978518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129302277</v>
+        <v>129294218</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>96038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,34 +4275,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628899</v>
+        <v>628798</v>
       </c>
       <c r="R35" t="n">
-        <v>6978480</v>
+        <v>6978072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>150, finns troligtvis mer i mossan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129290118</v>
+        <v>129296183</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,34 +4377,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628453</v>
+        <v>629055</v>
       </c>
       <c r="R36" t="n">
-        <v>6978518</v>
+        <v>6978511</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,45 +4463,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294218</v>
+        <v>129293171</v>
       </c>
       <c r="B37" t="n">
-        <v>96012</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628798</v>
+        <v>628702</v>
       </c>
       <c r="R37" t="n">
-        <v>6978072</v>
+        <v>6978339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4534,11 +4543,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4565,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129296183</v>
+        <v>129302235</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4576,34 +4580,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>629055</v>
+        <v>628629</v>
       </c>
       <c r="R38" t="n">
-        <v>6978511</v>
+        <v>6978532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293171</v>
+        <v>129302293</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4673,43 +4677,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628702</v>
+        <v>628737</v>
       </c>
       <c r="R39" t="n">
-        <v>6978339</v>
+        <v>6978300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,45 +4763,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129295187</v>
+        <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628834</v>
+        <v>628899</v>
       </c>
       <c r="R40" t="n">
-        <v>6978251</v>
+        <v>6978480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,6 +4834,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,45 +4865,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129294028</v>
+        <v>129290183</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628728</v>
+        <v>628436</v>
       </c>
       <c r="R41" t="n">
-        <v>6978173</v>
+        <v>6978498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4962,45 +4966,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293533</v>
+        <v>129294028</v>
       </c>
       <c r="B42" t="n">
-        <v>91997</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628623</v>
+        <v>628728</v>
       </c>
       <c r="R42" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,10 +5063,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296072</v>
+        <v>129291502</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,43 +5074,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628971</v>
+        <v>628564</v>
       </c>
       <c r="R43" t="n">
-        <v>6978518</v>
+        <v>6978436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5165,32 +5160,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B44" t="n">
-        <v>91827</v>
+        <v>91992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5200,10 +5195,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R44" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,37 +5257,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129290183</v>
+        <v>129296072</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628436</v>
+        <v>628971</v>
       </c>
       <c r="R45" t="n">
-        <v>6978498</v>
+        <v>6978518</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129296084</v>
+        <v>129290616</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628959</v>
+        <v>628499</v>
       </c>
       <c r="R47" t="n">
-        <v>6978530</v>
+        <v>6978448</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290616</v>
+        <v>129290361</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628499</v>
+        <v>628465</v>
       </c>
       <c r="R48" t="n">
-        <v>6978448</v>
+        <v>6978491</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290361</v>
+        <v>129296084</v>
       </c>
       <c r="B49" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628465</v>
+        <v>628959</v>
       </c>
       <c r="R49" t="n">
-        <v>6978491</v>
+        <v>6978530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5866,7 +5866,7 @@
         <v>129290084</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>129302231</v>
       </c>
       <c r="B52" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>129302233</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>129302275</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129302276</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>129295935</v>
       </c>
       <c r="B57" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>129302229</v>
       </c>
       <c r="B60" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302241</v>
+        <v>129302252</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628741</v>
+        <v>628837</v>
       </c>
       <c r="R61" t="n">
-        <v>6978271</v>
+        <v>6978500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,32 +6958,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302274</v>
+        <v>129302271</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>97575</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628659</v>
+        <v>628763</v>
       </c>
       <c r="R62" t="n">
-        <v>6978419</v>
+        <v>6978273</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302252</v>
+        <v>129302274</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628837</v>
+        <v>628659</v>
       </c>
       <c r="R63" t="n">
-        <v>6978500</v>
+        <v>6978419</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7126,11 +7126,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7157,32 +7152,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302271</v>
+        <v>129302241</v>
       </c>
       <c r="B64" t="n">
-        <v>97549</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7192,10 +7187,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628763</v>
+        <v>628741</v>
       </c>
       <c r="R64" t="n">
-        <v>6978273</v>
+        <v>6978271</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,6 +7223,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7254,10 +7254,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129295162</v>
+        <v>129291473</v>
       </c>
       <c r="B65" t="n">
-        <v>91997</v>
+        <v>98704</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,34 +7265,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628834</v>
+        <v>628549</v>
       </c>
       <c r="R65" t="n">
-        <v>6978251</v>
+        <v>6978449</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7351,10 +7355,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129292729</v>
+        <v>129290108</v>
       </c>
       <c r="B66" t="n">
-        <v>91997</v>
+        <v>98704</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7362,34 +7366,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628599</v>
+        <v>628447</v>
       </c>
       <c r="R66" t="n">
-        <v>6978448</v>
+        <v>6978522</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7451,7 +7459,7 @@
         <v>129291635</v>
       </c>
       <c r="B67" t="n">
-        <v>96012</v>
+        <v>96038</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7548,7 +7556,7 @@
         <v>129294000</v>
       </c>
       <c r="B68" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7642,54 +7650,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129297292</v>
+        <v>129295162</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628429</v>
+        <v>628834</v>
       </c>
       <c r="R69" t="n">
-        <v>6978625</v>
+        <v>6978251</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,10 +7747,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129302259</v>
+        <v>129292729</v>
       </c>
       <c r="B70" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7768,12 +7767,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7783,10 +7782,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628771</v>
+        <v>628599</v>
       </c>
       <c r="R70" t="n">
-        <v>6978154</v>
+        <v>6978448</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7845,7 +7844,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129302250</v>
+        <v>129297292</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -7873,17 +7872,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628495</v>
+        <v>628429</v>
       </c>
       <c r="R71" t="n">
-        <v>6978647</v>
+        <v>6978625</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,11 +7924,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7947,32 +7950,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302244</v>
+        <v>129302280</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7982,10 +7985,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628756</v>
+        <v>628692</v>
       </c>
       <c r="R72" t="n">
-        <v>6978337</v>
+        <v>6978432</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,7 +8025,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8049,32 +8052,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302254</v>
+        <v>129302259</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>91992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8084,10 +8087,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628894</v>
+        <v>628771</v>
       </c>
       <c r="R73" t="n">
-        <v>6978096</v>
+        <v>6978154</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8120,11 +8123,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8151,32 +8149,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302280</v>
+        <v>129302250</v>
       </c>
       <c r="B74" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8186,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628692</v>
+        <v>628495</v>
       </c>
       <c r="R74" t="n">
-        <v>6978432</v>
+        <v>6978647</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8226,7 +8224,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>200 ( ca) några blommande</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8253,49 +8251,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129291473</v>
+        <v>129302244</v>
       </c>
       <c r="B75" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628549</v>
+        <v>628756</v>
       </c>
       <c r="R75" t="n">
-        <v>6978449</v>
+        <v>6978337</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8328,6 +8322,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8354,49 +8353,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129290108</v>
+        <v>129302254</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628447</v>
+        <v>628894</v>
       </c>
       <c r="R76" t="n">
-        <v>6978522</v>
+        <v>6978096</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,6 +8424,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8455,10 +8455,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129289501</v>
+        <v>129302227</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,39 +8466,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628451</v>
+        <v>628851</v>
       </c>
       <c r="R77" t="n">
-        <v>6978596</v>
+        <v>6978504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8531,11 +8526,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8562,45 +8552,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129295124</v>
+        <v>129290447</v>
       </c>
       <c r="B78" t="n">
-        <v>91827</v>
+        <v>97575</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628788</v>
+        <v>628494</v>
       </c>
       <c r="R78" t="n">
-        <v>6978227</v>
+        <v>6978496</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8659,45 +8649,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129290447</v>
+        <v>129295124</v>
       </c>
       <c r="B79" t="n">
-        <v>97549</v>
+        <v>91837</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628494</v>
+        <v>628788</v>
       </c>
       <c r="R79" t="n">
-        <v>6978496</v>
+        <v>6978227</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8756,10 +8746,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302255</v>
+        <v>129289501</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8767,16 +8757,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8785,16 +8775,21 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628712</v>
+        <v>628451</v>
       </c>
       <c r="R80" t="n">
-        <v>6978376</v>
+        <v>6978596</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8831,7 +8826,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8858,49 +8853,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B81" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R81" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8937,7 +8928,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8946,7 +8937,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8965,45 +8955,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302227</v>
+        <v>129302281</v>
       </c>
       <c r="B82" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628851</v>
+        <v>628688</v>
       </c>
       <c r="R82" t="n">
-        <v>6978504</v>
+        <v>6978441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9038,12 +9032,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9256,50 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129293890</v>
+        <v>129302260</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>91992</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628691</v>
+        <v>628641</v>
       </c>
       <c r="R85" t="n">
-        <v>6978242</v>
+        <v>6978450</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9332,11 +9327,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9363,50 +9353,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129293914</v>
+        <v>129302258</v>
       </c>
       <c r="B86" t="n">
-        <v>57887</v>
+        <v>91992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628690</v>
+        <v>628851</v>
       </c>
       <c r="R86" t="n">
-        <v>6978221</v>
+        <v>6978502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9562,45 +9547,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129296097</v>
+        <v>129294276</v>
       </c>
       <c r="B88" t="n">
-        <v>80175</v>
+        <v>91752</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>48</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628959</v>
+        <v>628790</v>
       </c>
       <c r="R88" t="n">
-        <v>6978530</v>
+        <v>6978034</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9659,32 +9644,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129289873</v>
+        <v>129292746</v>
       </c>
       <c r="B89" t="n">
-        <v>91506</v>
+        <v>91837</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9694,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628447</v>
+        <v>628586</v>
       </c>
       <c r="R89" t="n">
-        <v>6978522</v>
+        <v>6978451</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9756,45 +9741,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129294276</v>
+        <v>129290229</v>
       </c>
       <c r="B90" t="n">
-        <v>91743</v>
+        <v>91837</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628790</v>
+        <v>628436</v>
       </c>
       <c r="R90" t="n">
-        <v>6978034</v>
+        <v>6978498</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129292746</v>
+        <v>129289873</v>
       </c>
       <c r="B91" t="n">
-        <v>91827</v>
+        <v>91504</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9888,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628586</v>
+        <v>628447</v>
       </c>
       <c r="R91" t="n">
-        <v>6978451</v>
+        <v>6978522</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9950,32 +9935,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129290229</v>
+        <v>129296097</v>
       </c>
       <c r="B92" t="n">
-        <v>91827</v>
+        <v>80175</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9970,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628436</v>
+        <v>628959</v>
       </c>
       <c r="R92" t="n">
-        <v>6978498</v>
+        <v>6978530</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,10 +10032,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129302232</v>
+        <v>129293890</v>
       </c>
       <c r="B93" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10058,34 +10043,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628742</v>
+        <v>628691</v>
       </c>
       <c r="R93" t="n">
-        <v>6978216</v>
+        <v>6978242</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10118,6 +10108,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10144,10 +10139,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129302267</v>
+        <v>129293914</v>
       </c>
       <c r="B94" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10155,34 +10150,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628603</v>
+        <v>628690</v>
       </c>
       <c r="R94" t="n">
-        <v>6978502</v>
+        <v>6978221</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,10 +10241,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302264</v>
+        <v>129302232</v>
       </c>
       <c r="B95" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10252,21 +10252,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628796</v>
+        <v>628742</v>
       </c>
       <c r="R95" t="n">
-        <v>6978261</v>
+        <v>6978216</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302260</v>
+        <v>129302267</v>
       </c>
       <c r="B96" t="n">
-        <v>91997</v>
+        <v>91837</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628641</v>
+        <v>628603</v>
       </c>
       <c r="R96" t="n">
-        <v>6978450</v>
+        <v>6978502</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,32 +10435,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129302258</v>
+        <v>129302264</v>
       </c>
       <c r="B97" t="n">
-        <v>91997</v>
+        <v>91837</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628851</v>
+        <v>628796</v>
       </c>
       <c r="R97" t="n">
-        <v>6978502</v>
+        <v>6978261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10641,7 +10641,7 @@
         <v>129293044</v>
       </c>
       <c r="B99" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10836,45 +10836,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129302263</v>
+        <v>129295020</v>
       </c>
       <c r="B101" t="n">
-        <v>91827</v>
+        <v>80181</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628810</v>
+        <v>628826</v>
       </c>
       <c r="R101" t="n">
-        <v>6978299</v>
+        <v>6978150</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10933,10 +10933,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302282</v>
+        <v>129295651</v>
       </c>
       <c r="B102" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10961,17 +10961,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628654</v>
+        <v>628796</v>
       </c>
       <c r="R102" t="n">
-        <v>6978418</v>
+        <v>6978373</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11004,11 +11008,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11035,32 +11034,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302287</v>
+        <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11070,10 +11069,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628649</v>
+        <v>628810</v>
       </c>
       <c r="R103" t="n">
-        <v>6978449</v>
+        <v>6978299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11106,11 +11105,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11137,10 +11131,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129295020</v>
+        <v>129302268</v>
       </c>
       <c r="B104" t="n">
-        <v>80181</v>
+        <v>97575</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11148,34 +11142,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628826</v>
+        <v>628719</v>
       </c>
       <c r="R104" t="n">
-        <v>6978150</v>
+        <v>6978594</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11234,10 +11228,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129295651</v>
+        <v>129302282</v>
       </c>
       <c r="B105" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11262,21 +11256,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628796</v>
+        <v>628654</v>
       </c>
       <c r="R105" t="n">
-        <v>6978373</v>
+        <v>6978418</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11309,6 +11299,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11335,32 +11330,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302268</v>
+        <v>129302287</v>
       </c>
       <c r="B106" t="n">
-        <v>97549</v>
+        <v>98704</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11370,10 +11365,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628719</v>
+        <v>628649</v>
       </c>
       <c r="R106" t="n">
-        <v>6978594</v>
+        <v>6978449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,6 +11401,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11746,7 +11746,7 @@
         <v>129293395</v>
       </c>
       <c r="B110" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>129289885</v>
       </c>
       <c r="B111" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302247</v>
+        <v>129293475</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628749</v>
+        <v>628623</v>
       </c>
       <c r="R112" t="n">
-        <v>6978349</v>
+        <v>6978341</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,11 +12008,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12039,32 +12034,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302289</v>
+        <v>129295820</v>
       </c>
       <c r="B113" t="n">
-        <v>57719</v>
+        <v>91992</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100110</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12074,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628493</v>
+        <v>628889</v>
       </c>
       <c r="R113" t="n">
-        <v>6978648</v>
+        <v>6978417</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,11 +12105,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12141,32 +12131,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302256</v>
+        <v>129302225</v>
       </c>
       <c r="B114" t="n">
-        <v>98595</v>
+        <v>91540</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12176,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628658</v>
+        <v>628856</v>
       </c>
       <c r="R114" t="n">
-        <v>6978439</v>
+        <v>6978527</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12212,11 +12202,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12243,32 +12228,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129295820</v>
+        <v>129302290</v>
       </c>
       <c r="B115" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12278,10 +12263,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628889</v>
+        <v>628712</v>
       </c>
       <c r="R115" t="n">
-        <v>6978417</v>
+        <v>6978591</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12340,10 +12325,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129293475</v>
+        <v>129302247</v>
       </c>
       <c r="B116" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12351,21 +12336,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12375,10 +12360,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628623</v>
+        <v>628749</v>
       </c>
       <c r="R116" t="n">
-        <v>6978341</v>
+        <v>6978349</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12411,6 +12396,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12437,32 +12427,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302290</v>
+        <v>129302289</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>57719</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12472,10 +12462,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628712</v>
+        <v>628493</v>
       </c>
       <c r="R117" t="n">
-        <v>6978591</v>
+        <v>6978648</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12508,6 +12498,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12534,32 +12529,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129302225</v>
+        <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>91542</v>
+        <v>98621</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12569,10 +12564,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628856</v>
+        <v>628658</v>
       </c>
       <c r="R118" t="n">
-        <v>6978527</v>
+        <v>6978439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12605,6 +12600,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12631,10 +12631,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129294695</v>
+        <v>129302257</v>
       </c>
       <c r="B119" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12651,25 +12651,25 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628831</v>
+        <v>628794</v>
       </c>
       <c r="R119" t="n">
-        <v>6978180</v>
+        <v>6978311</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,32 +12728,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129297070</v>
+        <v>129302242</v>
       </c>
       <c r="B120" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628764</v>
+        <v>628750</v>
       </c>
       <c r="R120" t="n">
-        <v>6978591</v>
+        <v>6978284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12799,6 +12799,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12825,10 +12830,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129295812</v>
+        <v>129293329</v>
       </c>
       <c r="B121" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,34 +12841,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628900</v>
+        <v>628640</v>
       </c>
       <c r="R121" t="n">
-        <v>6978416</v>
+        <v>6978364</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12922,32 +12936,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129302257</v>
+        <v>129302273</v>
       </c>
       <c r="B122" t="n">
-        <v>91997</v>
+        <v>80146</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12957,10 +12971,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628794</v>
+        <v>628878</v>
       </c>
       <c r="R122" t="n">
-        <v>6978311</v>
+        <v>6978535</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13019,45 +13033,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129302273</v>
+        <v>129294695</v>
       </c>
       <c r="B123" t="n">
-        <v>80146</v>
+        <v>91992</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628878</v>
+        <v>628831</v>
       </c>
       <c r="R123" t="n">
-        <v>6978535</v>
+        <v>6978180</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13116,54 +13130,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129293329</v>
+        <v>129297070</v>
       </c>
       <c r="B124" t="n">
-        <v>57724</v>
+        <v>91992</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628640</v>
+        <v>628764</v>
       </c>
       <c r="R124" t="n">
-        <v>6978364</v>
+        <v>6978591</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13222,10 +13227,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302242</v>
+        <v>129295812</v>
       </c>
       <c r="B125" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13233,34 +13238,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628750</v>
+        <v>628900</v>
       </c>
       <c r="R125" t="n">
-        <v>6978284</v>
+        <v>6978416</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13293,11 +13298,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13324,45 +13324,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129291548</v>
+        <v>129290523</v>
       </c>
       <c r="B126" t="n">
-        <v>80050</v>
+        <v>57727</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628549</v>
+        <v>628509</v>
       </c>
       <c r="R126" t="n">
-        <v>6978433</v>
+        <v>6978510</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13395,6 +13400,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13421,38 +13431,37 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129290523</v>
+        <v>129291461</v>
       </c>
       <c r="B127" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13461,10 +13470,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628509</v>
+        <v>628547</v>
       </c>
       <c r="R127" t="n">
-        <v>6978510</v>
+        <v>6978457</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13497,11 +13506,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13528,50 +13532,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129289677</v>
+        <v>129290692</v>
       </c>
       <c r="B128" t="n">
-        <v>57724</v>
+        <v>80106</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628484</v>
+        <v>628515</v>
       </c>
       <c r="R128" t="n">
-        <v>6978568</v>
+        <v>6978451</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13630,7 +13629,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129290692</v>
+        <v>129294090</v>
       </c>
       <c r="B129" t="n">
         <v>80106</v>
@@ -13661,14 +13660,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628515</v>
+        <v>628743</v>
       </c>
       <c r="R129" t="n">
-        <v>6978451</v>
+        <v>6978155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13727,10 +13726,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129294090</v>
+        <v>129291548</v>
       </c>
       <c r="B130" t="n">
-        <v>80106</v>
+        <v>80050</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13738,34 +13737,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628743</v>
+        <v>628549</v>
       </c>
       <c r="R130" t="n">
-        <v>6978155</v>
+        <v>6978433</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13824,37 +13823,38 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129291461</v>
+        <v>129289677</v>
       </c>
       <c r="B131" t="n">
-        <v>98678</v>
+        <v>57724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -13863,10 +13863,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628547</v>
+        <v>628484</v>
       </c>
       <c r="R131" t="n">
-        <v>6978457</v>
+        <v>6978568</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14127,7 +14127,7 @@
         <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129302228</v>
+        <v>129295655</v>
       </c>
       <c r="B136" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,34 +14329,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628870</v>
+        <v>628796</v>
       </c>
       <c r="R136" t="n">
-        <v>6978469</v>
+        <v>6978373</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14415,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B137" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14426,16 +14435,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -14443,26 +14452,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R137" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14495,6 +14500,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14521,7 +14531,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293208</v>
+        <v>129293275</v>
       </c>
       <c r="B138" t="n">
         <v>57727</v>
@@ -14561,10 +14571,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628695</v>
+        <v>628693</v>
       </c>
       <c r="R138" t="n">
-        <v>6978356</v>
+        <v>6978372</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14628,10 +14638,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129293275</v>
+        <v>129302228</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14639,39 +14649,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628693</v>
+        <v>628870</v>
       </c>
       <c r="R139" t="n">
-        <v>6978372</v>
+        <v>6978469</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14704,11 +14709,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14735,32 +14735,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129291606</v>
+        <v>129290695</v>
       </c>
       <c r="B140" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628564</v>
+        <v>628509</v>
       </c>
       <c r="R140" t="n">
-        <v>6978436</v>
+        <v>6978440</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14832,10 +14832,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129302266</v>
+        <v>129291606</v>
       </c>
       <c r="B141" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14843,21 +14843,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628639</v>
+        <v>628564</v>
       </c>
       <c r="R141" t="n">
-        <v>6978441</v>
+        <v>6978436</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14929,45 +14929,50 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129302288</v>
+        <v>129293977</v>
       </c>
       <c r="B142" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628636</v>
+        <v>628687</v>
       </c>
       <c r="R142" t="n">
-        <v>6978511</v>
+        <v>6978194</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15004,7 +15009,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15031,32 +15036,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129302272</v>
+        <v>129302266</v>
       </c>
       <c r="B143" t="n">
-        <v>97549</v>
+        <v>91837</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15066,10 +15071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628641</v>
+        <v>628639</v>
       </c>
       <c r="R143" t="n">
-        <v>6978450</v>
+        <v>6978441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15128,32 +15133,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129290695</v>
+        <v>129302288</v>
       </c>
       <c r="B144" t="n">
-        <v>80182</v>
+        <v>98704</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15163,10 +15168,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628509</v>
+        <v>628636</v>
       </c>
       <c r="R144" t="n">
-        <v>6978440</v>
+        <v>6978511</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15199,6 +15204,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15225,50 +15235,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129293977</v>
+        <v>129302272</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>97575</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628687</v>
+        <v>628641</v>
       </c>
       <c r="R145" t="n">
-        <v>6978194</v>
+        <v>6978450</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15301,11 +15306,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15332,32 +15332,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129295841</v>
+        <v>129302230</v>
       </c>
       <c r="B146" t="n">
-        <v>91743</v>
+        <v>91540</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15367,10 +15367,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628889</v>
+        <v>628766</v>
       </c>
       <c r="R146" t="n">
-        <v>6978417</v>
+        <v>6978195</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15429,10 +15429,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129295133</v>
+        <v>129302261</v>
       </c>
       <c r="B147" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15440,34 +15440,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628788</v>
+        <v>628794</v>
       </c>
       <c r="R147" t="n">
-        <v>6978227</v>
+        <v>6978311</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15526,49 +15526,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129290760</v>
+        <v>129302226</v>
       </c>
       <c r="B148" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628499</v>
+        <v>628849</v>
       </c>
       <c r="R148" t="n">
-        <v>6978448</v>
+        <v>6978507</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15627,10 +15623,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129295719</v>
+        <v>129302292</v>
       </c>
       <c r="B149" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15638,34 +15634,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628846</v>
+        <v>628819</v>
       </c>
       <c r="R149" t="n">
-        <v>6978364</v>
+        <v>6978067</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15698,6 +15694,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15724,10 +15725,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129295136</v>
+        <v>129302249</v>
       </c>
       <c r="B150" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15735,34 +15736,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628799</v>
+        <v>628539</v>
       </c>
       <c r="R150" t="n">
-        <v>6978234</v>
+        <v>6978526</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15795,6 +15796,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15821,10 +15827,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302230</v>
+        <v>129302238</v>
       </c>
       <c r="B151" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15832,21 +15838,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15856,10 +15862,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628766</v>
+        <v>628757</v>
       </c>
       <c r="R151" t="n">
-        <v>6978195</v>
+        <v>6978192</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15892,6 +15898,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15918,32 +15929,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302261</v>
+        <v>129302285</v>
       </c>
       <c r="B152" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15953,10 +15964,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628794</v>
+        <v>628656</v>
       </c>
       <c r="R152" t="n">
-        <v>6978311</v>
+        <v>6978459</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15989,6 +16000,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16015,10 +16031,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302226</v>
+        <v>129295136</v>
       </c>
       <c r="B153" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16026,34 +16042,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628849</v>
+        <v>628799</v>
       </c>
       <c r="R153" t="n">
-        <v>6978507</v>
+        <v>6978234</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16112,32 +16128,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129302292</v>
+        <v>129295841</v>
       </c>
       <c r="B154" t="n">
-        <v>79041</v>
+        <v>91752</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16147,10 +16163,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628819</v>
+        <v>628889</v>
       </c>
       <c r="R154" t="n">
-        <v>6978067</v>
+        <v>6978417</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16183,11 +16199,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16214,10 +16225,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302249</v>
+        <v>129295133</v>
       </c>
       <c r="B155" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16225,34 +16236,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628539</v>
+        <v>628788</v>
       </c>
       <c r="R155" t="n">
-        <v>6978526</v>
+        <v>6978227</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16285,11 +16296,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16316,45 +16322,49 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302238</v>
+        <v>129290760</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628757</v>
+        <v>628499</v>
       </c>
       <c r="R156" t="n">
-        <v>6978192</v>
+        <v>6978448</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16387,11 +16397,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,32 +16423,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302285</v>
+        <v>129302297</v>
       </c>
       <c r="B157" t="n">
-        <v>98678</v>
+        <v>100892</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16453,10 +16458,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628656</v>
+        <v>628720</v>
       </c>
       <c r="R157" t="n">
-        <v>6978459</v>
+        <v>6978591</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,11 +16494,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16520,45 +16520,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302297</v>
+        <v>129295719</v>
       </c>
       <c r="B158" t="n">
-        <v>100866</v>
+        <v>80146</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628720</v>
+        <v>628846</v>
       </c>
       <c r="R158" t="n">
-        <v>6978591</v>
+        <v>6978364</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16620,7 +16620,7 @@
         <v>129290278</v>
       </c>
       <c r="B159" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16637,12 +16637,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16714,27 +16714,27 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129295735</v>
+        <v>129289808</v>
       </c>
       <c r="B160" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -16745,14 +16745,14 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628841</v>
+        <v>628421</v>
       </c>
       <c r="R160" t="n">
-        <v>6978384</v>
+        <v>6978541</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16811,27 +16811,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129289808</v>
+        <v>129295735</v>
       </c>
       <c r="B161" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -16842,14 +16842,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628421</v>
+        <v>628841</v>
       </c>
       <c r="R161" t="n">
-        <v>6978541</v>
+        <v>6978384</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16908,10 +16908,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129302234</v>
+        <v>129302253</v>
       </c>
       <c r="B162" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16919,21 +16919,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628641</v>
+        <v>628759</v>
       </c>
       <c r="R162" t="n">
-        <v>6978450</v>
+        <v>6978235</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17005,10 +17005,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129302253</v>
+        <v>129302234</v>
       </c>
       <c r="B163" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17016,21 +17016,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628759</v>
+        <v>628641</v>
       </c>
       <c r="R163" t="n">
-        <v>6978235</v>
+        <v>6978450</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17105,7 +17105,7 @@
         <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2278,7 +2278,7 @@
         <v>129292781</v>
       </c>
       <c r="B15" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129295830</v>
       </c>
       <c r="B16" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302237</v>
+        <v>129302245</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628766</v>
+        <v>628749</v>
       </c>
       <c r="R18" t="n">
-        <v>6978173</v>
+        <v>6978341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,7 +2668,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302245</v>
+        <v>129302237</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628749</v>
+        <v>628766</v>
       </c>
       <c r="R19" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,7 +2773,7 @@
         <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,50 +2872,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294050</v>
+        <v>129293584</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628728</v>
+        <v>628624</v>
       </c>
       <c r="R21" t="n">
-        <v>6978173</v>
+        <v>6978328</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,11 +2943,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,7 +2972,7 @@
         <v>129292558</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294036</v>
+        <v>129302262</v>
       </c>
       <c r="B23" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,14 +3101,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628728</v>
+        <v>628800</v>
       </c>
       <c r="R23" t="n">
-        <v>6978173</v>
+        <v>6978306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,10 +3167,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129290628</v>
+        <v>129302265</v>
       </c>
       <c r="B24" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3212,10 +3202,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628499</v>
+        <v>628772</v>
       </c>
       <c r="R24" t="n">
-        <v>6978448</v>
+        <v>6978157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,32 +3264,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129293584</v>
+        <v>129302243</v>
       </c>
       <c r="B25" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3299,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628624</v>
+        <v>628743</v>
       </c>
       <c r="R25" t="n">
-        <v>6978328</v>
+        <v>6978315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,6 +3335,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,32 +3366,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302278</v>
+        <v>129302240</v>
       </c>
       <c r="B26" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3406,10 +3401,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628894</v>
+        <v>628764</v>
       </c>
       <c r="R26" t="n">
-        <v>6978483</v>
+        <v>6978279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3446,7 +3441,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,45 +3468,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302284</v>
+        <v>129294036</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628667</v>
+        <v>628728</v>
       </c>
       <c r="R27" t="n">
-        <v>6978461</v>
+        <v>6978173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,11 +3539,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,32 +3565,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302269</v>
+        <v>129290628</v>
       </c>
       <c r="B28" t="n">
-        <v>97575</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3610,10 +3600,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628792</v>
+        <v>628499</v>
       </c>
       <c r="R28" t="n">
-        <v>6978309</v>
+        <v>6978448</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302262</v>
+        <v>129294050</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,34 +3673,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628800</v>
+        <v>628728</v>
       </c>
       <c r="R29" t="n">
-        <v>6978306</v>
+        <v>6978173</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3743,6 +3738,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,32 +3769,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302265</v>
+        <v>129302284</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628772</v>
+        <v>628667</v>
       </c>
       <c r="R30" t="n">
-        <v>6978157</v>
+        <v>6978461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,6 +3840,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,32 +3871,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302243</v>
+        <v>129302278</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628743</v>
+        <v>628894</v>
       </c>
       <c r="R31" t="n">
-        <v>6978315</v>
+        <v>6978483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3946,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302240</v>
+        <v>129302269</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>97576</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4003,10 +4008,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628764</v>
+        <v>628792</v>
       </c>
       <c r="R32" t="n">
-        <v>6978279</v>
+        <v>6978309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,11 +4044,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4073,7 +4073,7 @@
         <v>129295187</v>
       </c>
       <c r="B33" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,45 +4167,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129290118</v>
+        <v>129294218</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>96039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628453</v>
+        <v>628798</v>
       </c>
       <c r="R34" t="n">
-        <v>6978518</v>
+        <v>6978072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,6 +4238,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,45 +4269,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294218</v>
+        <v>129290118</v>
       </c>
       <c r="B35" t="n">
-        <v>96038</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1079</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628798</v>
+        <v>628453</v>
       </c>
       <c r="R35" t="n">
-        <v>6978072</v>
+        <v>6978518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,11 +4340,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4766,7 +4766,7 @@
         <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,49 +4865,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290183</v>
+        <v>129291502</v>
       </c>
       <c r="B41" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628436</v>
+        <v>628564</v>
       </c>
       <c r="R41" t="n">
-        <v>6978498</v>
+        <v>6978436</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5063,32 +5059,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B43" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5098,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R43" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5160,45 +5156,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293533</v>
+        <v>129296072</v>
       </c>
       <c r="B44" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628623</v>
+        <v>628971</v>
       </c>
       <c r="R44" t="n">
-        <v>6978341</v>
+        <v>6978518</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5257,42 +5262,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129296072</v>
+        <v>129290183</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628971</v>
+        <v>628436</v>
       </c>
       <c r="R45" t="n">
-        <v>6978518</v>
+        <v>6978498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290616</v>
+        <v>129302294</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628499</v>
+        <v>628661</v>
       </c>
       <c r="R47" t="n">
-        <v>6978448</v>
+        <v>6978421</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,32 +5562,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290361</v>
+        <v>129302275</v>
       </c>
       <c r="B48" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628465</v>
+        <v>628663</v>
       </c>
       <c r="R48" t="n">
-        <v>6978491</v>
+        <v>6978428</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,6 +5633,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,32 +5664,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129296084</v>
+        <v>129302276</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628959</v>
+        <v>628648</v>
       </c>
       <c r="R49" t="n">
-        <v>6978530</v>
+        <v>6978420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,6 +5735,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5756,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290169</v>
+        <v>129290616</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5767,39 +5777,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628453</v>
+        <v>628499</v>
       </c>
       <c r="R50" t="n">
-        <v>6978518</v>
+        <v>6978448</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,11 +5837,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,49 +5863,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290084</v>
+        <v>129290361</v>
       </c>
       <c r="B51" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628475</v>
+        <v>628465</v>
       </c>
       <c r="R51" t="n">
-        <v>6978540</v>
+        <v>6978491</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,10 +5960,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302231</v>
+        <v>129296084</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5975,21 +5971,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5999,10 +5995,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628752</v>
+        <v>628959</v>
       </c>
       <c r="R52" t="n">
-        <v>6978198</v>
+        <v>6978530</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6061,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129302233</v>
+        <v>129290169</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6072,34 +6068,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628759</v>
+        <v>628453</v>
       </c>
       <c r="R53" t="n">
-        <v>6978233</v>
+        <v>6978518</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6132,6 +6133,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6158,45 +6164,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129302294</v>
+        <v>129290084</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628661</v>
+        <v>628475</v>
       </c>
       <c r="R54" t="n">
-        <v>6978421</v>
+        <v>6978540</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6255,32 +6265,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129302275</v>
+        <v>129302231</v>
       </c>
       <c r="B55" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628663</v>
+        <v>628752</v>
       </c>
       <c r="R55" t="n">
-        <v>6978428</v>
+        <v>6978198</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6326,11 +6336,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6357,32 +6362,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302276</v>
+        <v>129302233</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6392,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628648</v>
+        <v>628759</v>
       </c>
       <c r="R56" t="n">
-        <v>6978420</v>
+        <v>6978233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6428,11 +6433,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6459,45 +6459,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129295935</v>
+        <v>129293780</v>
       </c>
       <c r="B57" t="n">
-        <v>91554</v>
+        <v>57719</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>100110</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628907</v>
+        <v>628680</v>
       </c>
       <c r="R57" t="n">
-        <v>6978423</v>
+        <v>6978235</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6556,10 +6565,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129294015</v>
+        <v>129295935</v>
       </c>
       <c r="B58" t="n">
-        <v>80146</v>
+        <v>91554</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6567,34 +6576,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628728</v>
+        <v>628907</v>
       </c>
       <c r="R58" t="n">
-        <v>6978173</v>
+        <v>6978423</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,54 +6662,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B59" t="n">
-        <v>57719</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R59" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302229</v>
+        <v>129302274</v>
       </c>
       <c r="B60" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6770,21 +6770,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628761</v>
+        <v>628659</v>
       </c>
       <c r="R60" t="n">
-        <v>6978157</v>
+        <v>6978419</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6958,32 +6958,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302271</v>
+        <v>129302229</v>
       </c>
       <c r="B62" t="n">
-        <v>97575</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628763</v>
+        <v>628761</v>
       </c>
       <c r="R62" t="n">
-        <v>6978273</v>
+        <v>6978157</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302274</v>
+        <v>129302241</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628659</v>
+        <v>628741</v>
       </c>
       <c r="R63" t="n">
-        <v>6978419</v>
+        <v>6978271</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7126,6 +7126,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7152,32 +7157,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302241</v>
+        <v>129302271</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>97576</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7187,10 +7192,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628741</v>
+        <v>628763</v>
       </c>
       <c r="R64" t="n">
-        <v>6978271</v>
+        <v>6978273</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7223,11 +7228,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7254,10 +7254,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129291473</v>
+        <v>129295162</v>
       </c>
       <c r="B65" t="n">
-        <v>98704</v>
+        <v>91993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,38 +7265,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628549</v>
+        <v>628834</v>
       </c>
       <c r="R65" t="n">
-        <v>6978449</v>
+        <v>6978251</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7355,10 +7351,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129290108</v>
+        <v>129292729</v>
       </c>
       <c r="B66" t="n">
-        <v>98704</v>
+        <v>91993</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7366,38 +7362,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628447</v>
+        <v>628599</v>
       </c>
       <c r="R66" t="n">
-        <v>6978522</v>
+        <v>6978448</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7456,32 +7448,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129291635</v>
+        <v>129302250</v>
       </c>
       <c r="B67" t="n">
-        <v>96038</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7491,10 +7483,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628573</v>
+        <v>628495</v>
       </c>
       <c r="R67" t="n">
-        <v>6978423</v>
+        <v>6978647</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,6 +7519,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7553,10 +7550,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129294000</v>
+        <v>129302244</v>
       </c>
       <c r="B68" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7564,21 +7561,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7588,10 +7585,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628687</v>
+        <v>628756</v>
       </c>
       <c r="R68" t="n">
-        <v>6978194</v>
+        <v>6978337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7624,6 +7621,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7650,45 +7652,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129295162</v>
+        <v>129294000</v>
       </c>
       <c r="B69" t="n">
-        <v>91992</v>
+        <v>91540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628834</v>
+        <v>628687</v>
       </c>
       <c r="R69" t="n">
-        <v>6978251</v>
+        <v>6978194</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7747,10 +7749,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129292729</v>
+        <v>129291635</v>
       </c>
       <c r="B70" t="n">
-        <v>91992</v>
+        <v>96039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7758,21 +7760,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>1079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7782,10 +7784,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628599</v>
+        <v>628573</v>
       </c>
       <c r="R70" t="n">
-        <v>6978448</v>
+        <v>6978423</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7950,10 +7952,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302280</v>
+        <v>129291473</v>
       </c>
       <c r="B72" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7978,17 +7980,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628692</v>
+        <v>628549</v>
       </c>
       <c r="R72" t="n">
-        <v>6978432</v>
+        <v>6978449</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8021,11 +8027,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8052,10 +8053,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302259</v>
+        <v>129290108</v>
       </c>
       <c r="B73" t="n">
-        <v>91992</v>
+        <v>98705</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8063,34 +8064,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628771</v>
+        <v>628447</v>
       </c>
       <c r="R73" t="n">
-        <v>6978154</v>
+        <v>6978522</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8149,32 +8154,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302250</v>
+        <v>129302259</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8184,10 +8189,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628495</v>
+        <v>628771</v>
       </c>
       <c r="R74" t="n">
-        <v>6978647</v>
+        <v>6978154</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8220,11 +8225,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302244</v>
+        <v>129302254</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628756</v>
+        <v>628894</v>
       </c>
       <c r="R75" t="n">
-        <v>6978337</v>
+        <v>6978096</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8353,32 +8353,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129302254</v>
+        <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>57724</v>
+        <v>98705</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8388,10 +8388,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628894</v>
+        <v>628692</v>
       </c>
       <c r="R76" t="n">
-        <v>6978096</v>
+        <v>6978432</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8455,10 +8455,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129302227</v>
+        <v>129289501</v>
       </c>
       <c r="B77" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,34 +8466,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628851</v>
+        <v>628451</v>
       </c>
       <c r="R77" t="n">
-        <v>6978504</v>
+        <v>6978596</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8526,6 +8531,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8555,7 +8565,7 @@
         <v>129290447</v>
       </c>
       <c r="B78" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8652,7 +8662,7 @@
         <v>129295124</v>
       </c>
       <c r="B79" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8746,50 +8756,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129289501</v>
+        <v>129302281</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628451</v>
+        <v>628688</v>
       </c>
       <c r="R80" t="n">
-        <v>6978596</v>
+        <v>6978441</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8826,7 +8835,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8835,6 +8844,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8853,10 +8863,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302255</v>
+        <v>129302227</v>
       </c>
       <c r="B81" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8864,21 +8874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8888,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628712</v>
+        <v>628851</v>
       </c>
       <c r="R81" t="n">
-        <v>6978376</v>
+        <v>6978504</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,11 +8934,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8955,49 +8960,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B82" t="n">
-        <v>98704</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R82" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,7 +9035,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9043,7 +9044,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129291441</v>
+        <v>129296224</v>
       </c>
       <c r="B83" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9073,34 +9073,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>628547</v>
+        <v>629061</v>
       </c>
       <c r="R83" t="n">
-        <v>6978457</v>
+        <v>6978494</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129296224</v>
+        <v>129291441</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9170,34 +9170,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>629061</v>
+        <v>628547</v>
       </c>
       <c r="R84" t="n">
-        <v>6978494</v>
+        <v>6978457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9256,45 +9256,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129302260</v>
+        <v>129293914</v>
       </c>
       <c r="B85" t="n">
-        <v>91992</v>
+        <v>57887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628641</v>
+        <v>628690</v>
       </c>
       <c r="R85" t="n">
-        <v>6978450</v>
+        <v>6978221</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,32 +9358,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302258</v>
+        <v>129302291</v>
       </c>
       <c r="B86" t="n">
-        <v>91992</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9393,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628851</v>
+        <v>628794</v>
       </c>
       <c r="R86" t="n">
-        <v>6978502</v>
+        <v>6978373</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,45 +9455,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302291</v>
+        <v>129294276</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>91753</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>48</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628794</v>
+        <v>628790</v>
       </c>
       <c r="R87" t="n">
-        <v>6978373</v>
+        <v>6978034</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,45 +9552,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129294276</v>
+        <v>129292746</v>
       </c>
       <c r="B88" t="n">
-        <v>91752</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628790</v>
+        <v>628586</v>
       </c>
       <c r="R88" t="n">
-        <v>6978034</v>
+        <v>6978451</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,10 +9649,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129292746</v>
+        <v>129290229</v>
       </c>
       <c r="B89" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9679,10 +9684,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628586</v>
+        <v>628436</v>
       </c>
       <c r="R89" t="n">
-        <v>6978451</v>
+        <v>6978498</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,32 +9746,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129290229</v>
+        <v>129296097</v>
       </c>
       <c r="B90" t="n">
-        <v>91837</v>
+        <v>80175</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9776,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628436</v>
+        <v>628959</v>
       </c>
       <c r="R90" t="n">
-        <v>6978498</v>
+        <v>6978530</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9935,45 +9940,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129296097</v>
+        <v>129293890</v>
       </c>
       <c r="B92" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628959</v>
+        <v>628691</v>
       </c>
       <c r="R92" t="n">
-        <v>6978530</v>
+        <v>6978242</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10006,6 +10016,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10032,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129293890</v>
+        <v>129302232</v>
       </c>
       <c r="B93" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10043,39 +10058,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628691</v>
+        <v>628742</v>
       </c>
       <c r="R93" t="n">
-        <v>6978242</v>
+        <v>6978216</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10108,11 +10118,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10139,10 +10144,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129293914</v>
+        <v>129302267</v>
       </c>
       <c r="B94" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10150,39 +10155,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628690</v>
+        <v>628603</v>
       </c>
       <c r="R94" t="n">
-        <v>6978221</v>
+        <v>6978502</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,10 +10241,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302232</v>
+        <v>129302264</v>
       </c>
       <c r="B95" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10252,21 +10252,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628742</v>
+        <v>628796</v>
       </c>
       <c r="R95" t="n">
-        <v>6978216</v>
+        <v>6978261</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302267</v>
+        <v>129302260</v>
       </c>
       <c r="B96" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628603</v>
+        <v>628641</v>
       </c>
       <c r="R96" t="n">
-        <v>6978502</v>
+        <v>6978450</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,32 +10435,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129302264</v>
+        <v>129302258</v>
       </c>
       <c r="B97" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628796</v>
+        <v>628851</v>
       </c>
       <c r="R97" t="n">
-        <v>6978261</v>
+        <v>6978502</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10641,7 +10641,7 @@
         <v>129293044</v>
       </c>
       <c r="B99" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10933,49 +10933,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129295651</v>
+        <v>129302263</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628796</v>
+        <v>628810</v>
       </c>
       <c r="R102" t="n">
-        <v>6978373</v>
+        <v>6978299</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11034,32 +11030,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302263</v>
+        <v>129302282</v>
       </c>
       <c r="B103" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11069,10 +11065,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628810</v>
+        <v>628654</v>
       </c>
       <c r="R103" t="n">
-        <v>6978299</v>
+        <v>6978418</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11105,6 +11101,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11131,32 +11132,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302268</v>
+        <v>129302287</v>
       </c>
       <c r="B104" t="n">
-        <v>97575</v>
+        <v>98705</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11166,10 +11167,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628719</v>
+        <v>628649</v>
       </c>
       <c r="R104" t="n">
-        <v>6978594</v>
+        <v>6978449</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11202,6 +11203,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11228,32 +11234,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302282</v>
+        <v>129302268</v>
       </c>
       <c r="B105" t="n">
-        <v>98704</v>
+        <v>97576</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11263,10 +11269,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628654</v>
+        <v>628719</v>
       </c>
       <c r="R105" t="n">
-        <v>6978418</v>
+        <v>6978594</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,11 +11305,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11330,10 +11331,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302287</v>
+        <v>129295651</v>
       </c>
       <c r="B106" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11358,17 +11359,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628649</v>
+        <v>628796</v>
       </c>
       <c r="R106" t="n">
-        <v>6978449</v>
+        <v>6978373</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11401,11 +11406,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129302246</v>
+        <v>129289885</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,21 +11443,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11467,10 +11467,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628750</v>
+        <v>628447</v>
       </c>
       <c r="R107" t="n">
-        <v>6978346</v>
+        <v>6978522</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11503,11 +11503,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11534,10 +11529,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129302251</v>
+        <v>129293395</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11545,21 +11540,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11569,10 +11564,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628425</v>
+        <v>628616</v>
       </c>
       <c r="R108" t="n">
-        <v>6978621</v>
+        <v>6978368</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11605,11 +11600,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11743,10 +11733,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129293395</v>
+        <v>129302246</v>
       </c>
       <c r="B110" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11754,21 +11744,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11778,10 +11768,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>628616</v>
+        <v>628750</v>
       </c>
       <c r="R110" t="n">
-        <v>6978368</v>
+        <v>6978346</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11814,6 +11804,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11840,10 +11835,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129289885</v>
+        <v>129302251</v>
       </c>
       <c r="B111" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11851,21 +11846,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11875,10 +11870,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628447</v>
+        <v>628425</v>
       </c>
       <c r="R111" t="n">
-        <v>6978522</v>
+        <v>6978621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11911,6 +11906,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11940,7 +11940,7 @@
         <v>129293475</v>
       </c>
       <c r="B112" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12034,32 +12034,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129295820</v>
+        <v>129302225</v>
       </c>
       <c r="B113" t="n">
-        <v>91992</v>
+        <v>91540</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628889</v>
+        <v>628856</v>
       </c>
       <c r="R113" t="n">
-        <v>6978417</v>
+        <v>6978527</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12131,10 +12131,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302225</v>
+        <v>129302290</v>
       </c>
       <c r="B114" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12142,21 +12142,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628856</v>
+        <v>628712</v>
       </c>
       <c r="R114" t="n">
-        <v>6978527</v>
+        <v>6978591</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12228,32 +12228,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302290</v>
+        <v>129295820</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12263,10 +12263,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628712</v>
+        <v>628889</v>
       </c>
       <c r="R115" t="n">
-        <v>6978591</v>
+        <v>6978417</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12532,7 +12532,7 @@
         <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,45 +12631,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129302257</v>
+        <v>129295812</v>
       </c>
       <c r="B119" t="n">
-        <v>91992</v>
+        <v>91540</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628794</v>
+        <v>628900</v>
       </c>
       <c r="R119" t="n">
-        <v>6978311</v>
+        <v>6978416</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129302242</v>
+        <v>129293329</v>
       </c>
       <c r="B120" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,16 +12739,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12756,17 +12756,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628750</v>
+        <v>628640</v>
       </c>
       <c r="R120" t="n">
-        <v>6978284</v>
+        <v>6978364</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12799,11 +12808,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12830,54 +12834,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129293329</v>
+        <v>129294695</v>
       </c>
       <c r="B121" t="n">
-        <v>57724</v>
+        <v>91993</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628640</v>
+        <v>628831</v>
       </c>
       <c r="R121" t="n">
-        <v>6978364</v>
+        <v>6978180</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12936,32 +12931,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129302273</v>
+        <v>129297070</v>
       </c>
       <c r="B122" t="n">
-        <v>80146</v>
+        <v>91993</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12971,10 +12966,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628878</v>
+        <v>628764</v>
       </c>
       <c r="R122" t="n">
-        <v>6978535</v>
+        <v>6978591</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13033,45 +13028,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129294695</v>
+        <v>129302273</v>
       </c>
       <c r="B123" t="n">
-        <v>91992</v>
+        <v>80146</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628831</v>
+        <v>628878</v>
       </c>
       <c r="R123" t="n">
-        <v>6978180</v>
+        <v>6978535</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13130,32 +13125,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129297070</v>
+        <v>129302242</v>
       </c>
       <c r="B124" t="n">
-        <v>91992</v>
+        <v>57727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13165,10 +13160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628764</v>
+        <v>628750</v>
       </c>
       <c r="R124" t="n">
-        <v>6978591</v>
+        <v>6978284</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13201,6 +13196,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13227,45 +13227,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129295812</v>
+        <v>129302257</v>
       </c>
       <c r="B125" t="n">
-        <v>91540</v>
+        <v>91993</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628900</v>
+        <v>628794</v>
       </c>
       <c r="R125" t="n">
-        <v>6978416</v>
+        <v>6978311</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13324,50 +13324,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129290523</v>
+        <v>129291548</v>
       </c>
       <c r="B126" t="n">
-        <v>57727</v>
+        <v>80050</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628509</v>
+        <v>628549</v>
       </c>
       <c r="R126" t="n">
-        <v>6978510</v>
+        <v>6978433</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13400,11 +13395,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13431,37 +13421,38 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129291461</v>
+        <v>129289677</v>
       </c>
       <c r="B127" t="n">
-        <v>98704</v>
+        <v>57724</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13470,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628547</v>
+        <v>628484</v>
       </c>
       <c r="R127" t="n">
-        <v>6978457</v>
+        <v>6978568</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13532,45 +13523,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290692</v>
+        <v>129291461</v>
       </c>
       <c r="B128" t="n">
-        <v>80106</v>
+        <v>98705</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628515</v>
+        <v>628547</v>
       </c>
       <c r="R128" t="n">
-        <v>6978451</v>
+        <v>6978457</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13629,7 +13624,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129294090</v>
+        <v>129290692</v>
       </c>
       <c r="B129" t="n">
         <v>80106</v>
@@ -13660,14 +13655,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628743</v>
+        <v>628515</v>
       </c>
       <c r="R129" t="n">
-        <v>6978155</v>
+        <v>6978451</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13726,10 +13721,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129291548</v>
+        <v>129294090</v>
       </c>
       <c r="B130" t="n">
-        <v>80050</v>
+        <v>80106</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13737,34 +13732,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628549</v>
+        <v>628743</v>
       </c>
       <c r="R130" t="n">
-        <v>6978433</v>
+        <v>6978155</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13823,10 +13818,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129289677</v>
+        <v>129290523</v>
       </c>
       <c r="B131" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13834,16 +13829,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13854,7 +13849,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -13863,10 +13858,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628484</v>
+        <v>628509</v>
       </c>
       <c r="R131" t="n">
-        <v>6978568</v>
+        <v>6978510</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13899,6 +13894,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14127,7 +14127,7 @@
         <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B136" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,16 +14329,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14346,26 +14346,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R136" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14398,6 +14394,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14424,7 +14425,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293208</v>
+        <v>129293275</v>
       </c>
       <c r="B137" t="n">
         <v>57727</v>
@@ -14464,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628695</v>
+        <v>628693</v>
       </c>
       <c r="R137" t="n">
-        <v>6978356</v>
+        <v>6978372</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14531,10 +14532,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293275</v>
+        <v>129302228</v>
       </c>
       <c r="B138" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14542,39 +14543,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628693</v>
+        <v>628870</v>
       </c>
       <c r="R138" t="n">
-        <v>6978372</v>
+        <v>6978469</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14607,11 +14603,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14638,10 +14629,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129302228</v>
+        <v>129295655</v>
       </c>
       <c r="B139" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14649,34 +14640,43 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628870</v>
+        <v>628796</v>
       </c>
       <c r="R139" t="n">
-        <v>6978469</v>
+        <v>6978373</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14735,32 +14735,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129290695</v>
+        <v>129302266</v>
       </c>
       <c r="B140" t="n">
-        <v>80182</v>
+        <v>91838</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628509</v>
+        <v>628639</v>
       </c>
       <c r="R140" t="n">
-        <v>6978440</v>
+        <v>6978441</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14929,50 +14929,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129293977</v>
+        <v>129290695</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>80182</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628687</v>
+        <v>628509</v>
       </c>
       <c r="R142" t="n">
-        <v>6978194</v>
+        <v>6978440</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15005,11 +15000,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15036,10 +15026,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129302266</v>
+        <v>129293977</v>
       </c>
       <c r="B143" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15047,34 +15037,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628639</v>
+        <v>628687</v>
       </c>
       <c r="R143" t="n">
-        <v>6978441</v>
+        <v>6978194</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15107,6 +15102,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15136,7 +15136,7 @@
         <v>129302288</v>
       </c>
       <c r="B144" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>129302272</v>
       </c>
       <c r="B145" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15332,10 +15332,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B146" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15343,34 +15343,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R146" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15429,32 +15429,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302261</v>
+        <v>129295841</v>
       </c>
       <c r="B147" t="n">
-        <v>91837</v>
+        <v>91753</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15464,10 +15464,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628794</v>
+        <v>628889</v>
       </c>
       <c r="R147" t="n">
-        <v>6978311</v>
+        <v>6978417</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15526,10 +15526,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129302226</v>
+        <v>129295719</v>
       </c>
       <c r="B148" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15537,34 +15537,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628849</v>
+        <v>628846</v>
       </c>
       <c r="R148" t="n">
-        <v>6978507</v>
+        <v>6978364</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15623,45 +15623,49 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129302292</v>
+        <v>129290760</v>
       </c>
       <c r="B149" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628819</v>
+        <v>628499</v>
       </c>
       <c r="R149" t="n">
-        <v>6978067</v>
+        <v>6978448</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15694,11 +15698,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15725,10 +15724,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129302249</v>
+        <v>129295133</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15736,34 +15735,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628539</v>
+        <v>628788</v>
       </c>
       <c r="R150" t="n">
-        <v>6978526</v>
+        <v>6978227</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15796,11 +15795,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15827,10 +15821,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302238</v>
+        <v>129302292</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15838,21 +15832,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15862,10 +15856,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628757</v>
+        <v>628819</v>
       </c>
       <c r="R151" t="n">
-        <v>6978192</v>
+        <v>6978067</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15902,7 +15896,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15929,32 +15923,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302285</v>
+        <v>129302249</v>
       </c>
       <c r="B152" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15964,10 +15958,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628656</v>
+        <v>628539</v>
       </c>
       <c r="R152" t="n">
-        <v>6978459</v>
+        <v>6978526</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16004,7 +15998,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16031,10 +16025,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129295136</v>
+        <v>129302230</v>
       </c>
       <c r="B153" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16042,34 +16036,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628799</v>
+        <v>628766</v>
       </c>
       <c r="R153" t="n">
-        <v>6978234</v>
+        <v>6978195</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16128,32 +16122,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129295841</v>
+        <v>129302261</v>
       </c>
       <c r="B154" t="n">
-        <v>91752</v>
+        <v>91838</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16163,10 +16157,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628889</v>
+        <v>628794</v>
       </c>
       <c r="R154" t="n">
-        <v>6978417</v>
+        <v>6978311</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16225,7 +16219,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129295133</v>
+        <v>129302226</v>
       </c>
       <c r="B155" t="n">
         <v>91540</v>
@@ -16256,14 +16250,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628788</v>
+        <v>628849</v>
       </c>
       <c r="R155" t="n">
-        <v>6978227</v>
+        <v>6978507</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16322,49 +16316,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129290760</v>
+        <v>129302238</v>
       </c>
       <c r="B156" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628499</v>
+        <v>628757</v>
       </c>
       <c r="R156" t="n">
-        <v>6978448</v>
+        <v>6978192</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16397,6 +16387,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16423,32 +16418,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302297</v>
+        <v>129302285</v>
       </c>
       <c r="B157" t="n">
-        <v>100892</v>
+        <v>98705</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16458,10 +16453,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628720</v>
+        <v>628656</v>
       </c>
       <c r="R157" t="n">
-        <v>6978591</v>
+        <v>6978459</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16494,6 +16489,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16520,45 +16520,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129295719</v>
+        <v>129302297</v>
       </c>
       <c r="B158" t="n">
-        <v>80146</v>
+        <v>100894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628846</v>
+        <v>628720</v>
       </c>
       <c r="R158" t="n">
-        <v>6978364</v>
+        <v>6978591</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16620,7 +16620,7 @@
         <v>129290278</v>
       </c>
       <c r="B159" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16714,27 +16714,27 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129289808</v>
+        <v>129295735</v>
       </c>
       <c r="B160" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -16745,14 +16745,14 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628421</v>
+        <v>628841</v>
       </c>
       <c r="R160" t="n">
-        <v>6978541</v>
+        <v>6978384</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16811,27 +16811,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129295735</v>
+        <v>129289808</v>
       </c>
       <c r="B161" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -16842,14 +16842,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628841</v>
+        <v>628421</v>
       </c>
       <c r="R161" t="n">
-        <v>6978384</v>
+        <v>6978541</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16908,10 +16908,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129302253</v>
+        <v>129302234</v>
       </c>
       <c r="B162" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16919,21 +16919,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628759</v>
+        <v>628641</v>
       </c>
       <c r="R162" t="n">
-        <v>6978235</v>
+        <v>6978450</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17005,10 +17005,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129302234</v>
+        <v>129302253</v>
       </c>
       <c r="B163" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17016,21 +17016,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628641</v>
+        <v>628759</v>
       </c>
       <c r="R163" t="n">
-        <v>6978450</v>
+        <v>6978235</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17105,7 +17105,7 @@
         <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129292781</v>
+        <v>129295830</v>
       </c>
       <c r="B15" t="n">
         <v>92258</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628896</v>
       </c>
       <c r="R15" t="n">
-        <v>6978436</v>
+        <v>6978430</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295830</v>
+        <v>129295766</v>
       </c>
       <c r="B16" t="n">
-        <v>92258</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,34 +2383,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628896</v>
+        <v>628846</v>
       </c>
       <c r="R16" t="n">
-        <v>6978430</v>
+        <v>6978364</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295766</v>
+        <v>129292781</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>92258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,34 +2480,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628846</v>
+        <v>628590</v>
       </c>
       <c r="R17" t="n">
-        <v>6978364</v>
+        <v>6978436</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302245</v>
+        <v>129302237</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628749</v>
+        <v>628766</v>
       </c>
       <c r="R18" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,7 +2668,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302237</v>
+        <v>129302245</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628766</v>
+        <v>628749</v>
       </c>
       <c r="R19" t="n">
-        <v>6978173</v>
+        <v>6978341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,7 +2773,7 @@
         <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,45 +2872,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293584</v>
+        <v>129294050</v>
       </c>
       <c r="B21" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628624</v>
+        <v>628728</v>
       </c>
       <c r="R21" t="n">
-        <v>6978328</v>
+        <v>6978173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,6 +2948,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,49 +2979,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129292558</v>
+        <v>129290628</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628589</v>
+        <v>628499</v>
       </c>
       <c r="R22" t="n">
-        <v>6978414</v>
+        <v>6978448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,45 +3076,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302262</v>
+        <v>129292558</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628800</v>
+        <v>628589</v>
       </c>
       <c r="R23" t="n">
-        <v>6978306</v>
+        <v>6978414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3167,7 +3177,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302265</v>
+        <v>129302262</v>
       </c>
       <c r="B24" t="n">
         <v>91838</v>
@@ -3202,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628772</v>
+        <v>628800</v>
       </c>
       <c r="R24" t="n">
-        <v>6978157</v>
+        <v>6978306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,10 +3274,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302243</v>
+        <v>129302265</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3299,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628743</v>
+        <v>628772</v>
       </c>
       <c r="R25" t="n">
-        <v>6978315</v>
+        <v>6978157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,11 +3345,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302240</v>
+        <v>129302243</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3401,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628764</v>
+        <v>628743</v>
       </c>
       <c r="R26" t="n">
-        <v>6978279</v>
+        <v>6978315</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3441,7 +3446,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,10 +3473,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294036</v>
+        <v>129302240</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,34 +3484,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628728</v>
+        <v>628764</v>
       </c>
       <c r="R27" t="n">
-        <v>6978173</v>
+        <v>6978279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3539,6 +3544,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3565,32 +3575,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129290628</v>
+        <v>129293584</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3600,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628499</v>
+        <v>628624</v>
       </c>
       <c r="R28" t="n">
-        <v>6978448</v>
+        <v>6978328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294050</v>
+        <v>129294036</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3673,29 +3683,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
@@ -3738,11 +3743,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,32 +3769,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302284</v>
+        <v>129302269</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628667</v>
+        <v>628792</v>
       </c>
       <c r="R30" t="n">
-        <v>6978461</v>
+        <v>6978309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,11 +3840,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,7 +3869,7 @@
         <v>129302278</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3973,32 +3968,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302269</v>
+        <v>129302284</v>
       </c>
       <c r="B32" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4008,10 +4003,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628792</v>
+        <v>628667</v>
       </c>
       <c r="R32" t="n">
-        <v>6978309</v>
+        <v>6978461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,45 +4070,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129295187</v>
+        <v>129302277</v>
       </c>
       <c r="B33" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628834</v>
+        <v>628899</v>
       </c>
       <c r="R33" t="n">
-        <v>6978251</v>
+        <v>6978480</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4141,6 +4141,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4167,45 +4172,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129294218</v>
+        <v>129296183</v>
       </c>
       <c r="B34" t="n">
-        <v>96039</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628798</v>
+        <v>629055</v>
       </c>
       <c r="R34" t="n">
-        <v>6978072</v>
+        <v>6978511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,11 +4243,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4269,10 +4269,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129290118</v>
+        <v>129293171</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,34 +4280,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628453</v>
+        <v>628702</v>
       </c>
       <c r="R35" t="n">
-        <v>6978518</v>
+        <v>6978339</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4366,10 +4375,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129296183</v>
+        <v>129295187</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,34 +4386,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>629055</v>
+        <v>628834</v>
       </c>
       <c r="R36" t="n">
-        <v>6978511</v>
+        <v>6978251</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293171</v>
+        <v>129290118</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,43 +4483,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628702</v>
+        <v>628453</v>
       </c>
       <c r="R37" t="n">
-        <v>6978339</v>
+        <v>6978518</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,45 +4569,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302235</v>
+        <v>129294218</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>96040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628629</v>
+        <v>628798</v>
       </c>
       <c r="R38" t="n">
-        <v>6978532</v>
+        <v>6978072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,6 +4640,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302293</v>
+        <v>129302235</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,21 +4682,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4701,10 +4706,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628737</v>
+        <v>628629</v>
       </c>
       <c r="R39" t="n">
-        <v>6978300</v>
+        <v>6978532</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,32 +4768,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129302277</v>
+        <v>129302293</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4798,10 +4803,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628899</v>
+        <v>628737</v>
       </c>
       <c r="R40" t="n">
-        <v>6978480</v>
+        <v>6978300</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4834,11 +4839,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,45 +4865,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129291502</v>
+        <v>129290183</v>
       </c>
       <c r="B41" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628564</v>
+        <v>628436</v>
       </c>
       <c r="R41" t="n">
-        <v>6978436</v>
+        <v>6978498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4962,10 +4966,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129294028</v>
+        <v>129296072</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4973,34 +4977,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628728</v>
+        <v>628971</v>
       </c>
       <c r="R42" t="n">
-        <v>6978173</v>
+        <v>6978518</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,45 +5072,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293533</v>
+        <v>129294028</v>
       </c>
       <c r="B43" t="n">
-        <v>91993</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628623</v>
+        <v>628728</v>
       </c>
       <c r="R43" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5156,54 +5169,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296072</v>
+        <v>129293533</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628971</v>
+        <v>628623</v>
       </c>
       <c r="R44" t="n">
-        <v>6978518</v>
+        <v>6978341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,49 +5266,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129290183</v>
+        <v>129291502</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628436</v>
+        <v>628564</v>
       </c>
       <c r="R45" t="n">
-        <v>6978498</v>
+        <v>6978436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129302294</v>
+        <v>129296084</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628661</v>
+        <v>628959</v>
       </c>
       <c r="R47" t="n">
-        <v>6978421</v>
+        <v>6978530</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,45 +5562,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129302275</v>
+        <v>129290169</v>
       </c>
       <c r="B48" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628663</v>
+        <v>628453</v>
       </c>
       <c r="R48" t="n">
-        <v>6978428</v>
+        <v>6978518</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5637,7 +5642,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,32 +5669,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129302276</v>
+        <v>129290361</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628648</v>
+        <v>628465</v>
       </c>
       <c r="R49" t="n">
-        <v>6978420</v>
+        <v>6978491</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,11 +5740,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,45 +5766,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290616</v>
+        <v>129290084</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628499</v>
+        <v>628475</v>
       </c>
       <c r="R50" t="n">
-        <v>6978448</v>
+        <v>6978540</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5863,7 +5867,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290361</v>
+        <v>129302233</v>
       </c>
       <c r="B51" t="n">
         <v>91540</v>
@@ -5898,10 +5902,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628465</v>
+        <v>628759</v>
       </c>
       <c r="R51" t="n">
-        <v>6978491</v>
+        <v>6978233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5960,10 +5964,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129296084</v>
+        <v>129302231</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5971,21 +5975,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5995,10 +5999,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628959</v>
+        <v>628752</v>
       </c>
       <c r="R52" t="n">
-        <v>6978530</v>
+        <v>6978198</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6057,10 +6061,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129290169</v>
+        <v>129290616</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6068,39 +6072,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628453</v>
+        <v>628499</v>
       </c>
       <c r="R53" t="n">
-        <v>6978518</v>
+        <v>6978448</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6133,11 +6132,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6158,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129290084</v>
+        <v>129302276</v>
       </c>
       <c r="B54" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6192,21 +6186,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628475</v>
+        <v>628648</v>
       </c>
       <c r="R54" t="n">
-        <v>6978540</v>
+        <v>6978420</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6239,6 +6229,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6265,32 +6260,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129302231</v>
+        <v>129302275</v>
       </c>
       <c r="B55" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6300,10 +6295,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628752</v>
+        <v>628663</v>
       </c>
       <c r="R55" t="n">
-        <v>6978198</v>
+        <v>6978428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6336,6 +6331,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,10 +6362,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302233</v>
+        <v>129302294</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628759</v>
+        <v>628661</v>
       </c>
       <c r="R56" t="n">
-        <v>6978233</v>
+        <v>6978421</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6459,54 +6459,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B57" t="n">
-        <v>57719</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R57" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,45 +6653,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129294015</v>
+        <v>129293780</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>57719</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628728</v>
+        <v>628680</v>
       </c>
       <c r="R59" t="n">
-        <v>6978173</v>
+        <v>6978235</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302274</v>
+        <v>129302229</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6770,21 +6770,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628659</v>
+        <v>628761</v>
       </c>
       <c r="R60" t="n">
-        <v>6978419</v>
+        <v>6978157</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302252</v>
+        <v>129302274</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628837</v>
+        <v>628659</v>
       </c>
       <c r="R61" t="n">
-        <v>6978500</v>
+        <v>6978419</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6927,11 +6927,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,10 +6953,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302229</v>
+        <v>129302241</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6969,21 +6964,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6993,10 +6988,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628761</v>
+        <v>628741</v>
       </c>
       <c r="R62" t="n">
-        <v>6978157</v>
+        <v>6978271</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7029,6 +7024,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7055,10 +7055,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302241</v>
+        <v>129302252</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628741</v>
+        <v>628837</v>
       </c>
       <c r="R63" t="n">
-        <v>6978271</v>
+        <v>6978500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7160,7 +7160,7 @@
         <v>129302271</v>
       </c>
       <c r="B64" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7254,45 +7254,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129295162</v>
+        <v>129297292</v>
       </c>
       <c r="B65" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628834</v>
+        <v>628429</v>
       </c>
       <c r="R65" t="n">
-        <v>6978251</v>
+        <v>6978625</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7351,7 +7360,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129292729</v>
+        <v>129295162</v>
       </c>
       <c r="B66" t="n">
         <v>91993</v>
@@ -7382,14 +7391,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628599</v>
+        <v>628834</v>
       </c>
       <c r="R66" t="n">
-        <v>6978448</v>
+        <v>6978251</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7448,32 +7457,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129302250</v>
+        <v>129292729</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7483,10 +7492,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628495</v>
+        <v>628599</v>
       </c>
       <c r="R67" t="n">
-        <v>6978647</v>
+        <v>6978448</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7519,11 +7528,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7550,32 +7554,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129302244</v>
+        <v>129291635</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>96040</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7585,10 +7589,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628756</v>
+        <v>628573</v>
       </c>
       <c r="R68" t="n">
-        <v>6978337</v>
+        <v>6978423</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7621,11 +7625,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7749,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129291635</v>
+        <v>129291473</v>
       </c>
       <c r="B70" t="n">
-        <v>96039</v>
+        <v>98706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7760,34 +7759,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1079</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628573</v>
+        <v>628549</v>
       </c>
       <c r="R70" t="n">
-        <v>6978423</v>
+        <v>6978449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7846,42 +7849,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129297292</v>
+        <v>129290108</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7890,10 +7888,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628429</v>
+        <v>628447</v>
       </c>
       <c r="R71" t="n">
-        <v>6978625</v>
+        <v>6978522</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7952,10 +7950,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129291473</v>
+        <v>129302259</v>
       </c>
       <c r="B72" t="n">
-        <v>98705</v>
+        <v>91993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7963,38 +7961,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628549</v>
+        <v>628771</v>
       </c>
       <c r="R72" t="n">
-        <v>6978449</v>
+        <v>6978154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8053,49 +8047,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129290108</v>
+        <v>129302250</v>
       </c>
       <c r="B73" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628447</v>
+        <v>628495</v>
       </c>
       <c r="R73" t="n">
-        <v>6978522</v>
+        <v>6978647</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8128,6 +8118,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8154,32 +8149,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302259</v>
+        <v>129302244</v>
       </c>
       <c r="B74" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8189,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628771</v>
+        <v>628756</v>
       </c>
       <c r="R74" t="n">
-        <v>6978154</v>
+        <v>6978337</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,6 +8220,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8356,7 +8356,7 @@
         <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8562,45 +8562,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129290447</v>
+        <v>129295124</v>
       </c>
       <c r="B78" t="n">
-        <v>97576</v>
+        <v>91838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628494</v>
+        <v>628788</v>
       </c>
       <c r="R78" t="n">
-        <v>6978496</v>
+        <v>6978227</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8659,45 +8659,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129295124</v>
+        <v>129290447</v>
       </c>
       <c r="B79" t="n">
-        <v>91838</v>
+        <v>97577</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628788</v>
+        <v>628494</v>
       </c>
       <c r="R79" t="n">
-        <v>6978227</v>
+        <v>6978496</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8756,49 +8756,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302281</v>
+        <v>129302227</v>
       </c>
       <c r="B80" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628688</v>
+        <v>628851</v>
       </c>
       <c r="R80" t="n">
-        <v>6978441</v>
+        <v>6978504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8833,18 +8829,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8863,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302227</v>
+        <v>129302255</v>
       </c>
       <c r="B81" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8874,21 +8864,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8898,10 +8888,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628851</v>
+        <v>628712</v>
       </c>
       <c r="R81" t="n">
-        <v>6978504</v>
+        <v>6978376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8934,6 +8924,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8960,45 +8955,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302255</v>
+        <v>129302281</v>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>98706</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628712</v>
+        <v>628688</v>
       </c>
       <c r="R82" t="n">
-        <v>6978376</v>
+        <v>6978441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9035,7 +9034,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9044,6 +9043,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129296224</v>
+        <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9073,34 +9073,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>629061</v>
+        <v>628547</v>
       </c>
       <c r="R83" t="n">
-        <v>6978494</v>
+        <v>6978457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129291441</v>
+        <v>129296224</v>
       </c>
       <c r="B84" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9170,34 +9170,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>628547</v>
+        <v>629061</v>
       </c>
       <c r="R84" t="n">
-        <v>6978457</v>
+        <v>6978494</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9256,50 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129293914</v>
+        <v>129296097</v>
       </c>
       <c r="B85" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628690</v>
+        <v>628959</v>
       </c>
       <c r="R85" t="n">
-        <v>6978221</v>
+        <v>6978530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9358,32 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302291</v>
+        <v>129289873</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>91504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9393,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628794</v>
+        <v>628447</v>
       </c>
       <c r="R86" t="n">
-        <v>6978373</v>
+        <v>6978522</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9455,45 +9450,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129294276</v>
+        <v>129293914</v>
       </c>
       <c r="B87" t="n">
-        <v>91753</v>
+        <v>57887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628790</v>
+        <v>628690</v>
       </c>
       <c r="R87" t="n">
-        <v>6978034</v>
+        <v>6978221</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129292746</v>
+        <v>129293890</v>
       </c>
       <c r="B88" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,34 +9563,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628586</v>
+        <v>628691</v>
       </c>
       <c r="R88" t="n">
-        <v>6978451</v>
+        <v>6978242</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9623,6 +9628,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9649,45 +9659,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129290229</v>
+        <v>129294276</v>
       </c>
       <c r="B89" t="n">
-        <v>91838</v>
+        <v>91753</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628436</v>
+        <v>628790</v>
       </c>
       <c r="R89" t="n">
-        <v>6978498</v>
+        <v>6978034</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9746,32 +9756,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129296097</v>
+        <v>129292746</v>
       </c>
       <c r="B90" t="n">
-        <v>80175</v>
+        <v>91838</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9781,10 +9791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628959</v>
+        <v>628586</v>
       </c>
       <c r="R90" t="n">
-        <v>6978530</v>
+        <v>6978451</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,32 +9853,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129289873</v>
+        <v>129290229</v>
       </c>
       <c r="B91" t="n">
-        <v>91504</v>
+        <v>91838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9878,10 +9888,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628447</v>
+        <v>628436</v>
       </c>
       <c r="R91" t="n">
-        <v>6978522</v>
+        <v>6978498</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9940,50 +9950,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129293890</v>
+        <v>129302260</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628691</v>
+        <v>628641</v>
       </c>
       <c r="R92" t="n">
-        <v>6978242</v>
+        <v>6978450</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10016,11 +10021,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10047,32 +10047,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129302232</v>
+        <v>129302258</v>
       </c>
       <c r="B93" t="n">
-        <v>91540</v>
+        <v>91993</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10082,10 +10082,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628742</v>
+        <v>628851</v>
       </c>
       <c r="R93" t="n">
-        <v>6978216</v>
+        <v>6978502</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,10 +10144,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129302267</v>
+        <v>129302232</v>
       </c>
       <c r="B94" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10155,21 +10155,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628603</v>
+        <v>628742</v>
       </c>
       <c r="R94" t="n">
-        <v>6978502</v>
+        <v>6978216</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,7 +10241,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302264</v>
+        <v>129302267</v>
       </c>
       <c r="B95" t="n">
         <v>91838</v>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628796</v>
+        <v>628603</v>
       </c>
       <c r="R95" t="n">
-        <v>6978261</v>
+        <v>6978502</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302260</v>
+        <v>129302264</v>
       </c>
       <c r="B96" t="n">
-        <v>91993</v>
+        <v>91838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628641</v>
+        <v>628796</v>
       </c>
       <c r="R96" t="n">
-        <v>6978450</v>
+        <v>6978261</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,32 +10435,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129302258</v>
+        <v>129302291</v>
       </c>
       <c r="B97" t="n">
-        <v>91993</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628851</v>
+        <v>628794</v>
       </c>
       <c r="R97" t="n">
-        <v>6978502</v>
+        <v>6978373</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,54 +10532,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129295410</v>
+        <v>129293044</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628767</v>
+        <v>628662</v>
       </c>
       <c r="R98" t="n">
-        <v>6978383</v>
+        <v>6978408</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,49 +10633,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129293044</v>
+        <v>129295410</v>
       </c>
       <c r="B99" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628662</v>
+        <v>628767</v>
       </c>
       <c r="R99" t="n">
-        <v>6978408</v>
+        <v>6978383</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11030,10 +11030,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302282</v>
+        <v>129295651</v>
       </c>
       <c r="B103" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11058,17 +11058,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628654</v>
+        <v>628796</v>
       </c>
       <c r="R103" t="n">
-        <v>6978418</v>
+        <v>6978373</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11101,11 +11105,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11132,32 +11131,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302287</v>
+        <v>129302268</v>
       </c>
       <c r="B104" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11167,10 +11166,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628649</v>
+        <v>628719</v>
       </c>
       <c r="R104" t="n">
-        <v>6978449</v>
+        <v>6978594</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11203,11 +11202,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11234,32 +11228,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302268</v>
+        <v>129302282</v>
       </c>
       <c r="B105" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11269,10 +11263,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628719</v>
+        <v>628654</v>
       </c>
       <c r="R105" t="n">
-        <v>6978594</v>
+        <v>6978418</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,6 +11299,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,10 +11330,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129295651</v>
+        <v>129302287</v>
       </c>
       <c r="B106" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11359,21 +11358,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628796</v>
+        <v>628649</v>
       </c>
       <c r="R106" t="n">
-        <v>6978373</v>
+        <v>6978449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,6 +11401,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129289885</v>
+        <v>129293300</v>
       </c>
       <c r="B107" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,34 +11443,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628447</v>
+        <v>628665</v>
       </c>
       <c r="R107" t="n">
-        <v>6978522</v>
+        <v>6978376</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11503,6 +11508,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11626,10 +11636,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129293300</v>
+        <v>129289885</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11637,39 +11647,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628665</v>
+        <v>628447</v>
       </c>
       <c r="R109" t="n">
-        <v>6978376</v>
+        <v>6978522</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11702,11 +11707,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129293475</v>
+        <v>129302225</v>
       </c>
       <c r="B112" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628623</v>
+        <v>628856</v>
       </c>
       <c r="R112" t="n">
-        <v>6978341</v>
+        <v>6978527</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12034,10 +12034,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302225</v>
+        <v>129302247</v>
       </c>
       <c r="B113" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12045,21 +12045,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628856</v>
+        <v>628749</v>
       </c>
       <c r="R113" t="n">
-        <v>6978527</v>
+        <v>6978349</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12105,6 +12105,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12131,32 +12136,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302290</v>
+        <v>129302289</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>57719</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12166,10 +12171,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628712</v>
+        <v>628493</v>
       </c>
       <c r="R114" t="n">
-        <v>6978591</v>
+        <v>6978648</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,6 +12207,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12325,10 +12335,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129302247</v>
+        <v>129293475</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12336,21 +12346,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12360,10 +12370,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628749</v>
+        <v>628623</v>
       </c>
       <c r="R116" t="n">
-        <v>6978349</v>
+        <v>6978341</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12396,11 +12406,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12427,32 +12432,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302289</v>
+        <v>129302290</v>
       </c>
       <c r="B117" t="n">
-        <v>57719</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12462,10 +12467,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628493</v>
+        <v>628712</v>
       </c>
       <c r="R117" t="n">
-        <v>6978648</v>
+        <v>6978591</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12498,11 +12503,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12532,7 +12532,7 @@
         <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,32 +12631,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129295812</v>
+        <v>129294695</v>
       </c>
       <c r="B119" t="n">
-        <v>91540</v>
+        <v>91993</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628900</v>
+        <v>628831</v>
       </c>
       <c r="R119" t="n">
-        <v>6978416</v>
+        <v>6978180</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,54 +12728,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129293329</v>
+        <v>129297070</v>
       </c>
       <c r="B120" t="n">
-        <v>57724</v>
+        <v>91993</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628640</v>
+        <v>628764</v>
       </c>
       <c r="R120" t="n">
-        <v>6978364</v>
+        <v>6978591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12834,32 +12825,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129294695</v>
+        <v>129295812</v>
       </c>
       <c r="B121" t="n">
-        <v>91993</v>
+        <v>91540</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12869,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628831</v>
+        <v>628900</v>
       </c>
       <c r="R121" t="n">
-        <v>6978180</v>
+        <v>6978416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12931,32 +12922,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129297070</v>
+        <v>129302273</v>
       </c>
       <c r="B122" t="n">
-        <v>91993</v>
+        <v>80146</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12966,10 +12957,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628764</v>
+        <v>628878</v>
       </c>
       <c r="R122" t="n">
-        <v>6978591</v>
+        <v>6978535</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13028,10 +13019,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129302273</v>
+        <v>129293329</v>
       </c>
       <c r="B123" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13039,34 +13030,43 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628878</v>
+        <v>628640</v>
       </c>
       <c r="R123" t="n">
-        <v>6978535</v>
+        <v>6978364</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13125,32 +13125,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302242</v>
+        <v>129302257</v>
       </c>
       <c r="B124" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628750</v>
+        <v>628794</v>
       </c>
       <c r="R124" t="n">
-        <v>6978284</v>
+        <v>6978311</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13196,11 +13196,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13227,32 +13222,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302257</v>
+        <v>129302242</v>
       </c>
       <c r="B125" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13262,10 +13257,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628794</v>
+        <v>628750</v>
       </c>
       <c r="R125" t="n">
-        <v>6978311</v>
+        <v>6978284</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13298,6 +13293,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13421,10 +13421,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129289677</v>
+        <v>129290523</v>
       </c>
       <c r="B127" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13432,16 +13432,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13452,7 +13452,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13461,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628484</v>
+        <v>628509</v>
       </c>
       <c r="R127" t="n">
-        <v>6978568</v>
+        <v>6978510</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13497,6 +13497,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13523,49 +13528,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129291461</v>
+        <v>129302239</v>
       </c>
       <c r="B128" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628547</v>
+        <v>628747</v>
       </c>
       <c r="R128" t="n">
-        <v>6978457</v>
+        <v>6978218</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13598,6 +13599,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13624,32 +13630,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129290692</v>
+        <v>129302296</v>
       </c>
       <c r="B129" t="n">
-        <v>80106</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13659,10 +13665,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628515</v>
+        <v>628449</v>
       </c>
       <c r="R129" t="n">
-        <v>6978451</v>
+        <v>6978612</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13721,10 +13727,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129294090</v>
+        <v>129302270</v>
       </c>
       <c r="B130" t="n">
-        <v>80106</v>
+        <v>97577</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13732,34 +13738,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628743</v>
+        <v>628812</v>
       </c>
       <c r="R130" t="n">
-        <v>6978155</v>
+        <v>6978062</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13818,10 +13824,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129290523</v>
+        <v>129289677</v>
       </c>
       <c r="B131" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13829,16 +13835,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13849,7 +13855,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -13858,10 +13864,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628509</v>
+        <v>628484</v>
       </c>
       <c r="R131" t="n">
-        <v>6978510</v>
+        <v>6978568</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13894,11 +13900,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13925,45 +13926,49 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129302296</v>
+        <v>129291461</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628449</v>
+        <v>628547</v>
       </c>
       <c r="R132" t="n">
-        <v>6978612</v>
+        <v>6978457</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14022,32 +14027,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129302239</v>
+        <v>129290692</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14057,10 +14062,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628747</v>
+        <v>628515</v>
       </c>
       <c r="R133" t="n">
-        <v>6978218</v>
+        <v>6978451</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14093,11 +14098,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14124,10 +14124,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129302270</v>
+        <v>129294090</v>
       </c>
       <c r="B134" t="n">
-        <v>97576</v>
+        <v>80106</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14135,34 +14135,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628812</v>
+        <v>628743</v>
       </c>
       <c r="R134" t="n">
-        <v>6978062</v>
+        <v>6978155</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14221,10 +14221,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129294072</v>
+        <v>129302228</v>
       </c>
       <c r="B135" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14232,34 +14232,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628731</v>
+        <v>628870</v>
       </c>
       <c r="R135" t="n">
-        <v>6978165</v>
+        <v>6978469</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129293208</v>
+        <v>129294072</v>
       </c>
       <c r="B136" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,39 +14329,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628695</v>
+        <v>628731</v>
       </c>
       <c r="R136" t="n">
-        <v>6978356</v>
+        <v>6978165</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14394,11 +14389,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14425,7 +14415,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293275</v>
+        <v>129293208</v>
       </c>
       <c r="B137" t="n">
         <v>57727</v>
@@ -14465,10 +14455,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628693</v>
+        <v>628695</v>
       </c>
       <c r="R137" t="n">
-        <v>6978372</v>
+        <v>6978356</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14532,10 +14522,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129302228</v>
+        <v>129293275</v>
       </c>
       <c r="B138" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14543,34 +14533,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628870</v>
+        <v>628693</v>
       </c>
       <c r="R138" t="n">
-        <v>6978469</v>
+        <v>6978372</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14603,6 +14598,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14735,32 +14735,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129302266</v>
+        <v>129290695</v>
       </c>
       <c r="B140" t="n">
-        <v>91838</v>
+        <v>80182</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628639</v>
+        <v>628509</v>
       </c>
       <c r="R140" t="n">
-        <v>6978441</v>
+        <v>6978440</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14929,45 +14929,50 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129290695</v>
+        <v>129293977</v>
       </c>
       <c r="B142" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628509</v>
+        <v>628687</v>
       </c>
       <c r="R142" t="n">
-        <v>6978440</v>
+        <v>6978194</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15000,6 +15005,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15026,10 +15036,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129293977</v>
+        <v>129302266</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15037,39 +15047,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628687</v>
+        <v>628639</v>
       </c>
       <c r="R143" t="n">
-        <v>6978194</v>
+        <v>6978441</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15102,11 +15107,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15133,32 +15133,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129302288</v>
+        <v>129302272</v>
       </c>
       <c r="B144" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15168,10 +15168,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628636</v>
+        <v>628641</v>
       </c>
       <c r="R144" t="n">
-        <v>6978511</v>
+        <v>6978450</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15204,11 +15204,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15235,32 +15230,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129302272</v>
+        <v>129302288</v>
       </c>
       <c r="B145" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15270,10 +15265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628641</v>
+        <v>628636</v>
       </c>
       <c r="R145" t="n">
-        <v>6978450</v>
+        <v>6978511</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15306,6 +15301,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15332,45 +15332,49 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129295136</v>
+        <v>129290760</v>
       </c>
       <c r="B146" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628799</v>
+        <v>628499</v>
       </c>
       <c r="R146" t="n">
-        <v>6978234</v>
+        <v>6978448</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15429,32 +15433,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129295841</v>
+        <v>129302226</v>
       </c>
       <c r="B147" t="n">
-        <v>91753</v>
+        <v>91540</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15464,10 +15468,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628889</v>
+        <v>628849</v>
       </c>
       <c r="R147" t="n">
-        <v>6978417</v>
+        <v>6978507</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15526,10 +15530,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129295719</v>
+        <v>129302230</v>
       </c>
       <c r="B148" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15537,34 +15541,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628846</v>
+        <v>628766</v>
       </c>
       <c r="R148" t="n">
-        <v>6978364</v>
+        <v>6978195</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15623,49 +15627,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129290760</v>
+        <v>129302261</v>
       </c>
       <c r="B149" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628499</v>
+        <v>628794</v>
       </c>
       <c r="R149" t="n">
-        <v>6978448</v>
+        <v>6978311</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15724,10 +15724,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129295133</v>
+        <v>129302249</v>
       </c>
       <c r="B150" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15735,34 +15735,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628788</v>
+        <v>628539</v>
       </c>
       <c r="R150" t="n">
-        <v>6978227</v>
+        <v>6978526</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15795,6 +15795,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15821,10 +15826,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302292</v>
+        <v>129302238</v>
       </c>
       <c r="B151" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15832,21 +15837,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15856,10 +15861,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628819</v>
+        <v>628757</v>
       </c>
       <c r="R151" t="n">
-        <v>6978067</v>
+        <v>6978192</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15896,7 +15901,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15923,10 +15928,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302249</v>
+        <v>129295719</v>
       </c>
       <c r="B152" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15934,34 +15939,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628539</v>
+        <v>628846</v>
       </c>
       <c r="R152" t="n">
-        <v>6978526</v>
+        <v>6978364</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15994,11 +15999,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16025,10 +16025,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B153" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16036,34 +16036,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R153" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16122,32 +16122,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129302261</v>
+        <v>129295841</v>
       </c>
       <c r="B154" t="n">
-        <v>91838</v>
+        <v>91753</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16157,10 +16157,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628794</v>
+        <v>628889</v>
       </c>
       <c r="R154" t="n">
-        <v>6978311</v>
+        <v>6978417</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16219,7 +16219,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302226</v>
+        <v>129295133</v>
       </c>
       <c r="B155" t="n">
         <v>91540</v>
@@ -16250,14 +16250,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628849</v>
+        <v>628788</v>
       </c>
       <c r="R155" t="n">
-        <v>6978507</v>
+        <v>6978227</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16316,10 +16316,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302238</v>
+        <v>129302292</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16327,21 +16327,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628757</v>
+        <v>628819</v>
       </c>
       <c r="R156" t="n">
-        <v>6978192</v>
+        <v>6978067</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,32 +16418,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302285</v>
+        <v>129302297</v>
       </c>
       <c r="B157" t="n">
-        <v>98705</v>
+        <v>100895</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16453,10 +16453,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628656</v>
+        <v>628720</v>
       </c>
       <c r="R157" t="n">
-        <v>6978459</v>
+        <v>6978591</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,11 +16489,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16520,32 +16515,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302297</v>
+        <v>129302285</v>
       </c>
       <c r="B158" t="n">
-        <v>100894</v>
+        <v>98706</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16555,10 +16550,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628720</v>
+        <v>628656</v>
       </c>
       <c r="R158" t="n">
-        <v>6978591</v>
+        <v>6978459</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16591,6 +16586,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16617,45 +16617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129290278</v>
+        <v>129295735</v>
       </c>
       <c r="B159" t="n">
-        <v>91993</v>
+        <v>80181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628451</v>
+        <v>628841</v>
       </c>
       <c r="R159" t="n">
-        <v>6978495</v>
+        <v>6978384</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16714,27 +16714,27 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129295735</v>
+        <v>129289808</v>
       </c>
       <c r="B160" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -16745,14 +16745,14 @@
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628841</v>
+        <v>628421</v>
       </c>
       <c r="R160" t="n">
-        <v>6978384</v>
+        <v>6978541</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16811,32 +16811,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129289808</v>
+        <v>129290278</v>
       </c>
       <c r="B161" t="n">
-        <v>79041</v>
+        <v>91993</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16846,10 +16846,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628421</v>
+        <v>628451</v>
       </c>
       <c r="R161" t="n">
-        <v>6978541</v>
+        <v>6978495</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17105,7 +17105,7 @@
         <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>129181897</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>129184366</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129184816</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129185300</v>
       </c>
       <c r="B9" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129184595</v>
       </c>
       <c r="B10" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>129182054</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129295830</v>
+        <v>129292781</v>
       </c>
       <c r="B15" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628896</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6978430</v>
+        <v>6978436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295766</v>
+        <v>129295830</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>92261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,34 +2383,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628846</v>
+        <v>628896</v>
       </c>
       <c r="R16" t="n">
-        <v>6978364</v>
+        <v>6978430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129292781</v>
+        <v>129295766</v>
       </c>
       <c r="B17" t="n">
-        <v>92258</v>
+        <v>80177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,34 +2480,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628590</v>
+        <v>628846</v>
       </c>
       <c r="R17" t="n">
-        <v>6978436</v>
+        <v>6978364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,50 +2872,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294050</v>
+        <v>129302269</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>97581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628728</v>
+        <v>628792</v>
       </c>
       <c r="R21" t="n">
-        <v>6978173</v>
+        <v>6978309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,11 +2943,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129290628</v>
+        <v>129302243</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,21 +2980,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3014,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628499</v>
+        <v>628743</v>
       </c>
       <c r="R22" t="n">
-        <v>6978448</v>
+        <v>6978315</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,6 +3040,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129292558</v>
+        <v>129293584</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,38 +3082,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628589</v>
+        <v>628624</v>
       </c>
       <c r="R23" t="n">
-        <v>6978414</v>
+        <v>6978328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,10 +3168,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302262</v>
+        <v>129294036</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,14 +3199,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628800</v>
+        <v>628728</v>
       </c>
       <c r="R24" t="n">
-        <v>6978306</v>
+        <v>6978173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302265</v>
+        <v>129290628</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628772</v>
+        <v>628499</v>
       </c>
       <c r="R25" t="n">
-        <v>6978157</v>
+        <v>6978448</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,7 +3362,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302243</v>
+        <v>129294050</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3400,16 +3391,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628743</v>
+        <v>628728</v>
       </c>
       <c r="R26" t="n">
-        <v>6978315</v>
+        <v>6978173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3446,7 +3442,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,45 +3469,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302240</v>
+        <v>129292558</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628764</v>
+        <v>628589</v>
       </c>
       <c r="R27" t="n">
-        <v>6978279</v>
+        <v>6978414</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,11 +3544,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,32 +3570,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129293584</v>
+        <v>129302262</v>
       </c>
       <c r="B28" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3610,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628624</v>
+        <v>628800</v>
       </c>
       <c r="R28" t="n">
-        <v>6978328</v>
+        <v>6978306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294036</v>
+        <v>129302265</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3703,14 +3698,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628728</v>
+        <v>628772</v>
       </c>
       <c r="R29" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,32 +3764,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302269</v>
+        <v>129302240</v>
       </c>
       <c r="B30" t="n">
-        <v>97577</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3799,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628792</v>
+        <v>628764</v>
       </c>
       <c r="R30" t="n">
-        <v>6978309</v>
+        <v>6978279</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,6 +3835,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302278</v>
+        <v>129302284</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628894</v>
+        <v>628667</v>
       </c>
       <c r="R31" t="n">
-        <v>6978483</v>
+        <v>6978461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,10 +3968,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302284</v>
+        <v>129302278</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628667</v>
+        <v>628894</v>
       </c>
       <c r="R32" t="n">
-        <v>6978461</v>
+        <v>6978483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,45 +4070,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129302277</v>
+        <v>129295187</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628899</v>
+        <v>628834</v>
       </c>
       <c r="R33" t="n">
-        <v>6978480</v>
+        <v>6978251</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4141,11 +4141,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4172,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129296183</v>
+        <v>129290118</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,34 +4178,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>629055</v>
+        <v>628453</v>
       </c>
       <c r="R34" t="n">
-        <v>6978511</v>
+        <v>6978518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4269,54 +4264,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129293171</v>
+        <v>129294218</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>96044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628702</v>
+        <v>628798</v>
       </c>
       <c r="R35" t="n">
-        <v>6978339</v>
+        <v>6978072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4349,6 +4335,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4375,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129295187</v>
+        <v>129296183</v>
       </c>
       <c r="B36" t="n">
-        <v>91838</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4386,34 +4377,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628834</v>
+        <v>629055</v>
       </c>
       <c r="R36" t="n">
-        <v>6978251</v>
+        <v>6978511</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4472,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129290118</v>
+        <v>129293171</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,34 +4474,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628453</v>
+        <v>628702</v>
       </c>
       <c r="R37" t="n">
-        <v>6978518</v>
+        <v>6978339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,45 +4569,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294218</v>
+        <v>129302235</v>
       </c>
       <c r="B38" t="n">
-        <v>96040</v>
+        <v>91543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1079</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628798</v>
+        <v>628629</v>
       </c>
       <c r="R38" t="n">
-        <v>6978072</v>
+        <v>6978532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,11 +4640,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4671,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302235</v>
+        <v>129302293</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4682,21 +4677,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4706,10 +4701,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628629</v>
+        <v>628737</v>
       </c>
       <c r="R39" t="n">
-        <v>6978532</v>
+        <v>6978300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4768,32 +4763,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129302293</v>
+        <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4803,10 +4798,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>628737</v>
+        <v>628899</v>
       </c>
       <c r="R40" t="n">
-        <v>6978300</v>
+        <v>6978480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4839,6 +4834,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150, finns troligtvis mer i mossan</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4865,49 +4865,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290183</v>
+        <v>129294028</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628436</v>
+        <v>628728</v>
       </c>
       <c r="R41" t="n">
-        <v>6978498</v>
+        <v>6978173</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4966,54 +4962,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296072</v>
+        <v>129293533</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91996</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628971</v>
+        <v>628623</v>
       </c>
       <c r="R42" t="n">
-        <v>6978518</v>
+        <v>6978341</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5072,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129294028</v>
+        <v>129291502</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5083,34 +5070,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628728</v>
+        <v>628564</v>
       </c>
       <c r="R43" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5169,45 +5156,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293533</v>
+        <v>129296072</v>
       </c>
       <c r="B44" t="n">
-        <v>91993</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628623</v>
+        <v>628971</v>
       </c>
       <c r="R44" t="n">
-        <v>6978341</v>
+        <v>6978518</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5266,45 +5262,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129291502</v>
+        <v>129290183</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628564</v>
+        <v>628436</v>
       </c>
       <c r="R45" t="n">
-        <v>6978436</v>
+        <v>6978498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5468,7 +5468,7 @@
         <v>129296084</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290169</v>
+        <v>129302233</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,39 +5573,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628453</v>
+        <v>628759</v>
       </c>
       <c r="R48" t="n">
-        <v>6978518</v>
+        <v>6978233</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5638,11 +5633,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5669,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290361</v>
+        <v>129302231</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628465</v>
+        <v>628752</v>
       </c>
       <c r="R49" t="n">
-        <v>6978491</v>
+        <v>6978198</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,49 +5756,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290084</v>
+        <v>129290616</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628475</v>
+        <v>628499</v>
       </c>
       <c r="R50" t="n">
-        <v>6978540</v>
+        <v>6978448</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5867,10 +5853,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302233</v>
+        <v>129290361</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5902,10 +5888,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628759</v>
+        <v>628465</v>
       </c>
       <c r="R51" t="n">
-        <v>6978233</v>
+        <v>6978491</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,10 +5950,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302231</v>
+        <v>129290169</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5975,34 +5961,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628752</v>
+        <v>628453</v>
       </c>
       <c r="R52" t="n">
-        <v>6978198</v>
+        <v>6978518</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6035,6 +6026,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,45 +6057,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129290616</v>
+        <v>129290084</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628499</v>
+        <v>628475</v>
       </c>
       <c r="R53" t="n">
-        <v>6978448</v>
+        <v>6978540</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6158,32 +6158,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129302276</v>
+        <v>129302294</v>
       </c>
       <c r="B54" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628648</v>
+        <v>628661</v>
       </c>
       <c r="R54" t="n">
-        <v>6978420</v>
+        <v>6978421</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6229,11 +6229,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6263,7 +6258,7 @@
         <v>129302275</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6362,32 +6357,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302294</v>
+        <v>129302276</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6392,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628661</v>
+        <v>628648</v>
       </c>
       <c r="R56" t="n">
-        <v>6978421</v>
+        <v>6978420</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6433,6 +6428,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6459,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129294015</v>
+        <v>129295935</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>91557</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6470,34 +6470,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628728</v>
+        <v>628907</v>
       </c>
       <c r="R57" t="n">
-        <v>6978173</v>
+        <v>6978423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129295935</v>
+        <v>129302274</v>
       </c>
       <c r="B58" t="n">
-        <v>91554</v>
+        <v>80148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6567,21 +6567,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628907</v>
+        <v>628659</v>
       </c>
       <c r="R58" t="n">
-        <v>6978423</v>
+        <v>6978419</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,54 +6653,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B59" t="n">
-        <v>57719</v>
+        <v>80148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R59" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6759,45 +6750,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302229</v>
+        <v>129293780</v>
       </c>
       <c r="B60" t="n">
-        <v>91540</v>
+        <v>57719</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628761</v>
+        <v>628680</v>
       </c>
       <c r="R60" t="n">
-        <v>6978157</v>
+        <v>6978235</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302274</v>
+        <v>129302229</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628659</v>
+        <v>628761</v>
       </c>
       <c r="R61" t="n">
-        <v>6978419</v>
+        <v>6978157</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7160,7 +7160,7 @@
         <v>129302271</v>
       </c>
       <c r="B64" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7254,54 +7254,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129297292</v>
+        <v>129295162</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91996</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628429</v>
+        <v>628834</v>
       </c>
       <c r="R65" t="n">
-        <v>6978625</v>
+        <v>6978251</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,10 +7351,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129295162</v>
+        <v>129292729</v>
       </c>
       <c r="B66" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7391,14 +7382,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628834</v>
+        <v>628599</v>
       </c>
       <c r="R66" t="n">
-        <v>6978251</v>
+        <v>6978448</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7457,10 +7448,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129292729</v>
+        <v>129291635</v>
       </c>
       <c r="B67" t="n">
-        <v>91993</v>
+        <v>96044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7468,21 +7459,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>1079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7492,10 +7483,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628599</v>
+        <v>628573</v>
       </c>
       <c r="R67" t="n">
-        <v>6978448</v>
+        <v>6978423</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7554,32 +7545,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129291635</v>
+        <v>129294000</v>
       </c>
       <c r="B68" t="n">
-        <v>96040</v>
+        <v>91543</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1079</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7589,10 +7580,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628573</v>
+        <v>628687</v>
       </c>
       <c r="R68" t="n">
-        <v>6978423</v>
+        <v>6978194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7651,10 +7642,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129294000</v>
+        <v>129297292</v>
       </c>
       <c r="B69" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7662,34 +7653,43 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628687</v>
+        <v>628429</v>
       </c>
       <c r="R69" t="n">
-        <v>6978194</v>
+        <v>6978625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129291473</v>
+        <v>129302259</v>
       </c>
       <c r="B70" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7759,38 +7759,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628549</v>
+        <v>628771</v>
       </c>
       <c r="R70" t="n">
-        <v>6978449</v>
+        <v>6978154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7849,49 +7845,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129290108</v>
+        <v>129302254</v>
       </c>
       <c r="B71" t="n">
-        <v>98706</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628447</v>
+        <v>628894</v>
       </c>
       <c r="R71" t="n">
-        <v>6978522</v>
+        <v>6978096</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7924,6 +7916,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7950,10 +7947,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302259</v>
+        <v>129291473</v>
       </c>
       <c r="B72" t="n">
-        <v>91993</v>
+        <v>98710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7961,34 +7958,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628771</v>
+        <v>628549</v>
       </c>
       <c r="R72" t="n">
-        <v>6978154</v>
+        <v>6978449</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8047,45 +8048,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302250</v>
+        <v>129290108</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628495</v>
+        <v>628447</v>
       </c>
       <c r="R73" t="n">
-        <v>6978647</v>
+        <v>6978522</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,11 +8123,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8149,7 +8149,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302244</v>
+        <v>129302250</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628756</v>
+        <v>628495</v>
       </c>
       <c r="R74" t="n">
-        <v>6978337</v>
+        <v>6978647</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302254</v>
+        <v>129302244</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628894</v>
+        <v>628756</v>
       </c>
       <c r="R75" t="n">
-        <v>6978096</v>
+        <v>6978337</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8356,7 +8356,7 @@
         <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8455,10 +8455,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129289501</v>
+        <v>129302227</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8466,39 +8466,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628451</v>
+        <v>628851</v>
       </c>
       <c r="R77" t="n">
-        <v>6978596</v>
+        <v>6978504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8531,11 +8526,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8565,7 +8555,7 @@
         <v>129295124</v>
       </c>
       <c r="B78" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8659,45 +8649,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129290447</v>
+        <v>129289501</v>
       </c>
       <c r="B79" t="n">
-        <v>97577</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628494</v>
+        <v>628451</v>
       </c>
       <c r="R79" t="n">
-        <v>6978496</v>
+        <v>6978596</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,6 +8725,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8756,32 +8756,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302227</v>
+        <v>129290447</v>
       </c>
       <c r="B80" t="n">
-        <v>91540</v>
+        <v>97581</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628851</v>
+        <v>628494</v>
       </c>
       <c r="R80" t="n">
-        <v>6978504</v>
+        <v>6978496</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8958,7 +8958,7 @@
         <v>129302281</v>
       </c>
       <c r="B82" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>129296224</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129296097</v>
+        <v>129302267</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>91841</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628959</v>
+        <v>628603</v>
       </c>
       <c r="R85" t="n">
-        <v>6978530</v>
+        <v>6978502</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,32 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129289873</v>
+        <v>129302232</v>
       </c>
       <c r="B86" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628447</v>
+        <v>628742</v>
       </c>
       <c r="R86" t="n">
-        <v>6978522</v>
+        <v>6978216</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129293914</v>
+        <v>129302264</v>
       </c>
       <c r="B87" t="n">
-        <v>57887</v>
+        <v>91841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9461,39 +9461,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628690</v>
+        <v>628796</v>
       </c>
       <c r="R87" t="n">
-        <v>6978221</v>
+        <v>6978261</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9552,50 +9547,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129293890</v>
+        <v>129302260</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>91996</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628691</v>
+        <v>628641</v>
       </c>
       <c r="R88" t="n">
-        <v>6978242</v>
+        <v>6978450</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9628,11 +9618,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9659,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129294276</v>
+        <v>129302258</v>
       </c>
       <c r="B89" t="n">
-        <v>91753</v>
+        <v>91996</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,34 +9655,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>48</v>
+        <v>1209</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628790</v>
+        <v>628851</v>
       </c>
       <c r="R89" t="n">
-        <v>6978034</v>
+        <v>6978502</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9756,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129292746</v>
+        <v>129302291</v>
       </c>
       <c r="B90" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9767,21 +9752,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9791,10 +9776,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628586</v>
+        <v>628794</v>
       </c>
       <c r="R90" t="n">
-        <v>6978451</v>
+        <v>6978373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9853,10 +9838,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129290229</v>
+        <v>129293890</v>
       </c>
       <c r="B91" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9864,34 +9849,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628436</v>
+        <v>628691</v>
       </c>
       <c r="R91" t="n">
-        <v>6978498</v>
+        <v>6978242</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9924,6 +9914,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9950,10 +9945,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129302260</v>
+        <v>129294276</v>
       </c>
       <c r="B92" t="n">
-        <v>91993</v>
+        <v>91756</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9961,34 +9956,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628641</v>
+        <v>628790</v>
       </c>
       <c r="R92" t="n">
-        <v>6978450</v>
+        <v>6978034</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,32 +10042,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129302258</v>
+        <v>129292746</v>
       </c>
       <c r="B93" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10082,10 +10077,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628851</v>
+        <v>628586</v>
       </c>
       <c r="R93" t="n">
-        <v>6978502</v>
+        <v>6978451</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,10 +10139,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129302232</v>
+        <v>129290229</v>
       </c>
       <c r="B94" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10155,21 +10150,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10179,10 +10174,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628742</v>
+        <v>628436</v>
       </c>
       <c r="R94" t="n">
-        <v>6978216</v>
+        <v>6978498</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,32 +10236,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302267</v>
+        <v>129289873</v>
       </c>
       <c r="B95" t="n">
-        <v>91838</v>
+        <v>91507</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10271,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628603</v>
+        <v>628447</v>
       </c>
       <c r="R95" t="n">
-        <v>6978502</v>
+        <v>6978522</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10333,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302264</v>
+        <v>129296097</v>
       </c>
       <c r="B96" t="n">
-        <v>91838</v>
+        <v>80177</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10368,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628796</v>
+        <v>628959</v>
       </c>
       <c r="R96" t="n">
-        <v>6978261</v>
+        <v>6978530</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,10 +10430,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129302291</v>
+        <v>129293914</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10446,34 +10441,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628794</v>
+        <v>628690</v>
       </c>
       <c r="R97" t="n">
-        <v>6978373</v>
+        <v>6978221</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,49 +10532,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129293044</v>
+        <v>129295410</v>
       </c>
       <c r="B98" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628662</v>
+        <v>628767</v>
       </c>
       <c r="R98" t="n">
-        <v>6978408</v>
+        <v>6978383</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10633,54 +10638,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129295410</v>
+        <v>129293044</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628767</v>
+        <v>628662</v>
       </c>
       <c r="R99" t="n">
-        <v>6978383</v>
+        <v>6978408</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10742,7 +10742,7 @@
         <v>129302295</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>129295020</v>
       </c>
       <c r="B101" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10933,32 +10933,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302263</v>
+        <v>129302282</v>
       </c>
       <c r="B102" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10968,10 +10968,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628810</v>
+        <v>628654</v>
       </c>
       <c r="R102" t="n">
-        <v>6978299</v>
+        <v>6978418</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11004,6 +11004,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11030,10 +11035,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129295651</v>
+        <v>129302287</v>
       </c>
       <c r="B103" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11058,21 +11063,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628796</v>
+        <v>628649</v>
       </c>
       <c r="R103" t="n">
-        <v>6978373</v>
+        <v>6978449</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11105,6 +11106,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11131,45 +11137,49 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302268</v>
+        <v>129295651</v>
       </c>
       <c r="B104" t="n">
-        <v>97577</v>
+        <v>98710</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628719</v>
+        <v>628796</v>
       </c>
       <c r="R104" t="n">
-        <v>6978594</v>
+        <v>6978373</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11228,32 +11238,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302282</v>
+        <v>129302263</v>
       </c>
       <c r="B105" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11263,10 +11273,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628654</v>
+        <v>628810</v>
       </c>
       <c r="R105" t="n">
-        <v>6978418</v>
+        <v>6978299</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11299,11 +11309,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11330,32 +11335,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302287</v>
+        <v>129302268</v>
       </c>
       <c r="B106" t="n">
-        <v>98706</v>
+        <v>97581</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11365,10 +11370,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628649</v>
+        <v>628719</v>
       </c>
       <c r="R106" t="n">
-        <v>6978449</v>
+        <v>6978594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11401,11 +11406,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129293300</v>
+        <v>129293395</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,39 +11443,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628665</v>
+        <v>628616</v>
       </c>
       <c r="R107" t="n">
-        <v>6978376</v>
+        <v>6978368</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11508,11 +11503,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11539,10 +11529,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129293395</v>
+        <v>129289885</v>
       </c>
       <c r="B108" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11574,10 +11564,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628616</v>
+        <v>628447</v>
       </c>
       <c r="R108" t="n">
-        <v>6978368</v>
+        <v>6978522</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11636,10 +11626,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129289885</v>
+        <v>129293300</v>
       </c>
       <c r="B109" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11647,34 +11637,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628447</v>
+        <v>628665</v>
       </c>
       <c r="R109" t="n">
-        <v>6978522</v>
+        <v>6978376</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,6 +11702,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11937,32 +11937,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302225</v>
+        <v>129302289</v>
       </c>
       <c r="B112" t="n">
-        <v>91540</v>
+        <v>57719</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628856</v>
+        <v>628493</v>
       </c>
       <c r="R112" t="n">
-        <v>6978527</v>
+        <v>6978648</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,6 +12008,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12034,32 +12039,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302247</v>
+        <v>129302256</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>98627</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12069,10 +12074,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628749</v>
+        <v>628658</v>
       </c>
       <c r="R113" t="n">
-        <v>6978349</v>
+        <v>6978439</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12109,7 +12114,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12136,32 +12141,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302289</v>
+        <v>129295820</v>
       </c>
       <c r="B114" t="n">
-        <v>57719</v>
+        <v>91996</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100110</v>
+        <v>1209</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12171,10 +12176,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628493</v>
+        <v>628889</v>
       </c>
       <c r="R114" t="n">
-        <v>6978648</v>
+        <v>6978417</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12207,11 +12212,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12238,32 +12238,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129295820</v>
+        <v>129293475</v>
       </c>
       <c r="B115" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12273,10 +12273,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628889</v>
+        <v>628623</v>
       </c>
       <c r="R115" t="n">
-        <v>6978417</v>
+        <v>6978341</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12335,10 +12335,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129293475</v>
+        <v>129302225</v>
       </c>
       <c r="B116" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12346,21 +12346,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12370,10 +12370,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628623</v>
+        <v>628856</v>
       </c>
       <c r="R116" t="n">
-        <v>6978341</v>
+        <v>6978527</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12435,7 +12435,7 @@
         <v>129302290</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12529,32 +12529,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129302256</v>
+        <v>129302247</v>
       </c>
       <c r="B118" t="n">
-        <v>98623</v>
+        <v>57727</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12564,10 +12564,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628658</v>
+        <v>628749</v>
       </c>
       <c r="R118" t="n">
-        <v>6978439</v>
+        <v>6978349</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>2 exemplar. Gamla blomstänger.</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12631,45 +12631,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129294695</v>
+        <v>129293329</v>
       </c>
       <c r="B119" t="n">
-        <v>91993</v>
+        <v>57724</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628831</v>
+        <v>628640</v>
       </c>
       <c r="R119" t="n">
-        <v>6978180</v>
+        <v>6978364</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,10 +12737,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129297070</v>
+        <v>129294695</v>
       </c>
       <c r="B120" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12759,14 +12768,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628764</v>
+        <v>628831</v>
       </c>
       <c r="R120" t="n">
-        <v>6978591</v>
+        <v>6978180</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,45 +12834,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129295812</v>
+        <v>129297070</v>
       </c>
       <c r="B121" t="n">
-        <v>91540</v>
+        <v>91996</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628900</v>
+        <v>628764</v>
       </c>
       <c r="R121" t="n">
-        <v>6978416</v>
+        <v>6978591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12922,10 +12931,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129302273</v>
+        <v>129295812</v>
       </c>
       <c r="B122" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12933,34 +12942,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628878</v>
+        <v>628900</v>
       </c>
       <c r="R122" t="n">
-        <v>6978535</v>
+        <v>6978416</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13019,54 +13028,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129293329</v>
+        <v>129302257</v>
       </c>
       <c r="B123" t="n">
-        <v>57724</v>
+        <v>91996</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628640</v>
+        <v>628794</v>
       </c>
       <c r="R123" t="n">
-        <v>6978364</v>
+        <v>6978311</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13125,32 +13125,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302257</v>
+        <v>129302273</v>
       </c>
       <c r="B124" t="n">
-        <v>91993</v>
+        <v>80148</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13160,10 +13160,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628794</v>
+        <v>628878</v>
       </c>
       <c r="R124" t="n">
-        <v>6978311</v>
+        <v>6978535</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13324,10 +13324,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129291548</v>
+        <v>129302270</v>
       </c>
       <c r="B126" t="n">
-        <v>80050</v>
+        <v>97581</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628549</v>
+        <v>628812</v>
       </c>
       <c r="R126" t="n">
-        <v>6978433</v>
+        <v>6978062</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13421,10 +13421,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129290523</v>
+        <v>129289677</v>
       </c>
       <c r="B127" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13432,16 +13432,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13452,7 +13452,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13461,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628509</v>
+        <v>628484</v>
       </c>
       <c r="R127" t="n">
-        <v>6978510</v>
+        <v>6978568</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13497,11 +13497,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13528,10 +13523,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129302239</v>
+        <v>129302296</v>
       </c>
       <c r="B128" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13539,21 +13534,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13563,10 +13558,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628747</v>
+        <v>628449</v>
       </c>
       <c r="R128" t="n">
-        <v>6978218</v>
+        <v>6978612</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13599,11 +13594,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13630,10 +13620,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129302296</v>
+        <v>129302239</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13641,21 +13631,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13665,10 +13655,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628449</v>
+        <v>628747</v>
       </c>
       <c r="R129" t="n">
-        <v>6978612</v>
+        <v>6978218</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13701,6 +13691,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13727,10 +13722,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129302270</v>
+        <v>129291548</v>
       </c>
       <c r="B130" t="n">
-        <v>97577</v>
+        <v>80052</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13738,21 +13733,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13762,10 +13757,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628812</v>
+        <v>628549</v>
       </c>
       <c r="R130" t="n">
-        <v>6978062</v>
+        <v>6978433</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13824,10 +13819,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129289677</v>
+        <v>129290523</v>
       </c>
       <c r="B131" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13835,16 +13830,16 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13855,7 +13850,7 @@
       <c r="I131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -13864,10 +13859,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628484</v>
+        <v>628509</v>
       </c>
       <c r="R131" t="n">
-        <v>6978568</v>
+        <v>6978510</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13900,6 +13895,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13926,49 +13926,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129291461</v>
+        <v>129290692</v>
       </c>
       <c r="B132" t="n">
-        <v>98706</v>
+        <v>80108</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628547</v>
+        <v>628515</v>
       </c>
       <c r="R132" t="n">
-        <v>6978457</v>
+        <v>6978451</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14027,10 +14023,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129290692</v>
+        <v>129294090</v>
       </c>
       <c r="B133" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14058,14 +14054,14 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628515</v>
+        <v>628743</v>
       </c>
       <c r="R133" t="n">
-        <v>6978451</v>
+        <v>6978155</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14124,45 +14120,49 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129294090</v>
+        <v>129291461</v>
       </c>
       <c r="B134" t="n">
-        <v>80106</v>
+        <v>98710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628743</v>
+        <v>628547</v>
       </c>
       <c r="R134" t="n">
-        <v>6978155</v>
+        <v>6978457</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14221,10 +14221,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129302228</v>
+        <v>129294072</v>
       </c>
       <c r="B135" t="n">
-        <v>91540</v>
+        <v>80148</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14232,34 +14232,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628870</v>
+        <v>628731</v>
       </c>
       <c r="R135" t="n">
-        <v>6978469</v>
+        <v>6978165</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129294072</v>
+        <v>129295655</v>
       </c>
       <c r="B136" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,34 +14329,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628731</v>
+        <v>628796</v>
       </c>
       <c r="R136" t="n">
-        <v>6978165</v>
+        <v>6978373</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14415,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293208</v>
+        <v>129302228</v>
       </c>
       <c r="B137" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14426,39 +14435,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628695</v>
+        <v>628870</v>
       </c>
       <c r="R137" t="n">
-        <v>6978356</v>
+        <v>6978469</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14491,11 +14495,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14522,7 +14521,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293275</v>
+        <v>129293208</v>
       </c>
       <c r="B138" t="n">
         <v>57727</v>
@@ -14562,10 +14561,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628693</v>
+        <v>628695</v>
       </c>
       <c r="R138" t="n">
-        <v>6978372</v>
+        <v>6978356</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14629,10 +14628,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129295655</v>
+        <v>129293275</v>
       </c>
       <c r="B139" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14640,16 +14639,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -14657,26 +14656,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628796</v>
+        <v>628693</v>
       </c>
       <c r="R139" t="n">
-        <v>6978373</v>
+        <v>6978372</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14709,6 +14704,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14735,45 +14735,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129290695</v>
+        <v>129293977</v>
       </c>
       <c r="B140" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628509</v>
+        <v>628687</v>
       </c>
       <c r="R140" t="n">
-        <v>6978440</v>
+        <v>6978194</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14806,6 +14811,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14832,10 +14842,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129291606</v>
+        <v>129302266</v>
       </c>
       <c r="B141" t="n">
-        <v>80146</v>
+        <v>91841</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14843,21 +14853,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14867,10 +14877,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628564</v>
+        <v>628639</v>
       </c>
       <c r="R141" t="n">
-        <v>6978436</v>
+        <v>6978441</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14929,50 +14939,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129293977</v>
+        <v>129302272</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>97581</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628687</v>
+        <v>628641</v>
       </c>
       <c r="R142" t="n">
-        <v>6978194</v>
+        <v>6978450</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15005,11 +15010,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15036,32 +15036,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129302266</v>
+        <v>129290695</v>
       </c>
       <c r="B143" t="n">
-        <v>91838</v>
+        <v>80184</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15071,10 +15071,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628639</v>
+        <v>628509</v>
       </c>
       <c r="R143" t="n">
-        <v>6978441</v>
+        <v>6978440</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15133,32 +15133,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129302272</v>
+        <v>129291606</v>
       </c>
       <c r="B144" t="n">
-        <v>97577</v>
+        <v>80148</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15168,10 +15168,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628641</v>
+        <v>628564</v>
       </c>
       <c r="R144" t="n">
-        <v>6978450</v>
+        <v>6978436</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15233,7 +15233,7 @@
         <v>129302288</v>
       </c>
       <c r="B145" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15332,10 +15332,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129290760</v>
+        <v>129295841</v>
       </c>
       <c r="B146" t="n">
-        <v>98706</v>
+        <v>91756</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15343,38 +15343,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628499</v>
+        <v>628889</v>
       </c>
       <c r="R146" t="n">
-        <v>6978448</v>
+        <v>6978417</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15433,45 +15429,49 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302226</v>
+        <v>129290760</v>
       </c>
       <c r="B147" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628849</v>
+        <v>628499</v>
       </c>
       <c r="R147" t="n">
-        <v>6978507</v>
+        <v>6978448</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15530,10 +15530,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B148" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15541,34 +15541,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R148" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15627,10 +15627,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129302261</v>
+        <v>129295133</v>
       </c>
       <c r="B149" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15638,34 +15638,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628794</v>
+        <v>628788</v>
       </c>
       <c r="R149" t="n">
-        <v>6978311</v>
+        <v>6978227</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15724,10 +15724,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129302249</v>
+        <v>129295719</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15735,34 +15735,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628539</v>
+        <v>628846</v>
       </c>
       <c r="R150" t="n">
-        <v>6978526</v>
+        <v>6978364</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15795,11 +15795,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15826,10 +15821,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302238</v>
+        <v>129302226</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15837,21 +15832,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15861,10 +15856,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628757</v>
+        <v>628849</v>
       </c>
       <c r="R151" t="n">
-        <v>6978192</v>
+        <v>6978507</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15897,11 +15892,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15928,10 +15918,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129295719</v>
+        <v>129302230</v>
       </c>
       <c r="B152" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15939,34 +15929,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628846</v>
+        <v>628766</v>
       </c>
       <c r="R152" t="n">
-        <v>6978364</v>
+        <v>6978195</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16025,10 +16015,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129295136</v>
+        <v>129302261</v>
       </c>
       <c r="B153" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16056,14 +16046,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628799</v>
+        <v>628794</v>
       </c>
       <c r="R153" t="n">
-        <v>6978234</v>
+        <v>6978311</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16122,32 +16112,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129295841</v>
+        <v>129302292</v>
       </c>
       <c r="B154" t="n">
-        <v>91753</v>
+        <v>79043</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16157,10 +16147,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628889</v>
+        <v>628819</v>
       </c>
       <c r="R154" t="n">
-        <v>6978417</v>
+        <v>6978067</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16193,6 +16183,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16219,10 +16214,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129295133</v>
+        <v>129302249</v>
       </c>
       <c r="B155" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16230,34 +16225,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628788</v>
+        <v>628539</v>
       </c>
       <c r="R155" t="n">
-        <v>6978227</v>
+        <v>6978526</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16290,6 +16285,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16316,10 +16316,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302292</v>
+        <v>129302238</v>
       </c>
       <c r="B156" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16327,21 +16327,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628819</v>
+        <v>628757</v>
       </c>
       <c r="R156" t="n">
-        <v>6978067</v>
+        <v>6978192</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,32 +16418,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302297</v>
+        <v>129302285</v>
       </c>
       <c r="B157" t="n">
-        <v>100895</v>
+        <v>98710</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16453,10 +16453,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628720</v>
+        <v>628656</v>
       </c>
       <c r="R157" t="n">
-        <v>6978591</v>
+        <v>6978459</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,6 +16489,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16515,32 +16520,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302285</v>
+        <v>129302297</v>
       </c>
       <c r="B158" t="n">
-        <v>98706</v>
+        <v>100899</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16550,10 +16555,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628656</v>
+        <v>628720</v>
       </c>
       <c r="R158" t="n">
-        <v>6978459</v>
+        <v>6978591</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16586,11 +16591,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16617,45 +16617,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129295735</v>
+        <v>129302253</v>
       </c>
       <c r="B159" t="n">
-        <v>80181</v>
+        <v>57887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628841</v>
+        <v>628759</v>
       </c>
       <c r="R159" t="n">
-        <v>6978384</v>
+        <v>6978235</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16714,32 +16714,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129289808</v>
+        <v>129302279</v>
       </c>
       <c r="B160" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628421</v>
+        <v>628884</v>
       </c>
       <c r="R160" t="n">
-        <v>6978541</v>
+        <v>6978488</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16785,6 +16785,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16814,7 +16819,7 @@
         <v>129290278</v>
       </c>
       <c r="B161" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16908,10 +16913,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129302234</v>
+        <v>129289808</v>
       </c>
       <c r="B162" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16919,21 +16924,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16943,10 +16948,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628641</v>
+        <v>628421</v>
       </c>
       <c r="R162" t="n">
-        <v>6978450</v>
+        <v>6978541</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17005,45 +17010,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129302253</v>
+        <v>129295735</v>
       </c>
       <c r="B163" t="n">
-        <v>57887</v>
+        <v>80183</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628759</v>
+        <v>628841</v>
       </c>
       <c r="R163" t="n">
-        <v>6978235</v>
+        <v>6978384</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17102,32 +17107,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129302279</v>
+        <v>129302234</v>
       </c>
       <c r="B164" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17137,10 +17142,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628884</v>
+        <v>628641</v>
       </c>
       <c r="R164" t="n">
-        <v>6978488</v>
+        <v>6978450</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17173,11 +17178,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2872,45 +2872,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302269</v>
+        <v>129294050</v>
       </c>
       <c r="B21" t="n">
-        <v>97581</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628792</v>
+        <v>628728</v>
       </c>
       <c r="R21" t="n">
-        <v>6978309</v>
+        <v>6978173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,6 +2948,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,45 +2979,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302243</v>
+        <v>129292558</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628743</v>
+        <v>628589</v>
       </c>
       <c r="R22" t="n">
-        <v>6978315</v>
+        <v>6978414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,11 +3054,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,32 +3080,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129293584</v>
+        <v>129302262</v>
       </c>
       <c r="B23" t="n">
-        <v>91996</v>
+        <v>91841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628624</v>
+        <v>628800</v>
       </c>
       <c r="R23" t="n">
-        <v>6978328</v>
+        <v>6978306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3177,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294036</v>
+        <v>129302265</v>
       </c>
       <c r="B24" t="n">
         <v>91841</v>
@@ -3199,14 +3208,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628728</v>
+        <v>628772</v>
       </c>
       <c r="R24" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3265,10 +3274,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129290628</v>
+        <v>129302243</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +3285,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628499</v>
+        <v>628743</v>
       </c>
       <c r="R25" t="n">
-        <v>6978448</v>
+        <v>6978315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,6 +3345,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294050</v>
+        <v>129302240</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3391,21 +3405,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628728</v>
+        <v>628764</v>
       </c>
       <c r="R26" t="n">
-        <v>6978173</v>
+        <v>6978279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3442,7 +3451,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,7 +3478,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129292558</v>
+        <v>129302284</v>
       </c>
       <c r="B27" t="n">
         <v>98710</v>
@@ -3497,21 +3506,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628589</v>
+        <v>628667</v>
       </c>
       <c r="R27" t="n">
-        <v>6978414</v>
+        <v>6978461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3544,6 +3549,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3570,32 +3580,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302262</v>
+        <v>129302278</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3605,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628800</v>
+        <v>628894</v>
       </c>
       <c r="R28" t="n">
-        <v>6978306</v>
+        <v>6978483</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,6 +3651,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3667,32 +3682,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302265</v>
+        <v>129293584</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>91996</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3702,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628772</v>
+        <v>628624</v>
       </c>
       <c r="R29" t="n">
-        <v>6978157</v>
+        <v>6978328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3764,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302240</v>
+        <v>129294036</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3775,34 +3790,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628764</v>
+        <v>628728</v>
       </c>
       <c r="R30" t="n">
-        <v>6978279</v>
+        <v>6978173</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3835,11 +3850,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,32 +3876,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302284</v>
+        <v>129290628</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3911,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628667</v>
+        <v>628499</v>
       </c>
       <c r="R31" t="n">
-        <v>6978461</v>
+        <v>6978448</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,11 +3947,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302278</v>
+        <v>129302269</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>97581</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4003,10 +4008,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628894</v>
+        <v>628792</v>
       </c>
       <c r="R32" t="n">
-        <v>6978483</v>
+        <v>6978309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,11 +4044,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4569,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302235</v>
+        <v>129302293</v>
       </c>
       <c r="B38" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628629</v>
+        <v>628737</v>
       </c>
       <c r="R38" t="n">
-        <v>6978532</v>
+        <v>6978300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302293</v>
+        <v>129302235</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>91543</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628737</v>
+        <v>628629</v>
       </c>
       <c r="R39" t="n">
-        <v>6978300</v>
+        <v>6978532</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129302233</v>
+        <v>129290169</v>
       </c>
       <c r="B48" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,34 +5573,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628759</v>
+        <v>628453</v>
       </c>
       <c r="R48" t="n">
-        <v>6978233</v>
+        <v>6978518</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,6 +5638,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5669,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129302231</v>
+        <v>129302233</v>
       </c>
       <c r="B49" t="n">
         <v>91543</v>
@@ -5694,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628752</v>
+        <v>628759</v>
       </c>
       <c r="R49" t="n">
-        <v>6978198</v>
+        <v>6978233</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,7 +5766,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290616</v>
+        <v>129302231</v>
       </c>
       <c r="B50" t="n">
         <v>91543</v>
@@ -5791,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628499</v>
+        <v>628752</v>
       </c>
       <c r="R50" t="n">
-        <v>6978448</v>
+        <v>6978198</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5853,7 +5863,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290361</v>
+        <v>129290616</v>
       </c>
       <c r="B51" t="n">
         <v>91543</v>
@@ -5888,10 +5898,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628465</v>
+        <v>628499</v>
       </c>
       <c r="R51" t="n">
-        <v>6978491</v>
+        <v>6978448</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5950,10 +5960,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129290169</v>
+        <v>129290361</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5961,39 +5971,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628453</v>
+        <v>628465</v>
       </c>
       <c r="R52" t="n">
-        <v>6978518</v>
+        <v>6978491</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6026,11 +6031,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6556,7 +6556,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129302274</v>
+        <v>129294015</v>
       </c>
       <c r="B58" t="n">
         <v>80148</v>
@@ -6587,14 +6587,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628659</v>
+        <v>628728</v>
       </c>
       <c r="R58" t="n">
-        <v>6978419</v>
+        <v>6978173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,45 +6653,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129294015</v>
+        <v>129293780</v>
       </c>
       <c r="B59" t="n">
-        <v>80148</v>
+        <v>57719</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628728</v>
+        <v>628680</v>
       </c>
       <c r="R59" t="n">
-        <v>6978173</v>
+        <v>6978235</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6750,54 +6759,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129293780</v>
+        <v>129302229</v>
       </c>
       <c r="B60" t="n">
-        <v>57719</v>
+        <v>91543</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628680</v>
+        <v>628761</v>
       </c>
       <c r="R60" t="n">
-        <v>6978235</v>
+        <v>6978157</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302229</v>
+        <v>129302274</v>
       </c>
       <c r="B61" t="n">
-        <v>91543</v>
+        <v>80148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628761</v>
+        <v>628659</v>
       </c>
       <c r="R61" t="n">
-        <v>6978157</v>
+        <v>6978419</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129302259</v>
+        <v>129291473</v>
       </c>
       <c r="B70" t="n">
-        <v>91996</v>
+        <v>98710</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7759,34 +7759,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628771</v>
+        <v>628549</v>
       </c>
       <c r="R70" t="n">
-        <v>6978154</v>
+        <v>6978449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7845,45 +7849,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129302254</v>
+        <v>129290108</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>98710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628894</v>
+        <v>628447</v>
       </c>
       <c r="R71" t="n">
-        <v>6978096</v>
+        <v>6978522</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,11 +7924,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7947,10 +7950,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129291473</v>
+        <v>129302259</v>
       </c>
       <c r="B72" t="n">
-        <v>98710</v>
+        <v>91996</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7958,38 +7961,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628549</v>
+        <v>628771</v>
       </c>
       <c r="R72" t="n">
-        <v>6978449</v>
+        <v>6978154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8048,49 +8047,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129290108</v>
+        <v>129302254</v>
       </c>
       <c r="B73" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628447</v>
+        <v>628894</v>
       </c>
       <c r="R73" t="n">
-        <v>6978522</v>
+        <v>6978096</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8123,6 +8118,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8455,32 +8455,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129302227</v>
+        <v>129290447</v>
       </c>
       <c r="B77" t="n">
-        <v>91543</v>
+        <v>97581</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628851</v>
+        <v>628494</v>
       </c>
       <c r="R77" t="n">
-        <v>6978504</v>
+        <v>6978496</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8552,45 +8552,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129295124</v>
+        <v>129302281</v>
       </c>
       <c r="B78" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628788</v>
+        <v>628688</v>
       </c>
       <c r="R78" t="n">
-        <v>6978227</v>
+        <v>6978441</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8625,12 +8629,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8649,10 +8659,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129289501</v>
+        <v>129295124</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8660,39 +8670,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628451</v>
+        <v>628788</v>
       </c>
       <c r="R79" t="n">
-        <v>6978596</v>
+        <v>6978227</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8725,11 +8730,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8756,45 +8756,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129290447</v>
+        <v>129289501</v>
       </c>
       <c r="B80" t="n">
-        <v>97581</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628494</v>
+        <v>628451</v>
       </c>
       <c r="R80" t="n">
-        <v>6978496</v>
+        <v>6978596</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8827,6 +8832,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8853,10 +8863,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302255</v>
+        <v>129302227</v>
       </c>
       <c r="B81" t="n">
-        <v>57724</v>
+        <v>91543</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8864,21 +8874,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8888,10 +8898,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628712</v>
+        <v>628851</v>
       </c>
       <c r="R81" t="n">
-        <v>6978376</v>
+        <v>6978504</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8924,11 +8934,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8955,49 +8960,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B82" t="n">
-        <v>98710</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R82" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,7 +9035,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9043,7 +9044,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9256,45 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129302267</v>
+        <v>129294276</v>
       </c>
       <c r="B85" t="n">
-        <v>91841</v>
+        <v>91756</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628603</v>
+        <v>628790</v>
       </c>
       <c r="R85" t="n">
-        <v>6978502</v>
+        <v>6978034</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302232</v>
+        <v>129292746</v>
       </c>
       <c r="B86" t="n">
-        <v>91543</v>
+        <v>91841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628742</v>
+        <v>628586</v>
       </c>
       <c r="R86" t="n">
-        <v>6978216</v>
+        <v>6978451</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302264</v>
+        <v>129290229</v>
       </c>
       <c r="B87" t="n">
         <v>91841</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628796</v>
+        <v>628436</v>
       </c>
       <c r="R87" t="n">
-        <v>6978261</v>
+        <v>6978498</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,45 +9547,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129302260</v>
+        <v>129293914</v>
       </c>
       <c r="B88" t="n">
-        <v>91996</v>
+        <v>57887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628641</v>
+        <v>628690</v>
       </c>
       <c r="R88" t="n">
-        <v>6978450</v>
+        <v>6978221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,7 +9649,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302258</v>
+        <v>129302260</v>
       </c>
       <c r="B89" t="n">
         <v>91996</v>
@@ -9679,10 +9684,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628851</v>
+        <v>628641</v>
       </c>
       <c r="R89" t="n">
-        <v>6978502</v>
+        <v>6978450</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,32 +9746,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302291</v>
+        <v>129302258</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>91996</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9776,10 +9781,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628794</v>
+        <v>628851</v>
       </c>
       <c r="R90" t="n">
-        <v>6978373</v>
+        <v>6978502</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9838,10 +9843,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129293890</v>
+        <v>129302291</v>
       </c>
       <c r="B91" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9849,39 +9854,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628691</v>
+        <v>628794</v>
       </c>
       <c r="R91" t="n">
-        <v>6978242</v>
+        <v>6978373</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9914,11 +9914,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9945,45 +9940,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129294276</v>
+        <v>129289873</v>
       </c>
       <c r="B92" t="n">
-        <v>91756</v>
+        <v>91507</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>48</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628790</v>
+        <v>628447</v>
       </c>
       <c r="R92" t="n">
-        <v>6978034</v>
+        <v>6978522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10042,32 +10037,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129292746</v>
+        <v>129296097</v>
       </c>
       <c r="B93" t="n">
-        <v>91841</v>
+        <v>80177</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10077,10 +10072,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628586</v>
+        <v>628959</v>
       </c>
       <c r="R93" t="n">
-        <v>6978451</v>
+        <v>6978530</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10139,10 +10134,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129290229</v>
+        <v>129293890</v>
       </c>
       <c r="B94" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10150,34 +10145,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628436</v>
+        <v>628691</v>
       </c>
       <c r="R94" t="n">
-        <v>6978498</v>
+        <v>6978242</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10210,6 +10210,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,32 +10241,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129289873</v>
+        <v>129302267</v>
       </c>
       <c r="B95" t="n">
-        <v>91507</v>
+        <v>91841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10271,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628447</v>
+        <v>628603</v>
       </c>
       <c r="R95" t="n">
-        <v>6978522</v>
+        <v>6978502</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10333,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129296097</v>
+        <v>129302232</v>
       </c>
       <c r="B96" t="n">
-        <v>80177</v>
+        <v>91543</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10368,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628959</v>
+        <v>628742</v>
       </c>
       <c r="R96" t="n">
-        <v>6978530</v>
+        <v>6978216</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10430,10 +10435,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129293914</v>
+        <v>129302264</v>
       </c>
       <c r="B97" t="n">
-        <v>57887</v>
+        <v>91841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10441,39 +10446,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628690</v>
+        <v>628796</v>
       </c>
       <c r="R97" t="n">
-        <v>6978221</v>
+        <v>6978261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10836,45 +10836,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129295020</v>
+        <v>129302282</v>
       </c>
       <c r="B101" t="n">
-        <v>80183</v>
+        <v>98710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628826</v>
+        <v>628654</v>
       </c>
       <c r="R101" t="n">
-        <v>6978150</v>
+        <v>6978418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,6 +10907,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10933,7 +10938,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302282</v>
+        <v>129302287</v>
       </c>
       <c r="B102" t="n">
         <v>98710</v>
@@ -10968,10 +10973,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628654</v>
+        <v>628649</v>
       </c>
       <c r="R102" t="n">
-        <v>6978418</v>
+        <v>6978449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11008,7 +11013,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 stycken</t>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11035,32 +11040,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302287</v>
+        <v>129302268</v>
       </c>
       <c r="B103" t="n">
-        <v>98710</v>
+        <v>97581</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11070,10 +11075,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628649</v>
+        <v>628719</v>
       </c>
       <c r="R103" t="n">
-        <v>6978449</v>
+        <v>6978594</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11106,11 +11111,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11137,49 +11137,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129295651</v>
+        <v>129302263</v>
       </c>
       <c r="B104" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628796</v>
+        <v>628810</v>
       </c>
       <c r="R104" t="n">
-        <v>6978373</v>
+        <v>6978299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11238,45 +11234,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302263</v>
+        <v>129295020</v>
       </c>
       <c r="B105" t="n">
-        <v>91841</v>
+        <v>80183</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628810</v>
+        <v>628826</v>
       </c>
       <c r="R105" t="n">
-        <v>6978299</v>
+        <v>6978150</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11335,45 +11331,49 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302268</v>
+        <v>129295651</v>
       </c>
       <c r="B106" t="n">
-        <v>97581</v>
+        <v>98710</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628719</v>
+        <v>628796</v>
       </c>
       <c r="R106" t="n">
-        <v>6978594</v>
+        <v>6978373</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12631,54 +12631,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129293329</v>
+        <v>129294695</v>
       </c>
       <c r="B119" t="n">
-        <v>57724</v>
+        <v>91996</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628640</v>
+        <v>628831</v>
       </c>
       <c r="R119" t="n">
-        <v>6978364</v>
+        <v>6978180</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12737,7 +12728,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129294695</v>
+        <v>129297070</v>
       </c>
       <c r="B120" t="n">
         <v>91996</v>
@@ -12768,14 +12759,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628831</v>
+        <v>628764</v>
       </c>
       <c r="R120" t="n">
-        <v>6978180</v>
+        <v>6978591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12834,45 +12825,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129297070</v>
+        <v>129295812</v>
       </c>
       <c r="B121" t="n">
-        <v>91996</v>
+        <v>91543</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628764</v>
+        <v>628900</v>
       </c>
       <c r="R121" t="n">
-        <v>6978591</v>
+        <v>6978416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12931,10 +12922,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129295812</v>
+        <v>129293329</v>
       </c>
       <c r="B122" t="n">
-        <v>91543</v>
+        <v>57724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12942,34 +12933,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628900</v>
+        <v>628640</v>
       </c>
       <c r="R122" t="n">
-        <v>6978416</v>
+        <v>6978364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14424,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129302228</v>
+        <v>129293208</v>
       </c>
       <c r="B137" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14435,34 +14435,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628870</v>
+        <v>628695</v>
       </c>
       <c r="R137" t="n">
-        <v>6978469</v>
+        <v>6978356</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14495,6 +14500,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14521,7 +14531,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293208</v>
+        <v>129293275</v>
       </c>
       <c r="B138" t="n">
         <v>57727</v>
@@ -14561,10 +14571,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628695</v>
+        <v>628693</v>
       </c>
       <c r="R138" t="n">
-        <v>6978356</v>
+        <v>6978372</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14628,10 +14638,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129293275</v>
+        <v>129302228</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14639,39 +14649,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628693</v>
+        <v>628870</v>
       </c>
       <c r="R139" t="n">
-        <v>6978372</v>
+        <v>6978469</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14704,11 +14709,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -1172,7 +1172,7 @@
         <v>129181897</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>129184366</v>
       </c>
       <c r="B7" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>129184816</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129185300</v>
       </c>
       <c r="B9" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129184595</v>
       </c>
       <c r="B10" t="n">
-        <v>80108</v>
+        <v>80109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>129182054</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>129292781</v>
       </c>
       <c r="B15" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129295830</v>
       </c>
       <c r="B16" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,45 +2469,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295766</v>
+        <v>129302237</v>
       </c>
       <c r="B17" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628846</v>
+        <v>628766</v>
       </c>
       <c r="R17" t="n">
-        <v>6978364</v>
+        <v>6978173</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,6 +2540,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,7 +2571,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302237</v>
+        <v>129302245</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2601,10 +2606,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628766</v>
+        <v>628749</v>
       </c>
       <c r="R18" t="n">
-        <v>6978173</v>
+        <v>6978341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2641,7 +2646,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,45 +2673,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302245</v>
+        <v>129295766</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628749</v>
+        <v>628846</v>
       </c>
       <c r="R19" t="n">
-        <v>6978341</v>
+        <v>6978364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2773,7 +2773,7 @@
         <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,50 +2872,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294050</v>
+        <v>129292558</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628728</v>
+        <v>628589</v>
       </c>
       <c r="R21" t="n">
-        <v>6978173</v>
+        <v>6978414</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,11 +2947,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,49 +2973,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129292558</v>
+        <v>129302240</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628589</v>
+        <v>628764</v>
       </c>
       <c r="R22" t="n">
-        <v>6978414</v>
+        <v>6978279</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,6 +3044,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302262</v>
+        <v>129302243</v>
       </c>
       <c r="B23" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3091,21 +3086,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3115,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628800</v>
+        <v>628743</v>
       </c>
       <c r="R23" t="n">
-        <v>6978306</v>
+        <v>6978315</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,6 +3146,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,32 +3177,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302265</v>
+        <v>129302284</v>
       </c>
       <c r="B24" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628772</v>
+        <v>628667</v>
       </c>
       <c r="R24" t="n">
-        <v>6978157</v>
+        <v>6978461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,6 +3248,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3274,32 +3279,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302243</v>
+        <v>129302278</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3309,10 +3314,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628743</v>
+        <v>628894</v>
       </c>
       <c r="R25" t="n">
-        <v>6978315</v>
+        <v>6978483</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,7 +3354,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302240</v>
+        <v>129302262</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3387,21 +3392,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628764</v>
+        <v>628800</v>
       </c>
       <c r="R26" t="n">
-        <v>6978279</v>
+        <v>6978306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3447,11 +3452,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,32 +3478,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302284</v>
+        <v>129302265</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628667</v>
+        <v>628772</v>
       </c>
       <c r="R27" t="n">
-        <v>6978461</v>
+        <v>6978157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,11 +3549,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3580,32 +3575,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302278</v>
+        <v>129302269</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3615,10 +3610,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628894</v>
+        <v>628792</v>
       </c>
       <c r="R28" t="n">
-        <v>6978483</v>
+        <v>6978309</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,11 +3646,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3685,7 +3675,7 @@
         <v>129293584</v>
       </c>
       <c r="B29" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,7 +3772,7 @@
         <v>129294036</v>
       </c>
       <c r="B30" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3879,7 +3869,7 @@
         <v>129290628</v>
       </c>
       <c r="B31" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3973,45 +3963,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302269</v>
+        <v>129294050</v>
       </c>
       <c r="B32" t="n">
-        <v>97581</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628792</v>
+        <v>628728</v>
       </c>
       <c r="R32" t="n">
-        <v>6978309</v>
+        <v>6978173</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,6 +4039,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129295187</v>
+        <v>129296183</v>
       </c>
       <c r="B33" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628834</v>
+        <v>629055</v>
       </c>
       <c r="R33" t="n">
-        <v>6978251</v>
+        <v>6978511</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129290118</v>
+        <v>129302235</v>
       </c>
       <c r="B34" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628453</v>
+        <v>628629</v>
       </c>
       <c r="R34" t="n">
-        <v>6978518</v>
+        <v>6978532</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,45 +4264,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294218</v>
+        <v>129302293</v>
       </c>
       <c r="B35" t="n">
-        <v>96044</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1079</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628798</v>
+        <v>628737</v>
       </c>
       <c r="R35" t="n">
-        <v>6978072</v>
+        <v>6978300</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4335,11 +4335,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,10 +4361,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129296183</v>
+        <v>129295187</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,34 +4372,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>629055</v>
+        <v>628834</v>
       </c>
       <c r="R36" t="n">
-        <v>6978511</v>
+        <v>6978251</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293171</v>
+        <v>129290118</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,43 +4469,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628702</v>
+        <v>628453</v>
       </c>
       <c r="R37" t="n">
-        <v>6978339</v>
+        <v>6978518</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,45 +4555,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302293</v>
+        <v>129294218</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>96046</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628737</v>
+        <v>628798</v>
       </c>
       <c r="R38" t="n">
-        <v>6978300</v>
+        <v>6978072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4640,6 +4626,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302235</v>
+        <v>129293171</v>
       </c>
       <c r="B39" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,34 +4668,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628629</v>
+        <v>628702</v>
       </c>
       <c r="R39" t="n">
-        <v>6978532</v>
+        <v>6978339</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129294028</v>
+        <v>129302248</v>
       </c>
       <c r="B41" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4876,34 +4876,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628728</v>
+        <v>628679</v>
       </c>
       <c r="R41" t="n">
-        <v>6978173</v>
+        <v>6978469</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,6 +4936,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,45 +4967,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293533</v>
+        <v>129294028</v>
       </c>
       <c r="B42" t="n">
-        <v>91996</v>
+        <v>91545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628623</v>
+        <v>628728</v>
       </c>
       <c r="R42" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5059,32 +5064,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B43" t="n">
-        <v>91841</v>
+        <v>91998</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R43" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5156,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296072</v>
+        <v>129291502</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5167,43 +5172,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628971</v>
+        <v>628564</v>
       </c>
       <c r="R44" t="n">
-        <v>6978518</v>
+        <v>6978436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,37 +5258,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129290183</v>
+        <v>129296072</v>
       </c>
       <c r="B45" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5301,10 +5302,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628436</v>
+        <v>628971</v>
       </c>
       <c r="R45" t="n">
-        <v>6978498</v>
+        <v>6978518</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5363,45 +5364,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129302248</v>
+        <v>129290183</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628679</v>
+        <v>628436</v>
       </c>
       <c r="R46" t="n">
-        <v>6978469</v>
+        <v>6978498</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5434,11 +5439,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5465,10 +5465,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129296084</v>
+        <v>129290616</v>
       </c>
       <c r="B47" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628959</v>
+        <v>628499</v>
       </c>
       <c r="R47" t="n">
-        <v>6978530</v>
+        <v>6978448</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290169</v>
+        <v>129290361</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,39 +5573,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628453</v>
+        <v>628465</v>
       </c>
       <c r="R48" t="n">
-        <v>6978518</v>
+        <v>6978491</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5638,11 +5633,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5669,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129302233</v>
+        <v>129296084</v>
       </c>
       <c r="B49" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5680,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628759</v>
+        <v>628959</v>
       </c>
       <c r="R49" t="n">
-        <v>6978233</v>
+        <v>6978530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,10 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129302231</v>
+        <v>129290169</v>
       </c>
       <c r="B50" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5777,34 +5767,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628752</v>
+        <v>628453</v>
       </c>
       <c r="R50" t="n">
-        <v>6978198</v>
+        <v>6978518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,6 +5832,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,10 +5863,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290616</v>
+        <v>129302294</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5874,21 +5874,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628499</v>
+        <v>628661</v>
       </c>
       <c r="R51" t="n">
-        <v>6978448</v>
+        <v>6978421</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5960,32 +5960,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129290361</v>
+        <v>129302275</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628465</v>
+        <v>628663</v>
       </c>
       <c r="R52" t="n">
-        <v>6978491</v>
+        <v>6978428</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6031,6 +6031,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6057,10 +6062,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129290084</v>
+        <v>129302276</v>
       </c>
       <c r="B53" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6085,21 +6090,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628475</v>
+        <v>628648</v>
       </c>
       <c r="R53" t="n">
-        <v>6978540</v>
+        <v>6978420</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6132,6 +6133,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6158,45 +6164,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129302294</v>
+        <v>129290084</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628661</v>
+        <v>628475</v>
       </c>
       <c r="R54" t="n">
-        <v>6978421</v>
+        <v>6978540</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6255,32 +6265,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129302275</v>
+        <v>129302231</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6290,10 +6300,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628663</v>
+        <v>628752</v>
       </c>
       <c r="R55" t="n">
-        <v>6978428</v>
+        <v>6978198</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6326,11 +6336,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6357,32 +6362,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302276</v>
+        <v>129302233</v>
       </c>
       <c r="B56" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6392,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628648</v>
+        <v>628759</v>
       </c>
       <c r="R56" t="n">
-        <v>6978420</v>
+        <v>6978233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6428,11 +6433,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6462,7 +6462,7 @@
         <v>129295935</v>
       </c>
       <c r="B57" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129294015</v>
+        <v>129302274</v>
       </c>
       <c r="B58" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6587,14 +6587,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628728</v>
+        <v>628659</v>
       </c>
       <c r="R58" t="n">
-        <v>6978173</v>
+        <v>6978419</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,54 +6653,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129293780</v>
+        <v>129302241</v>
       </c>
       <c r="B59" t="n">
-        <v>57719</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628680</v>
+        <v>628741</v>
       </c>
       <c r="R59" t="n">
-        <v>6978235</v>
+        <v>6978271</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6733,6 +6724,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6759,10 +6755,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302229</v>
+        <v>129302252</v>
       </c>
       <c r="B60" t="n">
-        <v>91543</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6770,21 +6766,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6794,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628761</v>
+        <v>628837</v>
       </c>
       <c r="R60" t="n">
-        <v>6978157</v>
+        <v>6978500</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,6 +6826,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6856,32 +6857,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302274</v>
+        <v>129302271</v>
       </c>
       <c r="B61" t="n">
-        <v>80148</v>
+        <v>97583</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6892,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628659</v>
+        <v>628763</v>
       </c>
       <c r="R61" t="n">
-        <v>6978419</v>
+        <v>6978273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6953,10 +6954,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302241</v>
+        <v>129294015</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,34 +6965,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628741</v>
+        <v>628728</v>
       </c>
       <c r="R62" t="n">
-        <v>6978271</v>
+        <v>6978173</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7024,11 +7025,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7055,45 +7051,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302252</v>
+        <v>129293780</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>57719</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100110</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628837</v>
+        <v>628680</v>
       </c>
       <c r="R63" t="n">
-        <v>6978500</v>
+        <v>6978235</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7126,11 +7131,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7157,32 +7157,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302271</v>
+        <v>129302229</v>
       </c>
       <c r="B64" t="n">
-        <v>97581</v>
+        <v>91545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628763</v>
+        <v>628761</v>
       </c>
       <c r="R64" t="n">
-        <v>6978273</v>
+        <v>6978157</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7257,7 +7257,7 @@
         <v>129295162</v>
       </c>
       <c r="B65" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>129292729</v>
       </c>
       <c r="B66" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>129291635</v>
       </c>
       <c r="B67" t="n">
-        <v>96044</v>
+        <v>96046</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>129294000</v>
       </c>
       <c r="B68" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129291473</v>
+        <v>129302259</v>
       </c>
       <c r="B70" t="n">
-        <v>98710</v>
+        <v>91998</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7759,38 +7759,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628549</v>
+        <v>628771</v>
       </c>
       <c r="R70" t="n">
-        <v>6978449</v>
+        <v>6978154</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7849,10 +7845,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129290108</v>
+        <v>129291473</v>
       </c>
       <c r="B71" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7879,7 +7875,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7888,10 +7884,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628447</v>
+        <v>628549</v>
       </c>
       <c r="R71" t="n">
-        <v>6978522</v>
+        <v>6978449</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7950,10 +7946,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302259</v>
+        <v>129290108</v>
       </c>
       <c r="B72" t="n">
-        <v>91996</v>
+        <v>98712</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7961,34 +7957,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628771</v>
+        <v>628447</v>
       </c>
       <c r="R72" t="n">
-        <v>6978154</v>
+        <v>6978522</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302254</v>
+        <v>129302250</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8058,16 +8058,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628894</v>
+        <v>628495</v>
       </c>
       <c r="R73" t="n">
-        <v>6978096</v>
+        <v>6978647</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8149,7 +8149,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302250</v>
+        <v>129302244</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628495</v>
+        <v>628756</v>
       </c>
       <c r="R74" t="n">
-        <v>6978647</v>
+        <v>6978337</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302244</v>
+        <v>129302254</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628756</v>
+        <v>628894</v>
       </c>
       <c r="R75" t="n">
-        <v>6978337</v>
+        <v>6978096</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8356,7 +8356,7 @@
         <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8455,45 +8455,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129290447</v>
+        <v>129295124</v>
       </c>
       <c r="B77" t="n">
-        <v>97581</v>
+        <v>91843</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628494</v>
+        <v>628788</v>
       </c>
       <c r="R77" t="n">
-        <v>6978496</v>
+        <v>6978227</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8552,49 +8552,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129302281</v>
+        <v>129289501</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628688</v>
+        <v>628451</v>
       </c>
       <c r="R78" t="n">
-        <v>6978441</v>
+        <v>6978596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8631,7 +8632,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8640,7 +8641,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8659,45 +8659,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129295124</v>
+        <v>129290447</v>
       </c>
       <c r="B79" t="n">
-        <v>91841</v>
+        <v>97583</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628788</v>
+        <v>628494</v>
       </c>
       <c r="R79" t="n">
-        <v>6978227</v>
+        <v>6978496</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8756,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129289501</v>
+        <v>129302227</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8767,39 +8767,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628451</v>
+        <v>628851</v>
       </c>
       <c r="R80" t="n">
-        <v>6978596</v>
+        <v>6978504</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8832,11 +8827,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8863,45 +8853,49 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302227</v>
+        <v>129302281</v>
       </c>
       <c r="B81" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628851</v>
+        <v>628688</v>
       </c>
       <c r="R81" t="n">
-        <v>6978504</v>
+        <v>6978441</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8936,12 +8930,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>129296224</v>
       </c>
       <c r="B84" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>129294276</v>
       </c>
       <c r="B85" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9353,32 +9353,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129292746</v>
+        <v>129289873</v>
       </c>
       <c r="B86" t="n">
-        <v>91841</v>
+        <v>91509</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628586</v>
+        <v>628447</v>
       </c>
       <c r="R86" t="n">
-        <v>6978451</v>
+        <v>6978522</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,10 +9450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129290229</v>
+        <v>129293890</v>
       </c>
       <c r="B87" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9461,34 +9461,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628436</v>
+        <v>628691</v>
       </c>
       <c r="R87" t="n">
-        <v>6978498</v>
+        <v>6978242</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9521,6 +9526,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9649,32 +9659,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302260</v>
+        <v>129302232</v>
       </c>
       <c r="B89" t="n">
-        <v>91996</v>
+        <v>91545</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9684,10 +9694,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628641</v>
+        <v>628742</v>
       </c>
       <c r="R89" t="n">
-        <v>6978450</v>
+        <v>6978216</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9746,10 +9756,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302258</v>
+        <v>129302260</v>
       </c>
       <c r="B90" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9781,10 +9791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628851</v>
+        <v>628641</v>
       </c>
       <c r="R90" t="n">
-        <v>6978502</v>
+        <v>6978450</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9843,32 +9853,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302291</v>
+        <v>129302258</v>
       </c>
       <c r="B91" t="n">
-        <v>79043</v>
+        <v>91998</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9878,10 +9888,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628794</v>
+        <v>628851</v>
       </c>
       <c r="R91" t="n">
-        <v>6978373</v>
+        <v>6978502</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9940,32 +9950,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129289873</v>
+        <v>129302291</v>
       </c>
       <c r="B92" t="n">
-        <v>91507</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9975,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628447</v>
+        <v>628794</v>
       </c>
       <c r="R92" t="n">
-        <v>6978522</v>
+        <v>6978373</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10037,32 +10047,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129296097</v>
+        <v>129292746</v>
       </c>
       <c r="B93" t="n">
-        <v>80177</v>
+        <v>91843</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10072,10 +10082,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628959</v>
+        <v>628586</v>
       </c>
       <c r="R93" t="n">
-        <v>6978530</v>
+        <v>6978451</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10134,10 +10144,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129293890</v>
+        <v>129290229</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10145,39 +10155,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628691</v>
+        <v>628436</v>
       </c>
       <c r="R94" t="n">
-        <v>6978242</v>
+        <v>6978498</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10210,11 +10215,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10241,32 +10241,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302267</v>
+        <v>129296097</v>
       </c>
       <c r="B95" t="n">
-        <v>91841</v>
+        <v>80178</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628603</v>
+        <v>628959</v>
       </c>
       <c r="R95" t="n">
-        <v>6978502</v>
+        <v>6978530</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,10 +10338,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302232</v>
+        <v>129302267</v>
       </c>
       <c r="B96" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10349,21 +10349,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628742</v>
+        <v>628603</v>
       </c>
       <c r="R96" t="n">
-        <v>6978216</v>
+        <v>6978502</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10438,7 +10438,7 @@
         <v>129302264</v>
       </c>
       <c r="B97" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10532,54 +10532,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129295410</v>
+        <v>129293044</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628767</v>
+        <v>628662</v>
       </c>
       <c r="R98" t="n">
-        <v>6978383</v>
+        <v>6978408</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,49 +10633,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129293044</v>
+        <v>129302295</v>
       </c>
       <c r="B99" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628662</v>
+        <v>628463</v>
       </c>
       <c r="R99" t="n">
-        <v>6978408</v>
+        <v>6978635</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10739,10 +10730,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129302295</v>
+        <v>129295410</v>
       </c>
       <c r="B100" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10750,34 +10741,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>628463</v>
+        <v>628767</v>
       </c>
       <c r="R100" t="n">
-        <v>6978635</v>
+        <v>6978383</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10836,10 +10836,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129302282</v>
+        <v>129295651</v>
       </c>
       <c r="B101" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10864,17 +10864,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628654</v>
+        <v>628796</v>
       </c>
       <c r="R101" t="n">
-        <v>6978418</v>
+        <v>6978373</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,11 +10911,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10938,45 +10937,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302287</v>
+        <v>129295020</v>
       </c>
       <c r="B102" t="n">
-        <v>98710</v>
+        <v>80184</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628649</v>
+        <v>628826</v>
       </c>
       <c r="R102" t="n">
-        <v>6978449</v>
+        <v>6978150</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11009,11 +11008,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11040,32 +11034,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302268</v>
+        <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>97581</v>
+        <v>91843</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11075,10 +11069,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628719</v>
+        <v>628810</v>
       </c>
       <c r="R103" t="n">
-        <v>6978594</v>
+        <v>6978299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11137,32 +11131,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302263</v>
+        <v>129302282</v>
       </c>
       <c r="B104" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11172,10 +11166,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628810</v>
+        <v>628654</v>
       </c>
       <c r="R104" t="n">
-        <v>6978299</v>
+        <v>6978418</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11208,6 +11202,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11234,45 +11233,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129295020</v>
+        <v>129302287</v>
       </c>
       <c r="B105" t="n">
-        <v>80183</v>
+        <v>98712</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628826</v>
+        <v>628649</v>
       </c>
       <c r="R105" t="n">
-        <v>6978150</v>
+        <v>6978449</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,6 +11304,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11331,49 +11335,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129295651</v>
+        <v>129302268</v>
       </c>
       <c r="B106" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628796</v>
+        <v>628719</v>
       </c>
       <c r="R106" t="n">
-        <v>6978373</v>
+        <v>6978594</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11435,7 +11435,7 @@
         <v>129293395</v>
       </c>
       <c r="B107" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>129289885</v>
       </c>
       <c r="B108" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129293300</v>
+        <v>129302251</v>
       </c>
       <c r="B109" t="n">
         <v>57727</v>
@@ -11655,21 +11655,16 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628665</v>
+        <v>628425</v>
       </c>
       <c r="R109" t="n">
-        <v>6978376</v>
+        <v>6978621</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11706,7 +11701,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11835,7 +11830,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129302251</v>
+        <v>129293300</v>
       </c>
       <c r="B111" t="n">
         <v>57727</v>
@@ -11864,16 +11859,21 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628425</v>
+        <v>628665</v>
       </c>
       <c r="R111" t="n">
-        <v>6978621</v>
+        <v>6978376</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12039,32 +12039,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302256</v>
+        <v>129302247</v>
       </c>
       <c r="B113" t="n">
-        <v>98627</v>
+        <v>57727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628658</v>
+        <v>628749</v>
       </c>
       <c r="R113" t="n">
-        <v>6978439</v>
+        <v>6978349</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>2 exemplar. Gamla blomstänger.</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12144,7 +12144,7 @@
         <v>129295820</v>
       </c>
       <c r="B114" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>129293475</v>
       </c>
       <c r="B115" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>129302225</v>
       </c>
       <c r="B116" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>129302290</v>
       </c>
       <c r="B117" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12529,32 +12529,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129302247</v>
+        <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>57727</v>
+        <v>98629</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12564,10 +12564,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628749</v>
+        <v>628658</v>
       </c>
       <c r="R118" t="n">
-        <v>6978349</v>
+        <v>6978439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>2 exemplar. Gamla blomstänger.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12634,7 +12634,7 @@
         <v>129294695</v>
       </c>
       <c r="B119" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12728,32 +12728,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129297070</v>
+        <v>129302242</v>
       </c>
       <c r="B120" t="n">
-        <v>91996</v>
+        <v>57727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628764</v>
+        <v>628750</v>
       </c>
       <c r="R120" t="n">
-        <v>6978591</v>
+        <v>6978284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12799,6 +12799,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12825,45 +12830,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129295812</v>
+        <v>129297070</v>
       </c>
       <c r="B121" t="n">
-        <v>91543</v>
+        <v>91998</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628900</v>
+        <v>628764</v>
       </c>
       <c r="R121" t="n">
-        <v>6978416</v>
+        <v>6978591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12922,10 +12927,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129293329</v>
+        <v>129295812</v>
       </c>
       <c r="B122" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12933,43 +12938,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628640</v>
+        <v>628900</v>
       </c>
       <c r="R122" t="n">
-        <v>6978364</v>
+        <v>6978416</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13028,45 +13024,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129302257</v>
+        <v>129293329</v>
       </c>
       <c r="B123" t="n">
-        <v>91996</v>
+        <v>57724</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628794</v>
+        <v>628640</v>
       </c>
       <c r="R123" t="n">
-        <v>6978311</v>
+        <v>6978364</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13125,32 +13130,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302273</v>
+        <v>129302257</v>
       </c>
       <c r="B124" t="n">
-        <v>80148</v>
+        <v>91998</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13160,10 +13165,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628878</v>
+        <v>628794</v>
       </c>
       <c r="R124" t="n">
-        <v>6978535</v>
+        <v>6978311</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13222,10 +13227,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302242</v>
+        <v>129302273</v>
       </c>
       <c r="B125" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13233,21 +13238,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13257,10 +13262,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628750</v>
+        <v>628878</v>
       </c>
       <c r="R125" t="n">
-        <v>6978284</v>
+        <v>6978535</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13293,11 +13298,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13324,10 +13324,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129302270</v>
+        <v>129291548</v>
       </c>
       <c r="B126" t="n">
-        <v>97581</v>
+        <v>80053</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628812</v>
+        <v>628549</v>
       </c>
       <c r="R126" t="n">
-        <v>6978062</v>
+        <v>6978433</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13523,32 +13523,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129302296</v>
+        <v>129290692</v>
       </c>
       <c r="B128" t="n">
-        <v>79043</v>
+        <v>80109</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13558,10 +13558,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628449</v>
+        <v>628515</v>
       </c>
       <c r="R128" t="n">
-        <v>6978612</v>
+        <v>6978451</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13620,45 +13620,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129302239</v>
+        <v>129294090</v>
       </c>
       <c r="B129" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628747</v>
+        <v>628743</v>
       </c>
       <c r="R129" t="n">
-        <v>6978218</v>
+        <v>6978155</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13691,11 +13691,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13722,32 +13717,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129291548</v>
+        <v>129302239</v>
       </c>
       <c r="B130" t="n">
-        <v>80052</v>
+        <v>57727</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13757,10 +13752,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628549</v>
+        <v>628747</v>
       </c>
       <c r="R130" t="n">
-        <v>6978433</v>
+        <v>6978218</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13793,6 +13788,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13819,10 +13819,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129290523</v>
+        <v>129302296</v>
       </c>
       <c r="B131" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13830,39 +13830,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628509</v>
+        <v>628449</v>
       </c>
       <c r="R131" t="n">
-        <v>6978510</v>
+        <v>6978612</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13895,11 +13890,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13926,45 +13916,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129290692</v>
+        <v>129290523</v>
       </c>
       <c r="B132" t="n">
-        <v>80108</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628515</v>
+        <v>628509</v>
       </c>
       <c r="R132" t="n">
-        <v>6978451</v>
+        <v>6978510</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13997,6 +13992,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14023,45 +14023,49 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129294090</v>
+        <v>129291461</v>
       </c>
       <c r="B133" t="n">
-        <v>80108</v>
+        <v>98712</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628743</v>
+        <v>628547</v>
       </c>
       <c r="R133" t="n">
-        <v>6978155</v>
+        <v>6978457</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14120,49 +14124,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129291461</v>
+        <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628547</v>
+        <v>628812</v>
       </c>
       <c r="R134" t="n">
-        <v>6978457</v>
+        <v>6978062</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14224,7 +14224,7 @@
         <v>129294072</v>
       </c>
       <c r="B135" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B136" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,16 +14329,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14346,26 +14346,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R136" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14398,6 +14394,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14424,7 +14425,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293208</v>
+        <v>129293275</v>
       </c>
       <c r="B137" t="n">
         <v>57727</v>
@@ -14464,10 +14465,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628695</v>
+        <v>628693</v>
       </c>
       <c r="R137" t="n">
-        <v>6978356</v>
+        <v>6978372</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14531,10 +14532,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129293275</v>
+        <v>129295655</v>
       </c>
       <c r="B138" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14542,16 +14543,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14559,22 +14560,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628693</v>
+        <v>628796</v>
       </c>
       <c r="R138" t="n">
-        <v>6978372</v>
+        <v>6978373</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14607,11 +14612,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14641,7 +14641,7 @@
         <v>129302228</v>
       </c>
       <c r="B139" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14735,50 +14735,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129293977</v>
+        <v>129302288</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628687</v>
+        <v>628636</v>
       </c>
       <c r="R140" t="n">
-        <v>6978194</v>
+        <v>6978511</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14815,7 +14810,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14842,32 +14837,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129302266</v>
+        <v>129290695</v>
       </c>
       <c r="B141" t="n">
-        <v>91841</v>
+        <v>80185</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14877,10 +14872,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628639</v>
+        <v>628509</v>
       </c>
       <c r="R141" t="n">
-        <v>6978441</v>
+        <v>6978440</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14939,32 +14934,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129302272</v>
+        <v>129291606</v>
       </c>
       <c r="B142" t="n">
-        <v>97581</v>
+        <v>80149</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14974,10 +14969,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628641</v>
+        <v>628564</v>
       </c>
       <c r="R142" t="n">
-        <v>6978450</v>
+        <v>6978436</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15036,45 +15031,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129290695</v>
+        <v>129293977</v>
       </c>
       <c r="B143" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628509</v>
+        <v>628687</v>
       </c>
       <c r="R143" t="n">
-        <v>6978440</v>
+        <v>6978194</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15107,6 +15107,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15133,10 +15138,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129291606</v>
+        <v>129302266</v>
       </c>
       <c r="B144" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15144,21 +15149,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15168,10 +15173,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628564</v>
+        <v>628639</v>
       </c>
       <c r="R144" t="n">
-        <v>6978436</v>
+        <v>6978441</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15230,32 +15235,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129302288</v>
+        <v>129302272</v>
       </c>
       <c r="B145" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15265,10 +15270,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628636</v>
+        <v>628641</v>
       </c>
       <c r="R145" t="n">
-        <v>6978511</v>
+        <v>6978450</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15301,11 +15306,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15332,32 +15332,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129295841</v>
+        <v>129302261</v>
       </c>
       <c r="B146" t="n">
-        <v>91756</v>
+        <v>91843</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15367,10 +15367,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628889</v>
+        <v>628794</v>
       </c>
       <c r="R146" t="n">
-        <v>6978417</v>
+        <v>6978311</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15429,49 +15429,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129290760</v>
+        <v>129302230</v>
       </c>
       <c r="B147" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628499</v>
+        <v>628766</v>
       </c>
       <c r="R147" t="n">
-        <v>6978448</v>
+        <v>6978195</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15530,10 +15526,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129295136</v>
+        <v>129302226</v>
       </c>
       <c r="B148" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15541,34 +15537,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628799</v>
+        <v>628849</v>
       </c>
       <c r="R148" t="n">
-        <v>6978234</v>
+        <v>6978507</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15627,10 +15623,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129295133</v>
+        <v>129302238</v>
       </c>
       <c r="B149" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15638,34 +15634,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628788</v>
+        <v>628757</v>
       </c>
       <c r="R149" t="n">
-        <v>6978227</v>
+        <v>6978192</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15698,6 +15694,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15724,10 +15725,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129295719</v>
+        <v>129302249</v>
       </c>
       <c r="B150" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15735,34 +15736,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628846</v>
+        <v>628539</v>
       </c>
       <c r="R150" t="n">
-        <v>6978364</v>
+        <v>6978526</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15795,6 +15796,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15821,32 +15827,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129302226</v>
+        <v>129295841</v>
       </c>
       <c r="B151" t="n">
-        <v>91543</v>
+        <v>91758</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15856,10 +15862,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628849</v>
+        <v>628889</v>
       </c>
       <c r="R151" t="n">
-        <v>6978507</v>
+        <v>6978417</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15918,10 +15924,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129302230</v>
+        <v>129295136</v>
       </c>
       <c r="B152" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15929,34 +15935,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628766</v>
+        <v>628799</v>
       </c>
       <c r="R152" t="n">
-        <v>6978195</v>
+        <v>6978234</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16015,10 +16021,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302261</v>
+        <v>129295133</v>
       </c>
       <c r="B153" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16026,34 +16032,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628794</v>
+        <v>628788</v>
       </c>
       <c r="R153" t="n">
-        <v>6978311</v>
+        <v>6978227</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16112,10 +16118,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129302292</v>
+        <v>129295719</v>
       </c>
       <c r="B154" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16123,34 +16129,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628819</v>
+        <v>628846</v>
       </c>
       <c r="R154" t="n">
-        <v>6978067</v>
+        <v>6978364</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16183,11 +16189,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16214,45 +16215,49 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302249</v>
+        <v>129290760</v>
       </c>
       <c r="B155" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628539</v>
+        <v>628499</v>
       </c>
       <c r="R155" t="n">
-        <v>6978526</v>
+        <v>6978448</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16285,11 +16290,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16316,10 +16316,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302238</v>
+        <v>129302292</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16327,21 +16327,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628757</v>
+        <v>628819</v>
       </c>
       <c r="R156" t="n">
-        <v>6978192</v>
+        <v>6978067</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16421,7 +16421,7 @@
         <v>129302285</v>
       </c>
       <c r="B157" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>129302297</v>
       </c>
       <c r="B158" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16617,32 +16617,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129302253</v>
+        <v>129290278</v>
       </c>
       <c r="B159" t="n">
-        <v>57887</v>
+        <v>91998</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16652,10 +16652,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628759</v>
+        <v>628451</v>
       </c>
       <c r="R159" t="n">
-        <v>6978235</v>
+        <v>6978495</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16714,32 +16714,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129302279</v>
+        <v>129302234</v>
       </c>
       <c r="B160" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628884</v>
+        <v>628641</v>
       </c>
       <c r="R160" t="n">
-        <v>6978488</v>
+        <v>6978450</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16785,11 +16785,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16816,45 +16811,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129290278</v>
+        <v>129295735</v>
       </c>
       <c r="B161" t="n">
-        <v>91996</v>
+        <v>80184</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628451</v>
+        <v>628841</v>
       </c>
       <c r="R161" t="n">
-        <v>6978495</v>
+        <v>6978384</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16916,7 +16911,7 @@
         <v>129289808</v>
       </c>
       <c r="B162" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17010,45 +17005,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129295735</v>
+        <v>129302253</v>
       </c>
       <c r="B163" t="n">
-        <v>80183</v>
+        <v>57887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628841</v>
+        <v>628759</v>
       </c>
       <c r="R163" t="n">
-        <v>6978384</v>
+        <v>6978235</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17107,32 +17102,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129302234</v>
+        <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17142,10 +17137,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628641</v>
+        <v>628884</v>
       </c>
       <c r="R164" t="n">
-        <v>6978450</v>
+        <v>6978488</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17178,6 +17173,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,32 +2275,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129292781</v>
+        <v>129302237</v>
       </c>
       <c r="B15" t="n">
-        <v>92263</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628766</v>
       </c>
       <c r="R15" t="n">
-        <v>6978436</v>
+        <v>6978173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,6 +2346,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,32 +2377,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295830</v>
+        <v>129302245</v>
       </c>
       <c r="B16" t="n">
-        <v>92263</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628896</v>
+        <v>628749</v>
       </c>
       <c r="R16" t="n">
-        <v>6978430</v>
+        <v>6978341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,6 +2448,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,32 +2479,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129302237</v>
+        <v>129292781</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>92267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2504,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628766</v>
+        <v>628590</v>
       </c>
       <c r="R17" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,11 +2550,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,32 +2576,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302245</v>
+        <v>129295830</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>92267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628749</v>
+        <v>628896</v>
       </c>
       <c r="R18" t="n">
-        <v>6978341</v>
+        <v>6978430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,11 +2647,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,45 +2673,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129295766</v>
+        <v>129302283</v>
       </c>
       <c r="B19" t="n">
-        <v>80178</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628846</v>
+        <v>628664</v>
       </c>
       <c r="R19" t="n">
-        <v>6978364</v>
+        <v>6978446</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,6 +2744,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,45 +2775,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129302283</v>
+        <v>129295766</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>80178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628664</v>
+        <v>628846</v>
       </c>
       <c r="R20" t="n">
-        <v>6978446</v>
+        <v>6978364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,11 +2846,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,49 +2872,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129292558</v>
+        <v>129302269</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>97587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628589</v>
+        <v>628792</v>
       </c>
       <c r="R21" t="n">
-        <v>6978414</v>
+        <v>6978309</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302240</v>
+        <v>129294036</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,34 +2980,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628764</v>
+        <v>628728</v>
       </c>
       <c r="R22" t="n">
-        <v>6978279</v>
+        <v>6978173</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3044,11 +3040,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129302243</v>
+        <v>129290628</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,21 +3077,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3110,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628743</v>
+        <v>628499</v>
       </c>
       <c r="R23" t="n">
-        <v>6978315</v>
+        <v>6978448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,11 +3137,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3177,10 +3163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129302284</v>
+        <v>129293584</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>92002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3188,21 +3174,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3212,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628667</v>
+        <v>628624</v>
       </c>
       <c r="R24" t="n">
-        <v>6978461</v>
+        <v>6978328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3248,11 +3234,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,32 +3260,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302278</v>
+        <v>129302243</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3314,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628894</v>
+        <v>628743</v>
       </c>
       <c r="R25" t="n">
-        <v>6978483</v>
+        <v>6978315</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,7 +3335,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302262</v>
+        <v>129302240</v>
       </c>
       <c r="B26" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3392,21 +3373,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3416,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628800</v>
+        <v>628764</v>
       </c>
       <c r="R26" t="n">
-        <v>6978306</v>
+        <v>6978279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,6 +3433,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,10 +3464,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129302265</v>
+        <v>129294050</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,34 +3475,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628772</v>
+        <v>628728</v>
       </c>
       <c r="R27" t="n">
-        <v>6978157</v>
+        <v>6978173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,6 +3540,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,45 +3571,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302269</v>
+        <v>129292558</v>
       </c>
       <c r="B28" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628792</v>
+        <v>628589</v>
       </c>
       <c r="R28" t="n">
-        <v>6978309</v>
+        <v>6978414</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,32 +3672,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129293584</v>
+        <v>129302262</v>
       </c>
       <c r="B29" t="n">
-        <v>91998</v>
+        <v>91847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628624</v>
+        <v>628800</v>
       </c>
       <c r="R29" t="n">
-        <v>6978328</v>
+        <v>6978306</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,10 +3769,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294036</v>
+        <v>129302265</v>
       </c>
       <c r="B30" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,14 +3800,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628728</v>
+        <v>628772</v>
       </c>
       <c r="R30" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3866,32 +3866,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129290628</v>
+        <v>129302284</v>
       </c>
       <c r="B31" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628499</v>
+        <v>628667</v>
       </c>
       <c r="R31" t="n">
-        <v>6978448</v>
+        <v>6978461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3937,6 +3937,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,50 +3968,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294050</v>
+        <v>129302278</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628728</v>
+        <v>628894</v>
       </c>
       <c r="R32" t="n">
-        <v>6978173</v>
+        <v>6978483</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129296183</v>
+        <v>129290118</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>629055</v>
+        <v>628453</v>
       </c>
       <c r="R33" t="n">
-        <v>6978511</v>
+        <v>6978518</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129302235</v>
+        <v>129293171</v>
       </c>
       <c r="B34" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4178,34 +4178,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628629</v>
+        <v>628702</v>
       </c>
       <c r="R34" t="n">
-        <v>6978532</v>
+        <v>6978339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4264,10 +4273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129302293</v>
+        <v>129295187</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,34 +4284,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628737</v>
+        <v>628834</v>
       </c>
       <c r="R35" t="n">
-        <v>6978300</v>
+        <v>6978251</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4361,32 +4370,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129295187</v>
+        <v>129294218</v>
       </c>
       <c r="B36" t="n">
-        <v>91843</v>
+        <v>96050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4396,10 +4405,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628834</v>
+        <v>628798</v>
       </c>
       <c r="R36" t="n">
-        <v>6978251</v>
+        <v>6978072</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4432,6 +4441,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129290118</v>
+        <v>129296183</v>
       </c>
       <c r="B37" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4469,34 +4483,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628453</v>
+        <v>629055</v>
       </c>
       <c r="R37" t="n">
-        <v>6978518</v>
+        <v>6978511</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,45 +4569,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294218</v>
+        <v>129302293</v>
       </c>
       <c r="B38" t="n">
-        <v>96046</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1079</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628798</v>
+        <v>628737</v>
       </c>
       <c r="R38" t="n">
-        <v>6978072</v>
+        <v>6978300</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,11 +4640,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293171</v>
+        <v>129302235</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,43 +4677,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628702</v>
+        <v>628629</v>
       </c>
       <c r="R39" t="n">
-        <v>6978339</v>
+        <v>6978532</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129294028</v>
+        <v>129291502</v>
       </c>
       <c r="B42" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4978,34 +4978,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628728</v>
+        <v>628564</v>
       </c>
       <c r="R42" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5064,45 +5064,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293533</v>
+        <v>129294028</v>
       </c>
       <c r="B43" t="n">
-        <v>91998</v>
+        <v>91549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628623</v>
+        <v>628728</v>
       </c>
       <c r="R43" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5161,32 +5161,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B44" t="n">
-        <v>91843</v>
+        <v>92002</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R44" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5258,42 +5258,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129296072</v>
+        <v>129290183</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5302,10 +5297,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628971</v>
+        <v>628436</v>
       </c>
       <c r="R45" t="n">
-        <v>6978518</v>
+        <v>6978498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,37 +5359,42 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129290183</v>
+        <v>129296072</v>
       </c>
       <c r="B46" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628436</v>
+        <v>628971</v>
       </c>
       <c r="R46" t="n">
-        <v>6978498</v>
+        <v>6978518</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5465,45 +5465,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290616</v>
+        <v>129290084</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628499</v>
+        <v>628475</v>
       </c>
       <c r="R47" t="n">
-        <v>6978448</v>
+        <v>6978540</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,10 +5566,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290361</v>
+        <v>129302294</v>
       </c>
       <c r="B48" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5573,21 +5577,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5601,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628465</v>
+        <v>628661</v>
       </c>
       <c r="R48" t="n">
-        <v>6978491</v>
+        <v>6978421</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,10 +5663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129296084</v>
+        <v>129290616</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5674,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5698,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628959</v>
+        <v>628499</v>
       </c>
       <c r="R49" t="n">
-        <v>6978530</v>
+        <v>6978448</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,10 +5760,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290169</v>
+        <v>129290361</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5767,39 +5771,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628453</v>
+        <v>628465</v>
       </c>
       <c r="R50" t="n">
-        <v>6978518</v>
+        <v>6978491</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,11 +5831,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,10 +5857,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302294</v>
+        <v>129302231</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5874,21 +5868,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5898,10 +5892,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628661</v>
+        <v>628752</v>
       </c>
       <c r="R51" t="n">
-        <v>6978421</v>
+        <v>6978198</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5960,32 +5954,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302275</v>
+        <v>129302233</v>
       </c>
       <c r="B52" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5995,10 +5989,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628663</v>
+        <v>628759</v>
       </c>
       <c r="R52" t="n">
-        <v>6978428</v>
+        <v>6978233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6031,11 +6025,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6062,10 +6051,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129302276</v>
+        <v>129302275</v>
       </c>
       <c r="B53" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6097,10 +6086,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628648</v>
+        <v>628663</v>
       </c>
       <c r="R53" t="n">
-        <v>6978420</v>
+        <v>6978428</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6137,7 +6126,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>80 stycken</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6164,10 +6153,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129290084</v>
+        <v>129302276</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6192,21 +6181,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628475</v>
+        <v>628648</v>
       </c>
       <c r="R54" t="n">
-        <v>6978540</v>
+        <v>6978420</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6239,6 +6224,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6265,10 +6255,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129302231</v>
+        <v>129290169</v>
       </c>
       <c r="B55" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6276,34 +6266,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628752</v>
+        <v>628453</v>
       </c>
       <c r="R55" t="n">
-        <v>6978198</v>
+        <v>6978518</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6336,6 +6331,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,10 +6362,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302233</v>
+        <v>129296084</v>
       </c>
       <c r="B56" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628759</v>
+        <v>628959</v>
       </c>
       <c r="R56" t="n">
-        <v>6978233</v>
+        <v>6978530</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129295935</v>
+        <v>129302241</v>
       </c>
       <c r="B57" t="n">
-        <v>91559</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6470,21 +6470,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628907</v>
+        <v>628741</v>
       </c>
       <c r="R57" t="n">
-        <v>6978423</v>
+        <v>6978271</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6530,6 +6530,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6556,45 +6561,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129302274</v>
+        <v>129293780</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57719</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628659</v>
+        <v>628680</v>
       </c>
       <c r="R58" t="n">
-        <v>6978419</v>
+        <v>6978235</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,10 +6667,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302241</v>
+        <v>129302274</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6664,21 +6678,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6688,10 +6702,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628741</v>
+        <v>628659</v>
       </c>
       <c r="R59" t="n">
-        <v>6978271</v>
+        <v>6978419</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6724,11 +6738,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6755,10 +6764,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129302252</v>
+        <v>129295935</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>91563</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6766,21 +6775,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6799,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628837</v>
+        <v>628907</v>
       </c>
       <c r="R60" t="n">
-        <v>6978500</v>
+        <v>6978423</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6826,11 +6835,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6857,45 +6861,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302271</v>
+        <v>129294015</v>
       </c>
       <c r="B61" t="n">
-        <v>97583</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628763</v>
+        <v>628728</v>
       </c>
       <c r="R61" t="n">
-        <v>6978273</v>
+        <v>6978173</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6954,10 +6958,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129294015</v>
+        <v>129302229</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6965,34 +6969,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628728</v>
+        <v>628761</v>
       </c>
       <c r="R62" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7051,54 +7055,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129293780</v>
+        <v>129302252</v>
       </c>
       <c r="B63" t="n">
-        <v>57719</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100110</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628680</v>
+        <v>628837</v>
       </c>
       <c r="R63" t="n">
-        <v>6978235</v>
+        <v>6978500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7131,6 +7126,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7157,32 +7157,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302229</v>
+        <v>129302271</v>
       </c>
       <c r="B64" t="n">
-        <v>91545</v>
+        <v>97587</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7192,10 +7192,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628761</v>
+        <v>628763</v>
       </c>
       <c r="R64" t="n">
-        <v>6978157</v>
+        <v>6978273</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7254,10 +7254,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129295162</v>
+        <v>129290108</v>
       </c>
       <c r="B65" t="n">
-        <v>91998</v>
+        <v>98716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7265,34 +7265,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628834</v>
+        <v>628447</v>
       </c>
       <c r="R65" t="n">
-        <v>6978251</v>
+        <v>6978522</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7351,32 +7355,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129292729</v>
+        <v>129302250</v>
       </c>
       <c r="B66" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7386,10 +7390,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628599</v>
+        <v>628495</v>
       </c>
       <c r="R66" t="n">
-        <v>6978448</v>
+        <v>6978647</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7422,6 +7426,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7448,32 +7457,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129291635</v>
+        <v>129302244</v>
       </c>
       <c r="B67" t="n">
-        <v>96046</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7483,10 +7492,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628573</v>
+        <v>628756</v>
       </c>
       <c r="R67" t="n">
-        <v>6978423</v>
+        <v>6978337</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7519,6 +7528,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7545,45 +7559,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129294000</v>
+        <v>129295162</v>
       </c>
       <c r="B68" t="n">
-        <v>91545</v>
+        <v>92002</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628687</v>
+        <v>628834</v>
       </c>
       <c r="R68" t="n">
-        <v>6978194</v>
+        <v>6978251</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,54 +7656,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129297292</v>
+        <v>129292729</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628429</v>
+        <v>628599</v>
       </c>
       <c r="R69" t="n">
-        <v>6978625</v>
+        <v>6978448</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,32 +7753,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129302259</v>
+        <v>129294000</v>
       </c>
       <c r="B70" t="n">
-        <v>91998</v>
+        <v>91549</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7783,10 +7788,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628771</v>
+        <v>628687</v>
       </c>
       <c r="R70" t="n">
-        <v>6978154</v>
+        <v>6978194</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7848,7 +7853,7 @@
         <v>129291473</v>
       </c>
       <c r="B71" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,10 +7951,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129290108</v>
+        <v>129302259</v>
       </c>
       <c r="B72" t="n">
-        <v>98712</v>
+        <v>92002</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7957,38 +7962,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628447</v>
+        <v>628771</v>
       </c>
       <c r="R72" t="n">
-        <v>6978522</v>
+        <v>6978154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8047,32 +8048,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302250</v>
+        <v>129291635</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>96050</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8082,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628495</v>
+        <v>628573</v>
       </c>
       <c r="R73" t="n">
-        <v>6978647</v>
+        <v>6978423</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8118,11 +8119,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8149,7 +8145,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302244</v>
+        <v>129297292</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8177,17 +8173,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628756</v>
+        <v>628429</v>
       </c>
       <c r="R74" t="n">
-        <v>6978337</v>
+        <v>6978625</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8220,11 +8225,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8356,7 +8356,7 @@
         <v>129302280</v>
       </c>
       <c r="B76" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>129295124</v>
       </c>
       <c r="B77" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>129290447</v>
       </c>
       <c r="B79" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>129302227</v>
       </c>
       <c r="B80" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8853,49 +8853,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B81" t="n">
-        <v>98712</v>
+        <v>57724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R81" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8932,7 +8928,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8941,7 +8937,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8960,45 +8955,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302255</v>
+        <v>129302281</v>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628712</v>
+        <v>628688</v>
       </c>
       <c r="R82" t="n">
-        <v>6978376</v>
+        <v>6978441</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9035,7 +9034,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9044,6 +9043,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9256,45 +9256,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129294276</v>
+        <v>129293914</v>
       </c>
       <c r="B85" t="n">
-        <v>91758</v>
+        <v>57887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628790</v>
+        <v>628690</v>
       </c>
       <c r="R85" t="n">
-        <v>6978034</v>
+        <v>6978221</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,32 +9358,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129289873</v>
+        <v>129302232</v>
       </c>
       <c r="B86" t="n">
-        <v>91509</v>
+        <v>91549</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9388,10 +9393,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628447</v>
+        <v>628742</v>
       </c>
       <c r="R86" t="n">
-        <v>6978522</v>
+        <v>6978216</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,50 +9455,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129293890</v>
+        <v>129302260</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628691</v>
+        <v>628641</v>
       </c>
       <c r="R87" t="n">
-        <v>6978242</v>
+        <v>6978450</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9526,11 +9526,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9557,50 +9552,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129293914</v>
+        <v>129302258</v>
       </c>
       <c r="B88" t="n">
-        <v>57887</v>
+        <v>92002</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628690</v>
+        <v>628851</v>
       </c>
       <c r="R88" t="n">
-        <v>6978221</v>
+        <v>6978502</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9659,10 +9649,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302232</v>
+        <v>129302291</v>
       </c>
       <c r="B89" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9670,21 +9660,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9694,10 +9684,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628742</v>
+        <v>628794</v>
       </c>
       <c r="R89" t="n">
-        <v>6978216</v>
+        <v>6978373</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9756,45 +9746,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129302260</v>
+        <v>129293890</v>
       </c>
       <c r="B90" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628641</v>
+        <v>628691</v>
       </c>
       <c r="R90" t="n">
-        <v>6978450</v>
+        <v>6978242</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9827,6 +9822,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,32 +9853,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302258</v>
+        <v>129302267</v>
       </c>
       <c r="B91" t="n">
-        <v>91998</v>
+        <v>91847</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628851</v>
+        <v>628603</v>
       </c>
       <c r="R91" t="n">
         <v>6978502</v>
@@ -9950,10 +9950,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129302291</v>
+        <v>129302264</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9961,21 +9961,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628794</v>
+        <v>628796</v>
       </c>
       <c r="R92" t="n">
-        <v>6978373</v>
+        <v>6978261</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,45 +10047,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129292746</v>
+        <v>129294276</v>
       </c>
       <c r="B93" t="n">
-        <v>91843</v>
+        <v>91762</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628586</v>
+        <v>628790</v>
       </c>
       <c r="R93" t="n">
-        <v>6978451</v>
+        <v>6978034</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,10 +10144,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129290229</v>
+        <v>129292746</v>
       </c>
       <c r="B94" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628436</v>
+        <v>628586</v>
       </c>
       <c r="R94" t="n">
-        <v>6978498</v>
+        <v>6978451</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,32 +10241,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129296097</v>
+        <v>129290229</v>
       </c>
       <c r="B95" t="n">
-        <v>80178</v>
+        <v>91847</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628959</v>
+        <v>628436</v>
       </c>
       <c r="R95" t="n">
-        <v>6978530</v>
+        <v>6978498</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302267</v>
+        <v>129289873</v>
       </c>
       <c r="B96" t="n">
-        <v>91843</v>
+        <v>91513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628603</v>
+        <v>628447</v>
       </c>
       <c r="R96" t="n">
-        <v>6978502</v>
+        <v>6978522</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,32 +10435,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129302264</v>
+        <v>129296097</v>
       </c>
       <c r="B97" t="n">
-        <v>91843</v>
+        <v>80178</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628796</v>
+        <v>628959</v>
       </c>
       <c r="R97" t="n">
-        <v>6978261</v>
+        <v>6978530</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10535,7 +10535,7 @@
         <v>129293044</v>
       </c>
       <c r="B98" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10836,49 +10836,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129295651</v>
+        <v>129295020</v>
       </c>
       <c r="B101" t="n">
-        <v>98712</v>
+        <v>80184</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628796</v>
+        <v>628826</v>
       </c>
       <c r="R101" t="n">
-        <v>6978373</v>
+        <v>6978150</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10937,45 +10933,49 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129295020</v>
+        <v>129295651</v>
       </c>
       <c r="B102" t="n">
-        <v>80184</v>
+        <v>98716</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628826</v>
+        <v>628796</v>
       </c>
       <c r="R102" t="n">
-        <v>6978150</v>
+        <v>6978373</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11037,7 +11037,7 @@
         <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>129302282</v>
       </c>
       <c r="B104" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>129302287</v>
       </c>
       <c r="B105" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>129302268</v>
       </c>
       <c r="B106" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129293395</v>
+        <v>129293300</v>
       </c>
       <c r="B107" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,34 +11443,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628616</v>
+        <v>628665</v>
       </c>
       <c r="R107" t="n">
-        <v>6978368</v>
+        <v>6978376</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11503,6 +11508,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11529,10 +11539,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129289885</v>
+        <v>129293395</v>
       </c>
       <c r="B108" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11564,10 +11574,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628447</v>
+        <v>628616</v>
       </c>
       <c r="R108" t="n">
-        <v>6978522</v>
+        <v>6978368</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11626,10 +11636,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129302251</v>
+        <v>129289885</v>
       </c>
       <c r="B109" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11637,21 +11647,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11661,10 +11671,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628425</v>
+        <v>628447</v>
       </c>
       <c r="R109" t="n">
-        <v>6978621</v>
+        <v>6978522</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11697,11 +11707,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11830,7 +11835,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129293300</v>
+        <v>129302251</v>
       </c>
       <c r="B111" t="n">
         <v>57727</v>
@@ -11859,21 +11864,16 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628665</v>
+        <v>628425</v>
       </c>
       <c r="R111" t="n">
-        <v>6978376</v>
+        <v>6978621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11937,32 +11937,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302289</v>
+        <v>129293475</v>
       </c>
       <c r="B112" t="n">
-        <v>57719</v>
+        <v>91847</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100110</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628493</v>
+        <v>628623</v>
       </c>
       <c r="R112" t="n">
-        <v>6978648</v>
+        <v>6978341</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,11 +12008,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12039,32 +12034,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129302247</v>
+        <v>129295820</v>
       </c>
       <c r="B113" t="n">
-        <v>57727</v>
+        <v>92002</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12074,10 +12069,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>628749</v>
+        <v>628889</v>
       </c>
       <c r="R113" t="n">
-        <v>6978349</v>
+        <v>6978417</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,11 +12105,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12141,32 +12131,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129295820</v>
+        <v>129302289</v>
       </c>
       <c r="B114" t="n">
-        <v>91998</v>
+        <v>57719</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1209</v>
+        <v>100110</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12176,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628889</v>
+        <v>628493</v>
       </c>
       <c r="R114" t="n">
-        <v>6978417</v>
+        <v>6978648</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12212,6 +12202,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12238,10 +12233,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129293475</v>
+        <v>129302225</v>
       </c>
       <c r="B115" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12249,21 +12244,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12273,10 +12268,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628623</v>
+        <v>628856</v>
       </c>
       <c r="R115" t="n">
-        <v>6978341</v>
+        <v>6978527</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12335,10 +12330,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129302225</v>
+        <v>129302290</v>
       </c>
       <c r="B116" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12346,21 +12341,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12370,10 +12365,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628856</v>
+        <v>628712</v>
       </c>
       <c r="R116" t="n">
-        <v>6978527</v>
+        <v>6978591</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12432,10 +12427,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302290</v>
+        <v>129302247</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12443,21 +12438,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12467,10 +12462,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628712</v>
+        <v>628749</v>
       </c>
       <c r="R117" t="n">
-        <v>6978591</v>
+        <v>6978349</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12503,6 +12498,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12532,7 +12532,7 @@
         <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,32 +12631,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129294695</v>
+        <v>129295812</v>
       </c>
       <c r="B119" t="n">
-        <v>91998</v>
+        <v>91549</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628831</v>
+        <v>628900</v>
       </c>
       <c r="R119" t="n">
-        <v>6978180</v>
+        <v>6978416</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,10 +12728,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129302242</v>
+        <v>129302273</v>
       </c>
       <c r="B120" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12739,21 +12739,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628750</v>
+        <v>628878</v>
       </c>
       <c r="R120" t="n">
-        <v>6978284</v>
+        <v>6978535</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12799,11 +12799,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12830,32 +12825,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129297070</v>
+        <v>129302242</v>
       </c>
       <c r="B121" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12865,10 +12860,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628764</v>
+        <v>628750</v>
       </c>
       <c r="R121" t="n">
-        <v>6978591</v>
+        <v>6978284</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12901,6 +12896,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12927,32 +12927,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129295812</v>
+        <v>129294695</v>
       </c>
       <c r="B122" t="n">
-        <v>91545</v>
+        <v>92002</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12962,10 +12962,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628900</v>
+        <v>628831</v>
       </c>
       <c r="R122" t="n">
-        <v>6978416</v>
+        <v>6978180</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13024,54 +13024,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129293329</v>
+        <v>129297070</v>
       </c>
       <c r="B123" t="n">
-        <v>57724</v>
+        <v>92002</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628640</v>
+        <v>628764</v>
       </c>
       <c r="R123" t="n">
-        <v>6978364</v>
+        <v>6978591</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13130,45 +13121,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129302257</v>
+        <v>129293329</v>
       </c>
       <c r="B124" t="n">
-        <v>91998</v>
+        <v>57724</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628794</v>
+        <v>628640</v>
       </c>
       <c r="R124" t="n">
-        <v>6978311</v>
+        <v>6978364</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13227,32 +13227,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302273</v>
+        <v>129302257</v>
       </c>
       <c r="B125" t="n">
-        <v>80149</v>
+        <v>92002</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13262,10 +13262,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628878</v>
+        <v>628794</v>
       </c>
       <c r="R125" t="n">
-        <v>6978535</v>
+        <v>6978311</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13421,38 +13421,37 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129289677</v>
+        <v>129291461</v>
       </c>
       <c r="B127" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13461,10 +13460,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628484</v>
+        <v>628547</v>
       </c>
       <c r="R127" t="n">
-        <v>6978568</v>
+        <v>6978457</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13717,10 +13716,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129302239</v>
+        <v>129302296</v>
       </c>
       <c r="B130" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13728,21 +13727,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13752,10 +13751,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628747</v>
+        <v>628449</v>
       </c>
       <c r="R130" t="n">
-        <v>6978218</v>
+        <v>6978612</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13788,11 +13787,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13819,10 +13813,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129302296</v>
+        <v>129302239</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13830,21 +13824,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13854,10 +13848,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628449</v>
+        <v>628747</v>
       </c>
       <c r="R131" t="n">
-        <v>6978612</v>
+        <v>6978218</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13890,6 +13884,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13916,10 +13915,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129290523</v>
+        <v>129289677</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13927,16 +13926,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -13947,7 +13946,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13956,10 +13955,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628509</v>
+        <v>628484</v>
       </c>
       <c r="R132" t="n">
-        <v>6978510</v>
+        <v>6978568</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13992,11 +13991,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14023,37 +14017,38 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129291461</v>
+        <v>129290523</v>
       </c>
       <c r="B133" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14062,10 +14057,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628547</v>
+        <v>628509</v>
       </c>
       <c r="R133" t="n">
-        <v>6978457</v>
+        <v>6978510</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14098,6 +14093,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14127,7 +14127,7 @@
         <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129293208</v>
+        <v>129295655</v>
       </c>
       <c r="B136" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,16 +14329,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14346,22 +14346,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628695</v>
+        <v>628796</v>
       </c>
       <c r="R136" t="n">
-        <v>6978356</v>
+        <v>6978373</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14394,11 +14398,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14425,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129293275</v>
+        <v>129302228</v>
       </c>
       <c r="B137" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14436,39 +14435,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628693</v>
+        <v>628870</v>
       </c>
       <c r="R137" t="n">
-        <v>6978372</v>
+        <v>6978469</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14501,11 +14495,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14532,10 +14521,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129295655</v>
+        <v>129293208</v>
       </c>
       <c r="B138" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14543,16 +14532,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14560,26 +14549,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628796</v>
+        <v>628695</v>
       </c>
       <c r="R138" t="n">
-        <v>6978373</v>
+        <v>6978356</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14612,6 +14597,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14638,10 +14628,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129302228</v>
+        <v>129293275</v>
       </c>
       <c r="B139" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14649,34 +14639,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628870</v>
+        <v>628693</v>
       </c>
       <c r="R139" t="n">
-        <v>6978469</v>
+        <v>6978372</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14709,6 +14704,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14738,7 +14738,7 @@
         <v>129302288</v>
       </c>
       <c r="B140" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14837,10 +14837,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129290695</v>
+        <v>129302272</v>
       </c>
       <c r="B141" t="n">
-        <v>80185</v>
+        <v>97587</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14848,21 +14848,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14872,10 +14872,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628509</v>
+        <v>628641</v>
       </c>
       <c r="R141" t="n">
-        <v>6978440</v>
+        <v>6978450</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14934,32 +14934,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129291606</v>
+        <v>129290695</v>
       </c>
       <c r="B142" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14969,10 +14969,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628564</v>
+        <v>628509</v>
       </c>
       <c r="R142" t="n">
-        <v>6978436</v>
+        <v>6978440</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15031,10 +15031,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129293977</v>
+        <v>129291606</v>
       </c>
       <c r="B143" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15042,39 +15042,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628687</v>
+        <v>628564</v>
       </c>
       <c r="R143" t="n">
-        <v>6978194</v>
+        <v>6978436</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15107,11 +15102,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15141,7 +15131,7 @@
         <v>129302266</v>
       </c>
       <c r="B144" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15235,45 +15225,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129302272</v>
+        <v>129293977</v>
       </c>
       <c r="B145" t="n">
-        <v>97583</v>
+        <v>57727</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628641</v>
+        <v>628687</v>
       </c>
       <c r="R145" t="n">
-        <v>6978450</v>
+        <v>6978194</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15306,6 +15301,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15332,32 +15332,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129302261</v>
+        <v>129302285</v>
       </c>
       <c r="B146" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15367,10 +15367,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628794</v>
+        <v>628656</v>
       </c>
       <c r="R146" t="n">
-        <v>6978311</v>
+        <v>6978459</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15403,6 +15403,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15429,32 +15434,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302230</v>
+        <v>129302297</v>
       </c>
       <c r="B147" t="n">
-        <v>91545</v>
+        <v>100905</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15464,10 +15469,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628766</v>
+        <v>628720</v>
       </c>
       <c r="R147" t="n">
-        <v>6978195</v>
+        <v>6978591</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15526,10 +15531,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129302226</v>
+        <v>129295136</v>
       </c>
       <c r="B148" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15537,34 +15542,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628849</v>
+        <v>628799</v>
       </c>
       <c r="R148" t="n">
-        <v>6978507</v>
+        <v>6978234</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15623,32 +15628,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129302238</v>
+        <v>129295841</v>
       </c>
       <c r="B149" t="n">
-        <v>57727</v>
+        <v>91762</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15658,10 +15663,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628757</v>
+        <v>628889</v>
       </c>
       <c r="R149" t="n">
-        <v>6978192</v>
+        <v>6978417</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15694,11 +15699,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15725,10 +15725,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129302249</v>
+        <v>129295133</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15736,34 +15736,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628539</v>
+        <v>628788</v>
       </c>
       <c r="R150" t="n">
-        <v>6978526</v>
+        <v>6978227</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15796,11 +15796,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15827,45 +15822,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129295841</v>
+        <v>129295719</v>
       </c>
       <c r="B151" t="n">
-        <v>91758</v>
+        <v>80149</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628889</v>
+        <v>628846</v>
       </c>
       <c r="R151" t="n">
-        <v>6978417</v>
+        <v>6978364</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15924,45 +15919,49 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129295136</v>
+        <v>129290760</v>
       </c>
       <c r="B152" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628799</v>
+        <v>628499</v>
       </c>
       <c r="R152" t="n">
-        <v>6978234</v>
+        <v>6978448</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16021,10 +16020,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129295133</v>
+        <v>129302230</v>
       </c>
       <c r="B153" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16052,14 +16051,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628788</v>
+        <v>628766</v>
       </c>
       <c r="R153" t="n">
-        <v>6978227</v>
+        <v>6978195</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16118,10 +16117,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129295719</v>
+        <v>129302226</v>
       </c>
       <c r="B154" t="n">
-        <v>80149</v>
+        <v>91549</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16129,34 +16128,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628846</v>
+        <v>628849</v>
       </c>
       <c r="R154" t="n">
-        <v>6978364</v>
+        <v>6978507</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16215,49 +16214,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129290760</v>
+        <v>129302249</v>
       </c>
       <c r="B155" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628499</v>
+        <v>628539</v>
       </c>
       <c r="R155" t="n">
-        <v>6978448</v>
+        <v>6978526</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16290,6 +16285,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16316,10 +16316,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302292</v>
+        <v>129302238</v>
       </c>
       <c r="B156" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16327,21 +16327,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628819</v>
+        <v>628757</v>
       </c>
       <c r="R156" t="n">
-        <v>6978067</v>
+        <v>6978192</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,32 +16418,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302285</v>
+        <v>129302261</v>
       </c>
       <c r="B157" t="n">
-        <v>98712</v>
+        <v>91847</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16453,10 +16453,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628656</v>
+        <v>628794</v>
       </c>
       <c r="R157" t="n">
-        <v>6978459</v>
+        <v>6978311</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,11 +16489,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ca 53 stycken kan finnas mer.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16520,32 +16515,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302297</v>
+        <v>129302292</v>
       </c>
       <c r="B158" t="n">
-        <v>100901</v>
+        <v>79044</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16555,10 +16550,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628720</v>
+        <v>628819</v>
       </c>
       <c r="R158" t="n">
-        <v>6978591</v>
+        <v>6978067</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16591,6 +16586,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16620,7 +16620,7 @@
         <v>129290278</v>
       </c>
       <c r="B159" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16714,45 +16714,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129302234</v>
+        <v>129295735</v>
       </c>
       <c r="B160" t="n">
-        <v>91545</v>
+        <v>80184</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628641</v>
+        <v>628841</v>
       </c>
       <c r="R160" t="n">
-        <v>6978450</v>
+        <v>6978384</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16811,27 +16811,27 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129295735</v>
+        <v>129289808</v>
       </c>
       <c r="B161" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -16842,14 +16842,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628841</v>
+        <v>628421</v>
       </c>
       <c r="R161" t="n">
-        <v>6978384</v>
+        <v>6978541</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16908,10 +16908,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129289808</v>
+        <v>129302234</v>
       </c>
       <c r="B162" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16919,21 +16919,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628421</v>
+        <v>628641</v>
       </c>
       <c r="R162" t="n">
-        <v>6978541</v>
+        <v>6978450</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17105,7 +17105,7 @@
         <v>129302279</v>
       </c>
       <c r="B164" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,32 +2275,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129302237</v>
+        <v>129292781</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>92268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628766</v>
+        <v>628590</v>
       </c>
       <c r="R15" t="n">
-        <v>6978173</v>
+        <v>6978436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,11 +2346,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,32 +2372,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129302245</v>
+        <v>129295830</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>92268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628749</v>
+        <v>628896</v>
       </c>
       <c r="R16" t="n">
-        <v>6978341</v>
+        <v>6978430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,11 +2443,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129292781</v>
+        <v>129295766</v>
       </c>
       <c r="B17" t="n">
-        <v>92267</v>
+        <v>80178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,34 +2480,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628590</v>
+        <v>628846</v>
       </c>
       <c r="R17" t="n">
-        <v>6978436</v>
+        <v>6978364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2576,32 +2566,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129295830</v>
+        <v>129302237</v>
       </c>
       <c r="B18" t="n">
-        <v>92267</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2611,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628896</v>
+        <v>628766</v>
       </c>
       <c r="R18" t="n">
-        <v>6978430</v>
+        <v>6978173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,6 +2637,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,32 +2668,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302283</v>
+        <v>129302245</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2708,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628664</v>
+        <v>628749</v>
       </c>
       <c r="R19" t="n">
-        <v>6978446</v>
+        <v>6978341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2748,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>60 stycken kan finnas mer gömda i mossan</t>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,45 +2770,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129295766</v>
+        <v>129302283</v>
       </c>
       <c r="B20" t="n">
-        <v>80178</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>628846</v>
+        <v>628664</v>
       </c>
       <c r="R20" t="n">
-        <v>6978364</v>
+        <v>6978446</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,6 +2841,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>60 stycken kan finnas mer gömda i mossan</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,32 +2872,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302269</v>
+        <v>129302262</v>
       </c>
       <c r="B21" t="n">
-        <v>97587</v>
+        <v>91848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628792</v>
+        <v>628800</v>
       </c>
       <c r="R21" t="n">
-        <v>6978309</v>
+        <v>6978306</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294036</v>
+        <v>129302265</v>
       </c>
       <c r="B22" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,14 +3000,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628728</v>
+        <v>628772</v>
       </c>
       <c r="R22" t="n">
-        <v>6978173</v>
+        <v>6978157</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,32 +3066,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129290628</v>
+        <v>129293584</v>
       </c>
       <c r="B23" t="n">
-        <v>91847</v>
+        <v>92003</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628499</v>
+        <v>628624</v>
       </c>
       <c r="R23" t="n">
-        <v>6978448</v>
+        <v>6978328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,45 +3163,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129293584</v>
+        <v>129294036</v>
       </c>
       <c r="B24" t="n">
-        <v>92002</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628624</v>
+        <v>628728</v>
       </c>
       <c r="R24" t="n">
-        <v>6978328</v>
+        <v>6978173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129302243</v>
+        <v>129290628</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,21 +3271,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628743</v>
+        <v>628499</v>
       </c>
       <c r="R25" t="n">
-        <v>6978315</v>
+        <v>6978448</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,11 +3331,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,7 +3357,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129302240</v>
+        <v>129294050</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3391,16 +3386,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628764</v>
+        <v>628728</v>
       </c>
       <c r="R26" t="n">
-        <v>6978279</v>
+        <v>6978173</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,50 +3464,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294050</v>
+        <v>129292558</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628728</v>
+        <v>628589</v>
       </c>
       <c r="R27" t="n">
-        <v>6978173</v>
+        <v>6978414</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,11 +3539,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3571,10 +3565,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129292558</v>
+        <v>129302284</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3599,21 +3593,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628589</v>
+        <v>628667</v>
       </c>
       <c r="R28" t="n">
-        <v>6978414</v>
+        <v>6978461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3646,6 +3636,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3672,32 +3667,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302262</v>
+        <v>129302278</v>
       </c>
       <c r="B29" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3707,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628800</v>
+        <v>628894</v>
       </c>
       <c r="R29" t="n">
-        <v>6978306</v>
+        <v>6978483</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3743,6 +3738,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,32 +3769,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302265</v>
+        <v>129302269</v>
       </c>
       <c r="B30" t="n">
-        <v>91847</v>
+        <v>97595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628772</v>
+        <v>628792</v>
       </c>
       <c r="R30" t="n">
-        <v>6978157</v>
+        <v>6978309</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3866,32 +3866,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302284</v>
+        <v>129302243</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628667</v>
+        <v>628743</v>
       </c>
       <c r="R31" t="n">
-        <v>6978461</v>
+        <v>6978315</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,32 +3968,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302278</v>
+        <v>129302240</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628894</v>
+        <v>628764</v>
       </c>
       <c r="R32" t="n">
-        <v>6978483</v>
+        <v>6978279</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4073,7 +4073,7 @@
         <v>129290118</v>
       </c>
       <c r="B33" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,54 +4167,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129293171</v>
+        <v>129294218</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>96058</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628702</v>
+        <v>628798</v>
       </c>
       <c r="R34" t="n">
-        <v>6978339</v>
+        <v>6978072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4247,6 +4238,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4276,7 +4272,7 @@
         <v>129295187</v>
       </c>
       <c r="B35" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,45 +4366,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294218</v>
+        <v>129296183</v>
       </c>
       <c r="B36" t="n">
-        <v>96050</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>628798</v>
+        <v>629055</v>
       </c>
       <c r="R36" t="n">
-        <v>6978072</v>
+        <v>6978511</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,11 +4437,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4472,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129296183</v>
+        <v>129293171</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,34 +4474,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>629055</v>
+        <v>628702</v>
       </c>
       <c r="R37" t="n">
-        <v>6978511</v>
+        <v>6978339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129302293</v>
+        <v>129302235</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>628737</v>
+        <v>628629</v>
       </c>
       <c r="R38" t="n">
-        <v>6978300</v>
+        <v>6978532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129302235</v>
+        <v>129302293</v>
       </c>
       <c r="B39" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>628629</v>
+        <v>628737</v>
       </c>
       <c r="R39" t="n">
-        <v>6978532</v>
+        <v>6978300</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>129302277</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,10 +4865,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129302248</v>
+        <v>129291502</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4876,21 +4876,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628679</v>
+        <v>628564</v>
       </c>
       <c r="R41" t="n">
-        <v>6978469</v>
+        <v>6978436</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,11 +4936,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,45 +4962,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129291502</v>
+        <v>129290183</v>
       </c>
       <c r="B42" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628564</v>
+        <v>628436</v>
       </c>
       <c r="R42" t="n">
-        <v>6978436</v>
+        <v>6978498</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5064,10 +5063,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129294028</v>
+        <v>129302248</v>
       </c>
       <c r="B43" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5075,34 +5074,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628728</v>
+        <v>628679</v>
       </c>
       <c r="R43" t="n">
-        <v>6978173</v>
+        <v>6978469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,6 +5134,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5161,45 +5165,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293533</v>
+        <v>129294028</v>
       </c>
       <c r="B44" t="n">
-        <v>92002</v>
+        <v>91550</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628623</v>
+        <v>628728</v>
       </c>
       <c r="R44" t="n">
-        <v>6978341</v>
+        <v>6978173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5258,10 +5262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129290183</v>
+        <v>129293533</v>
       </c>
       <c r="B45" t="n">
-        <v>98716</v>
+        <v>92003</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5269,38 +5273,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628436</v>
+        <v>628623</v>
       </c>
       <c r="R45" t="n">
-        <v>6978498</v>
+        <v>6978341</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5465,49 +5465,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290084</v>
+        <v>129290616</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628475</v>
+        <v>628499</v>
       </c>
       <c r="R47" t="n">
-        <v>6978540</v>
+        <v>6978448</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5566,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129302294</v>
+        <v>129290361</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5577,21 +5573,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5601,10 +5597,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628661</v>
+        <v>628465</v>
       </c>
       <c r="R48" t="n">
-        <v>6978421</v>
+        <v>6978491</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5663,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290616</v>
+        <v>129296084</v>
       </c>
       <c r="B49" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5674,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5698,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628499</v>
+        <v>628959</v>
       </c>
       <c r="R49" t="n">
-        <v>6978448</v>
+        <v>6978530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5760,32 +5756,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290361</v>
+        <v>129302275</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5795,10 +5791,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628465</v>
+        <v>628663</v>
       </c>
       <c r="R50" t="n">
-        <v>6978491</v>
+        <v>6978428</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5831,6 +5827,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5857,32 +5858,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302231</v>
+        <v>129302276</v>
       </c>
       <c r="B51" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5892,10 +5893,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628752</v>
+        <v>628648</v>
       </c>
       <c r="R51" t="n">
-        <v>6978198</v>
+        <v>6978420</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5928,6 +5929,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5957,7 +5963,7 @@
         <v>129302233</v>
       </c>
       <c r="B52" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6051,32 +6057,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129302275</v>
+        <v>129302231</v>
       </c>
       <c r="B53" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6086,10 +6092,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>628663</v>
+        <v>628752</v>
       </c>
       <c r="R53" t="n">
-        <v>6978428</v>
+        <v>6978198</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6122,11 +6128,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6153,45 +6154,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129302276</v>
+        <v>129290169</v>
       </c>
       <c r="B54" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628648</v>
+        <v>628453</v>
       </c>
       <c r="R54" t="n">
-        <v>6978420</v>
+        <v>6978518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6228,7 +6234,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>80 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6255,38 +6261,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129290169</v>
+        <v>129290084</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6295,10 +6300,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628453</v>
+        <v>628475</v>
       </c>
       <c r="R55" t="n">
-        <v>6978518</v>
+        <v>6978540</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6331,11 +6336,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,10 +6362,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129296084</v>
+        <v>129302294</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628959</v>
+        <v>628661</v>
       </c>
       <c r="R56" t="n">
-        <v>6978530</v>
+        <v>6978421</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129302241</v>
+        <v>129295935</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6470,21 +6470,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>628741</v>
+        <v>628907</v>
       </c>
       <c r="R57" t="n">
-        <v>6978271</v>
+        <v>6978423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6530,11 +6530,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6561,54 +6556,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B58" t="n">
-        <v>57719</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R58" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6667,45 +6653,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129302274</v>
+        <v>129293780</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>57719</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628659</v>
+        <v>628680</v>
       </c>
       <c r="R59" t="n">
-        <v>6978419</v>
+        <v>6978235</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6764,10 +6759,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129295935</v>
+        <v>129302274</v>
       </c>
       <c r="B60" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6775,21 +6770,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>628907</v>
+        <v>628659</v>
       </c>
       <c r="R60" t="n">
-        <v>6978423</v>
+        <v>6978419</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6861,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129294015</v>
+        <v>129302252</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6872,34 +6867,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628728</v>
+        <v>628837</v>
       </c>
       <c r="R61" t="n">
-        <v>6978173</v>
+        <v>6978500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,6 +6927,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,32 +6958,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302229</v>
+        <v>129302271</v>
       </c>
       <c r="B62" t="n">
-        <v>91549</v>
+        <v>97595</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628761</v>
+        <v>628763</v>
       </c>
       <c r="R62" t="n">
-        <v>6978157</v>
+        <v>6978273</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7055,10 +7055,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302252</v>
+        <v>129302229</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>91550</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7066,21 +7066,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628837</v>
+        <v>628761</v>
       </c>
       <c r="R63" t="n">
-        <v>6978500</v>
+        <v>6978157</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7126,11 +7126,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7157,32 +7152,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302271</v>
+        <v>129302241</v>
       </c>
       <c r="B64" t="n">
-        <v>97587</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7192,10 +7187,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628763</v>
+        <v>628741</v>
       </c>
       <c r="R64" t="n">
-        <v>6978273</v>
+        <v>6978271</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7228,6 +7223,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7254,37 +7254,42 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129290108</v>
+        <v>129297292</v>
       </c>
       <c r="B65" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7293,10 +7298,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628447</v>
+        <v>628429</v>
       </c>
       <c r="R65" t="n">
-        <v>6978522</v>
+        <v>6978625</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7355,32 +7360,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129302250</v>
+        <v>129302259</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>92003</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7390,10 +7395,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628495</v>
+        <v>628771</v>
       </c>
       <c r="R66" t="n">
-        <v>6978647</v>
+        <v>6978154</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,11 +7431,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7457,45 +7457,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129302244</v>
+        <v>129295162</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>92003</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>628756</v>
+        <v>628834</v>
       </c>
       <c r="R67" t="n">
-        <v>6978337</v>
+        <v>6978251</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7528,11 +7528,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7559,10 +7554,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129295162</v>
+        <v>129292729</v>
       </c>
       <c r="B68" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7590,14 +7585,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>628834</v>
+        <v>628599</v>
       </c>
       <c r="R68" t="n">
-        <v>6978251</v>
+        <v>6978448</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7656,10 +7651,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129292729</v>
+        <v>129291635</v>
       </c>
       <c r="B69" t="n">
-        <v>92002</v>
+        <v>96058</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7667,21 +7662,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>1079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7691,10 +7686,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628599</v>
+        <v>628573</v>
       </c>
       <c r="R69" t="n">
-        <v>6978448</v>
+        <v>6978423</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7756,7 +7751,7 @@
         <v>129294000</v>
       </c>
       <c r="B70" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,10 +7845,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129291473</v>
+        <v>129290108</v>
       </c>
       <c r="B71" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7880,7 +7875,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7889,10 +7884,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>628549</v>
+        <v>628447</v>
       </c>
       <c r="R71" t="n">
-        <v>6978449</v>
+        <v>6978522</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7951,32 +7946,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302259</v>
+        <v>129302254</v>
       </c>
       <c r="B72" t="n">
-        <v>92002</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7986,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628771</v>
+        <v>628894</v>
       </c>
       <c r="R72" t="n">
-        <v>6978154</v>
+        <v>6978096</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8022,6 +8017,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8048,32 +8048,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129291635</v>
+        <v>129302250</v>
       </c>
       <c r="B73" t="n">
-        <v>96050</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628573</v>
+        <v>628495</v>
       </c>
       <c r="R73" t="n">
-        <v>6978423</v>
+        <v>6978647</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8119,6 +8119,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8145,7 +8150,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129297292</v>
+        <v>129302244</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8173,26 +8178,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628429</v>
+        <v>628756</v>
       </c>
       <c r="R74" t="n">
-        <v>6978625</v>
+        <v>6978337</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,6 +8221,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8251,32 +8252,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302254</v>
+        <v>129302280</v>
       </c>
       <c r="B75" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8286,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628894</v>
+        <v>628692</v>
       </c>
       <c r="R75" t="n">
-        <v>6978096</v>
+        <v>6978432</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,7 +8327,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8353,10 +8354,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129302280</v>
+        <v>129291473</v>
       </c>
       <c r="B76" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8381,17 +8382,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628692</v>
+        <v>628549</v>
       </c>
       <c r="R76" t="n">
-        <v>6978432</v>
+        <v>6978449</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8424,11 +8429,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8455,45 +8455,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129295124</v>
+        <v>129302281</v>
       </c>
       <c r="B77" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628788</v>
+        <v>628688</v>
       </c>
       <c r="R77" t="n">
-        <v>6978227</v>
+        <v>6978441</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8528,12 +8532,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8552,50 +8562,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129289501</v>
+        <v>129290447</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628451</v>
+        <v>628494</v>
       </c>
       <c r="R78" t="n">
-        <v>6978596</v>
+        <v>6978496</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8628,11 +8633,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8659,45 +8659,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129290447</v>
+        <v>129295124</v>
       </c>
       <c r="B79" t="n">
-        <v>97587</v>
+        <v>91848</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>628494</v>
+        <v>628788</v>
       </c>
       <c r="R79" t="n">
-        <v>6978496</v>
+        <v>6978227</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8759,7 +8759,7 @@
         <v>129302227</v>
       </c>
       <c r="B80" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8853,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129302255</v>
+        <v>129289501</v>
       </c>
       <c r="B81" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8864,16 +8864,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8882,16 +8882,21 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>628712</v>
+        <v>628451</v>
       </c>
       <c r="R81" t="n">
-        <v>6978376</v>
+        <v>6978596</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8928,7 +8933,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Födosökande i träd. Flög iväg.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8955,49 +8960,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129302281</v>
+        <v>129302255</v>
       </c>
       <c r="B82" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>628688</v>
+        <v>628712</v>
       </c>
       <c r="R82" t="n">
-        <v>6978441</v>
+        <v>6978376</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9034,7 +9035,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+          <t>Födosökande i träd. Flög iväg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9043,7 +9044,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>129291441</v>
       </c>
       <c r="B83" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9256,50 +9256,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129293914</v>
+        <v>129296097</v>
       </c>
       <c r="B85" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628690</v>
+        <v>628959</v>
       </c>
       <c r="R85" t="n">
-        <v>6978221</v>
+        <v>6978530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9358,10 +9353,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302232</v>
+        <v>129302267</v>
       </c>
       <c r="B86" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9369,21 +9364,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9393,10 +9388,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628742</v>
+        <v>628603</v>
       </c>
       <c r="R86" t="n">
-        <v>6978216</v>
+        <v>6978502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9455,32 +9450,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302260</v>
+        <v>129302264</v>
       </c>
       <c r="B87" t="n">
-        <v>92002</v>
+        <v>91848</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9490,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628641</v>
+        <v>628796</v>
       </c>
       <c r="R87" t="n">
-        <v>6978450</v>
+        <v>6978261</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9552,10 +9547,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129302258</v>
+        <v>129294276</v>
       </c>
       <c r="B88" t="n">
-        <v>92002</v>
+        <v>91763</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,34 +9558,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628851</v>
+        <v>628790</v>
       </c>
       <c r="R88" t="n">
-        <v>6978502</v>
+        <v>6978034</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9649,10 +9644,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129302291</v>
+        <v>129292746</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9660,21 +9655,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9684,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628794</v>
+        <v>628586</v>
       </c>
       <c r="R89" t="n">
-        <v>6978373</v>
+        <v>6978451</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9746,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129293890</v>
+        <v>129290229</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9757,39 +9752,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628691</v>
+        <v>628436</v>
       </c>
       <c r="R90" t="n">
-        <v>6978242</v>
+        <v>6978498</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9822,11 +9812,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9853,32 +9838,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129302267</v>
+        <v>129289873</v>
       </c>
       <c r="B91" t="n">
-        <v>91847</v>
+        <v>91514</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9888,10 +9873,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628603</v>
+        <v>628447</v>
       </c>
       <c r="R91" t="n">
-        <v>6978502</v>
+        <v>6978522</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9950,10 +9935,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129302264</v>
+        <v>129293890</v>
       </c>
       <c r="B92" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9961,34 +9946,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628796</v>
+        <v>628691</v>
       </c>
       <c r="R92" t="n">
-        <v>6978261</v>
+        <v>6978242</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10021,6 +10011,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10047,45 +10042,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129294276</v>
+        <v>129293914</v>
       </c>
       <c r="B93" t="n">
-        <v>91762</v>
+        <v>57887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628790</v>
+        <v>628690</v>
       </c>
       <c r="R93" t="n">
-        <v>6978034</v>
+        <v>6978221</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,32 +10144,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129292746</v>
+        <v>129302260</v>
       </c>
       <c r="B94" t="n">
-        <v>91847</v>
+        <v>92003</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628586</v>
+        <v>628641</v>
       </c>
       <c r="R94" t="n">
-        <v>6978451</v>
+        <v>6978450</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,32 +10241,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129290229</v>
+        <v>129302258</v>
       </c>
       <c r="B95" t="n">
-        <v>91847</v>
+        <v>92003</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628436</v>
+        <v>628851</v>
       </c>
       <c r="R95" t="n">
-        <v>6978498</v>
+        <v>6978502</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129289873</v>
+        <v>129302232</v>
       </c>
       <c r="B96" t="n">
-        <v>91513</v>
+        <v>91550</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628447</v>
+        <v>628742</v>
       </c>
       <c r="R96" t="n">
-        <v>6978522</v>
+        <v>6978216</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10435,32 +10435,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129296097</v>
+        <v>129302291</v>
       </c>
       <c r="B97" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10470,10 +10470,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628959</v>
+        <v>628794</v>
       </c>
       <c r="R97" t="n">
-        <v>6978530</v>
+        <v>6978373</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10532,49 +10532,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129293044</v>
+        <v>129295410</v>
       </c>
       <c r="B98" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628662</v>
+        <v>628767</v>
       </c>
       <c r="R98" t="n">
-        <v>6978408</v>
+        <v>6978383</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10633,45 +10638,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129302295</v>
+        <v>129293044</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628463</v>
+        <v>628662</v>
       </c>
       <c r="R99" t="n">
-        <v>6978635</v>
+        <v>6978408</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10730,10 +10739,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129295410</v>
+        <v>129302295</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10741,43 +10750,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>628767</v>
+        <v>628463</v>
       </c>
       <c r="R100" t="n">
-        <v>6978383</v>
+        <v>6978635</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10836,45 +10836,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129295020</v>
+        <v>129302282</v>
       </c>
       <c r="B101" t="n">
-        <v>80184</v>
+        <v>98724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628826</v>
+        <v>628654</v>
       </c>
       <c r="R101" t="n">
-        <v>6978150</v>
+        <v>6978418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,6 +10907,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10933,10 +10938,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129295651</v>
+        <v>129302287</v>
       </c>
       <c r="B102" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10961,21 +10966,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628796</v>
+        <v>628649</v>
       </c>
       <c r="R102" t="n">
-        <v>6978373</v>
+        <v>6978449</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11008,6 +11009,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11037,7 +11043,7 @@
         <v>129302263</v>
       </c>
       <c r="B103" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11131,45 +11137,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129302282</v>
+        <v>129295020</v>
       </c>
       <c r="B104" t="n">
-        <v>98716</v>
+        <v>80184</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628654</v>
+        <v>628826</v>
       </c>
       <c r="R104" t="n">
-        <v>6978418</v>
+        <v>6978150</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11202,11 +11208,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11233,10 +11234,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129302287</v>
+        <v>129295651</v>
       </c>
       <c r="B105" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11261,17 +11262,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628649</v>
+        <v>628796</v>
       </c>
       <c r="R105" t="n">
-        <v>6978449</v>
+        <v>6978373</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11304,11 +11309,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11338,7 +11338,7 @@
         <v>129302268</v>
       </c>
       <c r="B106" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11432,10 +11432,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129293300</v>
+        <v>129293395</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11443,39 +11443,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>628665</v>
+        <v>628616</v>
       </c>
       <c r="R107" t="n">
-        <v>6978376</v>
+        <v>6978368</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11508,11 +11503,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11539,10 +11529,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129293395</v>
+        <v>129289885</v>
       </c>
       <c r="B108" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11574,10 +11564,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>628616</v>
+        <v>628447</v>
       </c>
       <c r="R108" t="n">
-        <v>6978368</v>
+        <v>6978522</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11636,10 +11626,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129289885</v>
+        <v>129293300</v>
       </c>
       <c r="B109" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11647,34 +11637,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628447</v>
+        <v>628665</v>
       </c>
       <c r="R109" t="n">
-        <v>6978522</v>
+        <v>6978376</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11707,6 +11702,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129293475</v>
+        <v>129302225</v>
       </c>
       <c r="B112" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628623</v>
+        <v>628856</v>
       </c>
       <c r="R112" t="n">
-        <v>6978341</v>
+        <v>6978527</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
         <v>129295820</v>
       </c>
       <c r="B113" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12131,32 +12131,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129302289</v>
+        <v>129293475</v>
       </c>
       <c r="B114" t="n">
-        <v>57719</v>
+        <v>91848</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100110</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628493</v>
+        <v>628623</v>
       </c>
       <c r="R114" t="n">
-        <v>6978648</v>
+        <v>6978341</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,11 +12202,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12233,10 +12228,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302225</v>
+        <v>129302290</v>
       </c>
       <c r="B115" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12244,21 +12239,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12268,10 +12263,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628856</v>
+        <v>628712</v>
       </c>
       <c r="R115" t="n">
-        <v>6978527</v>
+        <v>6978591</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12330,10 +12325,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129302290</v>
+        <v>129302247</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12341,21 +12336,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12365,10 +12360,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628712</v>
+        <v>628749</v>
       </c>
       <c r="R116" t="n">
-        <v>6978591</v>
+        <v>6978349</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12401,6 +12396,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12427,32 +12427,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302247</v>
+        <v>129302289</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628749</v>
+        <v>628493</v>
       </c>
       <c r="R117" t="n">
-        <v>6978349</v>
+        <v>6978648</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12532,7 +12532,7 @@
         <v>129302256</v>
       </c>
       <c r="B118" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12631,32 +12631,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129295812</v>
+        <v>129294695</v>
       </c>
       <c r="B119" t="n">
-        <v>91549</v>
+        <v>92003</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628900</v>
+        <v>628831</v>
       </c>
       <c r="R119" t="n">
-        <v>6978416</v>
+        <v>6978180</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,32 +12728,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129302273</v>
+        <v>129297070</v>
       </c>
       <c r="B120" t="n">
-        <v>80149</v>
+        <v>92003</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628878</v>
+        <v>628764</v>
       </c>
       <c r="R120" t="n">
-        <v>6978535</v>
+        <v>6978591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129302242</v>
+        <v>129295812</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12836,34 +12836,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628750</v>
+        <v>628900</v>
       </c>
       <c r="R121" t="n">
-        <v>6978284</v>
+        <v>6978416</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12896,11 +12896,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12927,45 +12922,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129294695</v>
+        <v>129293329</v>
       </c>
       <c r="B122" t="n">
-        <v>92002</v>
+        <v>57724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628831</v>
+        <v>628640</v>
       </c>
       <c r="R122" t="n">
-        <v>6978180</v>
+        <v>6978364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13024,10 +13028,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129297070</v>
+        <v>129302257</v>
       </c>
       <c r="B123" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13059,10 +13063,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628764</v>
+        <v>628794</v>
       </c>
       <c r="R123" t="n">
-        <v>6978591</v>
+        <v>6978311</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13121,10 +13125,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129293329</v>
+        <v>129302273</v>
       </c>
       <c r="B124" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13132,43 +13136,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628640</v>
+        <v>628878</v>
       </c>
       <c r="R124" t="n">
-        <v>6978364</v>
+        <v>6978535</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13227,32 +13222,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129302257</v>
+        <v>129302242</v>
       </c>
       <c r="B125" t="n">
-        <v>92002</v>
+        <v>57727</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13262,10 +13257,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628794</v>
+        <v>628750</v>
       </c>
       <c r="R125" t="n">
-        <v>6978311</v>
+        <v>6978284</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13298,6 +13293,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13421,37 +13421,38 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129291461</v>
+        <v>129289677</v>
       </c>
       <c r="B127" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13460,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628547</v>
+        <v>628484</v>
       </c>
       <c r="R127" t="n">
-        <v>6978457</v>
+        <v>6978568</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13522,45 +13523,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290692</v>
+        <v>129290523</v>
       </c>
       <c r="B128" t="n">
-        <v>80109</v>
+        <v>57727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628515</v>
+        <v>628509</v>
       </c>
       <c r="R128" t="n">
-        <v>6978451</v>
+        <v>6978510</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13593,6 +13599,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13619,45 +13630,49 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129294090</v>
+        <v>129291461</v>
       </c>
       <c r="B129" t="n">
-        <v>80109</v>
+        <v>98724</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628743</v>
+        <v>628547</v>
       </c>
       <c r="R129" t="n">
-        <v>6978155</v>
+        <v>6978457</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13716,32 +13731,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129302296</v>
+        <v>129290692</v>
       </c>
       <c r="B130" t="n">
-        <v>79044</v>
+        <v>80109</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13751,10 +13766,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628449</v>
+        <v>628515</v>
       </c>
       <c r="R130" t="n">
-        <v>6978612</v>
+        <v>6978451</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13813,45 +13828,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129302239</v>
+        <v>129294090</v>
       </c>
       <c r="B131" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628747</v>
+        <v>628743</v>
       </c>
       <c r="R131" t="n">
-        <v>6978218</v>
+        <v>6978155</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13884,11 +13899,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13915,10 +13925,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129289677</v>
+        <v>129302296</v>
       </c>
       <c r="B132" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13926,39 +13936,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628484</v>
+        <v>628449</v>
       </c>
       <c r="R132" t="n">
-        <v>6978568</v>
+        <v>6978612</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14017,7 +14022,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129290523</v>
+        <v>129302239</v>
       </c>
       <c r="B133" t="n">
         <v>57727</v>
@@ -14046,21 +14051,16 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628509</v>
+        <v>628747</v>
       </c>
       <c r="R133" t="n">
-        <v>6978510</v>
+        <v>6978218</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14127,7 +14127,7 @@
         <v>129302270</v>
       </c>
       <c r="B134" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14221,10 +14221,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129294072</v>
+        <v>129302228</v>
       </c>
       <c r="B135" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14232,34 +14232,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628731</v>
+        <v>628870</v>
       </c>
       <c r="R135" t="n">
-        <v>6978165</v>
+        <v>6978469</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14424,10 +14424,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129302228</v>
+        <v>129294072</v>
       </c>
       <c r="B137" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14435,34 +14435,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628870</v>
+        <v>628731</v>
       </c>
       <c r="R137" t="n">
-        <v>6978469</v>
+        <v>6978165</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14735,32 +14735,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129302288</v>
+        <v>129302266</v>
       </c>
       <c r="B140" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628636</v>
+        <v>628639</v>
       </c>
       <c r="R140" t="n">
-        <v>6978511</v>
+        <v>6978441</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14806,11 +14806,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14837,10 +14832,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129302272</v>
+        <v>129290695</v>
       </c>
       <c r="B141" t="n">
-        <v>97587</v>
+        <v>80185</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14848,21 +14843,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14872,10 +14867,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628641</v>
+        <v>628509</v>
       </c>
       <c r="R141" t="n">
-        <v>6978450</v>
+        <v>6978440</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14934,32 +14929,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129290695</v>
+        <v>129291606</v>
       </c>
       <c r="B142" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14969,10 +14964,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628509</v>
+        <v>628564</v>
       </c>
       <c r="R142" t="n">
-        <v>6978440</v>
+        <v>6978436</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15031,10 +15026,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129291606</v>
+        <v>129293977</v>
       </c>
       <c r="B143" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15042,34 +15037,39 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628564</v>
+        <v>628687</v>
       </c>
       <c r="R143" t="n">
-        <v>6978436</v>
+        <v>6978194</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15102,6 +15102,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15128,32 +15133,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129302266</v>
+        <v>129302288</v>
       </c>
       <c r="B144" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15163,10 +15168,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628639</v>
+        <v>628636</v>
       </c>
       <c r="R144" t="n">
-        <v>6978441</v>
+        <v>6978511</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15199,6 +15204,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15225,50 +15235,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129293977</v>
+        <v>129302272</v>
       </c>
       <c r="B145" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628687</v>
+        <v>628641</v>
       </c>
       <c r="R145" t="n">
-        <v>6978194</v>
+        <v>6978450</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15301,11 +15306,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15335,7 +15335,7 @@
         <v>129302285</v>
       </c>
       <c r="B146" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15434,45 +15434,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129302297</v>
+        <v>129295136</v>
       </c>
       <c r="B147" t="n">
-        <v>100905</v>
+        <v>91848</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>628720</v>
+        <v>628799</v>
       </c>
       <c r="R147" t="n">
-        <v>6978591</v>
+        <v>6978234</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15531,45 +15531,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129295136</v>
+        <v>129295841</v>
       </c>
       <c r="B148" t="n">
-        <v>91847</v>
+        <v>91763</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628799</v>
+        <v>628889</v>
       </c>
       <c r="R148" t="n">
-        <v>6978234</v>
+        <v>6978417</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15628,45 +15628,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129295841</v>
+        <v>129295133</v>
       </c>
       <c r="B149" t="n">
-        <v>91762</v>
+        <v>91550</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628889</v>
+        <v>628788</v>
       </c>
       <c r="R149" t="n">
-        <v>6978417</v>
+        <v>6978227</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15725,45 +15725,49 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129295133</v>
+        <v>129290760</v>
       </c>
       <c r="B150" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>628788</v>
+        <v>628499</v>
       </c>
       <c r="R150" t="n">
-        <v>6978227</v>
+        <v>6978448</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15822,10 +15826,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129295719</v>
+        <v>129302226</v>
       </c>
       <c r="B151" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15833,34 +15837,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>628846</v>
+        <v>628849</v>
       </c>
       <c r="R151" t="n">
-        <v>6978364</v>
+        <v>6978507</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15919,49 +15923,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129290760</v>
+        <v>129302230</v>
       </c>
       <c r="B152" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628499</v>
+        <v>628766</v>
       </c>
       <c r="R152" t="n">
-        <v>6978448</v>
+        <v>6978195</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16020,32 +16020,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129302230</v>
+        <v>129302297</v>
       </c>
       <c r="B153" t="n">
-        <v>91549</v>
+        <v>100913</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16055,10 +16055,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628766</v>
+        <v>628720</v>
       </c>
       <c r="R153" t="n">
-        <v>6978195</v>
+        <v>6978591</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16117,10 +16117,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129302226</v>
+        <v>129295719</v>
       </c>
       <c r="B154" t="n">
-        <v>91549</v>
+        <v>80149</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16128,34 +16128,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628849</v>
+        <v>628846</v>
       </c>
       <c r="R154" t="n">
-        <v>6978507</v>
+        <v>6978364</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16214,10 +16214,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129302249</v>
+        <v>129302261</v>
       </c>
       <c r="B155" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16225,21 +16225,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16249,10 +16249,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628539</v>
+        <v>628794</v>
       </c>
       <c r="R155" t="n">
-        <v>6978526</v>
+        <v>6978311</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16285,11 +16285,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16316,10 +16311,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129302238</v>
+        <v>129302292</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16327,21 +16322,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16351,10 +16346,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628757</v>
+        <v>628819</v>
       </c>
       <c r="R156" t="n">
-        <v>6978192</v>
+        <v>6978067</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16391,7 +16386,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,10 +16413,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129302261</v>
+        <v>129302249</v>
       </c>
       <c r="B157" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16429,21 +16424,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16453,10 +16448,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628794</v>
+        <v>628539</v>
       </c>
       <c r="R157" t="n">
-        <v>6978311</v>
+        <v>6978526</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16489,6 +16484,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16515,10 +16515,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129302292</v>
+        <v>129302238</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16526,21 +16526,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628819</v>
+        <v>628757</v>
       </c>
       <c r="R158" t="n">
-        <v>6978067</v>
+        <v>6978192</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16617,32 +16617,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129290278</v>
+        <v>129302234</v>
       </c>
       <c r="B159" t="n">
-        <v>92002</v>
+        <v>91550</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16652,10 +16652,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628451</v>
+        <v>628641</v>
       </c>
       <c r="R159" t="n">
-        <v>6978495</v>
+        <v>6978450</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16714,45 +16714,45 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129295735</v>
+        <v>129290278</v>
       </c>
       <c r="B160" t="n">
-        <v>80184</v>
+        <v>92003</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628841</v>
+        <v>628451</v>
       </c>
       <c r="R160" t="n">
-        <v>6978384</v>
+        <v>6978495</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16908,45 +16908,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129302234</v>
+        <v>129295735</v>
       </c>
       <c r="B162" t="n">
-        <v>91549</v>
+        <v>80184</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628641</v>
+        <v>628841</v>
       </c>
       <c r="R162" t="n">
-        <v>6978450</v>
+        <v>6978384</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17005,32 +17005,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129302253</v>
+        <v>129302279</v>
       </c>
       <c r="B163" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17040,10 +17040,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628759</v>
+        <v>628884</v>
       </c>
       <c r="R163" t="n">
-        <v>6978235</v>
+        <v>6978488</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17076,6 +17076,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17102,32 +17107,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129302279</v>
+        <v>129302253</v>
       </c>
       <c r="B164" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17137,10 +17142,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628884</v>
+        <v>628759</v>
       </c>
       <c r="R164" t="n">
-        <v>6978488</v>
+        <v>6978235</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17173,11 +17178,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>6 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">

--- a/artfynd/A 45998-2025 artfynd.xlsx
+++ b/artfynd/A 45998-2025 artfynd.xlsx
@@ -2275,32 +2275,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129292781</v>
+        <v>129302237</v>
       </c>
       <c r="B15" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628590</v>
+        <v>628766</v>
       </c>
       <c r="R15" t="n">
-        <v>6978436</v>
+        <v>6978173</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,6 +2346,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,32 +2377,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129295830</v>
+        <v>129302245</v>
       </c>
       <c r="B16" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628896</v>
+        <v>628749</v>
       </c>
       <c r="R16" t="n">
-        <v>6978430</v>
+        <v>6978341</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,6 +2448,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129295766</v>
+        <v>129292781</v>
       </c>
       <c r="B17" t="n">
-        <v>80178</v>
+        <v>92268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,34 +2490,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628846</v>
+        <v>628590</v>
       </c>
       <c r="R17" t="n">
-        <v>6978364</v>
+        <v>6978436</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,32 +2576,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129302237</v>
+        <v>129295830</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>92268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2601,10 +2611,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628766</v>
+        <v>628896</v>
       </c>
       <c r="R18" t="n">
-        <v>6978173</v>
+        <v>6978430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,11 +2647,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,45 +2673,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129302245</v>
+        <v>129295766</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>628749</v>
+        <v>628846</v>
       </c>
       <c r="R19" t="n">
-        <v>6978341</v>
+        <v>6978364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,11 +2744,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran. Färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129302262</v>
+        <v>129294050</v>
       </c>
       <c r="B21" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,34 +2883,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>628800</v>
+        <v>628728</v>
       </c>
       <c r="R21" t="n">
-        <v>6978306</v>
+        <v>6978173</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,6 +2948,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,45 +2979,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129302265</v>
+        <v>129292558</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>628772</v>
+        <v>628589</v>
       </c>
       <c r="R22" t="n">
-        <v>6978157</v>
+        <v>6978414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,45 +3080,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129293584</v>
+        <v>129294036</v>
       </c>
       <c r="B23" t="n">
-        <v>92003</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>628624</v>
+        <v>628728</v>
       </c>
       <c r="R23" t="n">
-        <v>6978328</v>
+        <v>6978173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3177,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294036</v>
+        <v>129290628</v>
       </c>
       <c r="B24" t="n">
         <v>91848</v>
@@ -3194,14 +3208,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>628728</v>
+        <v>628499</v>
       </c>
       <c r="R24" t="n">
-        <v>6978173</v>
+        <v>6978448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,32 +3274,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129290628</v>
+        <v>129293584</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>92003</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>628499</v>
+        <v>628624</v>
       </c>
       <c r="R25" t="n">
-        <v>6978448</v>
+        <v>6978328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3357,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294050</v>
+        <v>129302262</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,39 +3382,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>628728</v>
+        <v>628800</v>
       </c>
       <c r="R26" t="n">
-        <v>6978173</v>
+        <v>6978306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,11 +3442,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,49 +3468,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129292558</v>
+        <v>129302265</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>628589</v>
+        <v>628772</v>
       </c>
       <c r="R27" t="n">
-        <v>6978414</v>
+        <v>6978157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,32 +3565,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129302284</v>
+        <v>129302243</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3600,10 +3600,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>628667</v>
+        <v>628743</v>
       </c>
       <c r="R28" t="n">
-        <v>6978461</v>
+        <v>6978315</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3667,32 +3667,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129302278</v>
+        <v>129302240</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3702,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>628894</v>
+        <v>628764</v>
       </c>
       <c r="R29" t="n">
-        <v>6978483</v>
+        <v>6978279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,32 +3769,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129302269</v>
+        <v>129302284</v>
       </c>
       <c r="B30" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>628792</v>
+        <v>628667</v>
       </c>
       <c r="R30" t="n">
-        <v>6978309</v>
+        <v>6978461</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,6 +3840,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3866,32 +3871,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129302243</v>
+        <v>129302278</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3906,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>628743</v>
+        <v>628894</v>
       </c>
       <c r="R31" t="n">
-        <v>6978315</v>
+        <v>6978483</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,7 +3946,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett, fäska spår på tall.</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,32 +3973,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129302240</v>
+        <v>129302269</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>97595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4003,10 +4008,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>628764</v>
+        <v>628792</v>
       </c>
       <c r="R32" t="n">
-        <v>6978279</v>
+        <v>6978309</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4039,11 +4044,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,10 +4070,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129290118</v>
+        <v>129295187</v>
       </c>
       <c r="B33" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>628453</v>
+        <v>628834</v>
       </c>
       <c r="R33" t="n">
-        <v>6978518</v>
+        <v>6978251</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,45 +4167,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129294218</v>
+        <v>129290118</v>
       </c>
       <c r="B34" t="n">
-        <v>96058</v>
+        <v>91550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1079</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>628798</v>
+        <v>628453</v>
       </c>
       <c r="R34" t="n">
-        <v>6978072</v>
+        <v>6978518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,11 +4238,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4269,32 +4264,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295187</v>
+        <v>129294218</v>
       </c>
       <c r="B35" t="n">
-        <v>91848</v>
+        <v>96058</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>1079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4304,10 +4299,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>628834</v>
+        <v>628798</v>
       </c>
       <c r="R35" t="n">
-        <v>6978251</v>
+        <v>6978072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4340,6 +4335,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4366,10 +4366,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129296183</v>
+        <v>129293171</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,34 +4377,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>629055</v>
+        <v>628702</v>
       </c>
       <c r="R36" t="n">
-        <v>6978511</v>
+        <v>6978339</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,10 +4472,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293171</v>
+        <v>129296183</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,43 +4483,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>628702</v>
+        <v>629055</v>
       </c>
       <c r="R37" t="n">
-        <v>6978339</v>
+        <v>6978511</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4865,32 +4865,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129291502</v>
+        <v>129293533</v>
       </c>
       <c r="B41" t="n">
-        <v>91848</v>
+        <v>92003</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>628564</v>
+        <v>628623</v>
       </c>
       <c r="R41" t="n">
-        <v>6978436</v>
+        <v>6978341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4962,49 +4962,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129290183</v>
+        <v>129294028</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>628436</v>
+        <v>628728</v>
       </c>
       <c r="R42" t="n">
-        <v>6978498</v>
+        <v>6978173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5063,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129302248</v>
+        <v>129291502</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5074,21 +5070,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5098,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>628679</v>
+        <v>628564</v>
       </c>
       <c r="R43" t="n">
-        <v>6978469</v>
+        <v>6978436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5134,11 +5130,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5165,10 +5156,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129294028</v>
+        <v>129296072</v>
       </c>
       <c r="B44" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5176,34 +5167,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>628728</v>
+        <v>628971</v>
       </c>
       <c r="R44" t="n">
-        <v>6978173</v>
+        <v>6978518</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,10 +5262,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293533</v>
+        <v>129290183</v>
       </c>
       <c r="B45" t="n">
-        <v>92003</v>
+        <v>98724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5273,34 +5273,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>628623</v>
+        <v>628436</v>
       </c>
       <c r="R45" t="n">
-        <v>6978341</v>
+        <v>6978498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5359,7 +5363,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129296072</v>
+        <v>129302248</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5387,26 +5391,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>628971</v>
+        <v>628679</v>
       </c>
       <c r="R46" t="n">
-        <v>6978518</v>
+        <v>6978469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5439,6 +5434,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall, intill slutning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5465,45 +5465,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129290616</v>
+        <v>129290084</v>
       </c>
       <c r="B47" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>628499</v>
+        <v>628475</v>
       </c>
       <c r="R47" t="n">
-        <v>6978448</v>
+        <v>6978540</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,7 +5566,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129290361</v>
+        <v>129290616</v>
       </c>
       <c r="B48" t="n">
         <v>91550</v>
@@ -5597,10 +5601,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>628465</v>
+        <v>628499</v>
       </c>
       <c r="R48" t="n">
-        <v>6978491</v>
+        <v>6978448</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,10 +5663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129296084</v>
+        <v>129290361</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5670,21 +5674,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5694,10 +5698,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>628959</v>
+        <v>628465</v>
       </c>
       <c r="R49" t="n">
-        <v>6978530</v>
+        <v>6978491</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,32 +5760,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129302275</v>
+        <v>129296084</v>
       </c>
       <c r="B50" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5791,10 +5795,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>628663</v>
+        <v>628959</v>
       </c>
       <c r="R50" t="n">
-        <v>6978428</v>
+        <v>6978530</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5827,11 +5831,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5858,45 +5857,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129302276</v>
+        <v>129290169</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>628648</v>
+        <v>628453</v>
       </c>
       <c r="R51" t="n">
-        <v>6978420</v>
+        <v>6978518</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5933,7 +5937,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>80 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5960,10 +5964,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129302233</v>
+        <v>129302294</v>
       </c>
       <c r="B52" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5971,21 +5975,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5995,10 +5999,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>628759</v>
+        <v>628661</v>
       </c>
       <c r="R52" t="n">
-        <v>6978233</v>
+        <v>6978421</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6154,10 +6158,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129290169</v>
+        <v>129302233</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6165,39 +6169,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>628453</v>
+        <v>628759</v>
       </c>
       <c r="R54" t="n">
-        <v>6978518</v>
+        <v>6978233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6230,11 +6229,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6261,7 +6255,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129290084</v>
+        <v>129302275</v>
       </c>
       <c r="B55" t="n">
         <v>98724</v>
@@ -6289,21 +6283,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>628475</v>
+        <v>628663</v>
       </c>
       <c r="R55" t="n">
-        <v>6978540</v>
+        <v>6978428</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6336,6 +6326,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6362,32 +6357,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129302294</v>
+        <v>129302276</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6397,10 +6392,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>628661</v>
+        <v>628648</v>
       </c>
       <c r="R56" t="n">
-        <v>6978421</v>
+        <v>6978420</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6433,6 +6428,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>80 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,45 +6556,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129294015</v>
+        <v>129293780</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>57719</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>628728</v>
+        <v>628680</v>
       </c>
       <c r="R58" t="n">
-        <v>6978173</v>
+        <v>6978235</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6653,54 +6662,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129293780</v>
+        <v>129294015</v>
       </c>
       <c r="B59" t="n">
-        <v>57719</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>628680</v>
+        <v>628728</v>
       </c>
       <c r="R59" t="n">
-        <v>6978235</v>
+        <v>6978173</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129302252</v>
+        <v>129302229</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>91550</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>628837</v>
+        <v>628761</v>
       </c>
       <c r="R61" t="n">
-        <v>6978500</v>
+        <v>6978157</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6927,11 +6927,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,32 +6953,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129302271</v>
+        <v>129302241</v>
       </c>
       <c r="B62" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6993,10 +6988,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>628763</v>
+        <v>628741</v>
       </c>
       <c r="R62" t="n">
-        <v>6978273</v>
+        <v>6978271</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7029,6 +7024,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska spår av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7055,32 +7055,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129302229</v>
+        <v>129302271</v>
       </c>
       <c r="B63" t="n">
-        <v>91550</v>
+        <v>97595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>628761</v>
+        <v>628763</v>
       </c>
       <c r="R63" t="n">
-        <v>6978157</v>
+        <v>6978273</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129302241</v>
+        <v>129302252</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7163,21 +7163,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>628741</v>
+        <v>628837</v>
       </c>
       <c r="R64" t="n">
-        <v>6978271</v>
+        <v>6978500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska spår av tretåig hackspett på tall.</t>
+          <t>2 stycken, övriga läten</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7254,54 +7254,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129297292</v>
+        <v>129291635</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>96058</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>628429</v>
+        <v>628573</v>
       </c>
       <c r="R65" t="n">
-        <v>6978625</v>
+        <v>6978423</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7360,32 +7351,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129302259</v>
+        <v>129294000</v>
       </c>
       <c r="B66" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7395,10 +7386,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>628771</v>
+        <v>628687</v>
       </c>
       <c r="R66" t="n">
-        <v>6978154</v>
+        <v>6978194</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7651,45 +7642,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129291635</v>
+        <v>129297292</v>
       </c>
       <c r="B69" t="n">
-        <v>96058</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1079</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>628573</v>
+        <v>628429</v>
       </c>
       <c r="R69" t="n">
-        <v>6978423</v>
+        <v>6978625</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,45 +7748,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129294000</v>
+        <v>129291473</v>
       </c>
       <c r="B70" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>628687</v>
+        <v>628549</v>
       </c>
       <c r="R70" t="n">
-        <v>6978194</v>
+        <v>6978449</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7946,32 +7950,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129302254</v>
+        <v>129302259</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>92003</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7985,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>628894</v>
+        <v>628771</v>
       </c>
       <c r="R72" t="n">
-        <v>6978096</v>
+        <v>6978154</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8017,11 +8021,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8048,10 +8047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129302250</v>
+        <v>129302254</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,16 +8058,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8083,10 +8082,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>628495</v>
+        <v>628894</v>
       </c>
       <c r="R73" t="n">
-        <v>6978647</v>
+        <v>6978096</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8123,7 +8122,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8150,7 +8149,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129302244</v>
+        <v>129302250</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -8185,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>628756</v>
+        <v>628495</v>
       </c>
       <c r="R74" t="n">
-        <v>6978337</v>
+        <v>6978647</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,7 +8224,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
+          <t>Äldre spår ( födosök) avskalad/ avbarkad tunn död gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8252,32 +8251,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129302280</v>
+        <v>129302244</v>
       </c>
       <c r="B75" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>628692</v>
+        <v>628756</v>
       </c>
       <c r="R75" t="n">
-        <v>6978432</v>
+        <v>6978337</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8327,7 +8326,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>200 ( ca) några blommande</t>
+          <t>Ringhack av tretåig hackspett på gran, färska spår.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8354,7 +8353,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129291473</v>
+        <v>129302280</v>
       </c>
       <c r="B76" t="n">
         <v>98724</v>
@@ -8382,21 +8381,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>628549</v>
+        <v>628692</v>
       </c>
       <c r="R76" t="n">
-        <v>6978449</v>
+        <v>6978432</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,6 +8424,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>200 ( ca) några blommande</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8455,49 +8455,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129302281</v>
+        <v>129302227</v>
       </c>
       <c r="B77" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>628688</v>
+        <v>628851</v>
       </c>
       <c r="R77" t="n">
-        <v>6978441</v>
+        <v>6978504</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8532,18 +8528,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8562,45 +8552,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129290447</v>
+        <v>129302281</v>
       </c>
       <c r="B78" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>628494</v>
+        <v>628688</v>
       </c>
       <c r="R78" t="n">
-        <v>6978496</v>
+        <v>6978441</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8635,12 +8629,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I backen finns uppskattningsvis över 1000 knärötter. Täcker marken likt en matta. Exakta positionen är inte helt klarlagd, men det är i närheten av denna position.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8756,32 +8756,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129302227</v>
+        <v>129290447</v>
       </c>
       <c r="B80" t="n">
-        <v>91550</v>
+        <v>97595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>628851</v>
+        <v>628494</v>
       </c>
       <c r="R80" t="n">
-        <v>6978504</v>
+        <v>6978496</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129291441</v>
+        <v>129296224</v>
       </c>
       <c r="B83" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9073,34 +9073,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Nordsjöbron, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>628547</v>
+        <v>629061</v>
       </c>
       <c r="R83" t="n">
-        <v>6978457</v>
+        <v>6978494</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129296224</v>
+        <v>129291441</v>
       </c>
       <c r="B84" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9170,34 +9170,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nordsjöbron, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>629061</v>
+        <v>628547</v>
       </c>
       <c r="R84" t="n">
-        <v>6978494</v>
+        <v>6978457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9256,32 +9256,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129296097</v>
+        <v>129302260</v>
       </c>
       <c r="B85" t="n">
-        <v>80178</v>
+        <v>92003</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628959</v>
+        <v>628641</v>
       </c>
       <c r="R85" t="n">
-        <v>6978530</v>
+        <v>6978450</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9353,45 +9353,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129302267</v>
+        <v>129294276</v>
       </c>
       <c r="B86" t="n">
-        <v>91848</v>
+        <v>91763</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628603</v>
+        <v>628790</v>
       </c>
       <c r="R86" t="n">
-        <v>6978502</v>
+        <v>6978034</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9450,7 +9450,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129302264</v>
+        <v>129292746</v>
       </c>
       <c r="B87" t="n">
         <v>91848</v>
@@ -9485,10 +9485,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628796</v>
+        <v>628586</v>
       </c>
       <c r="R87" t="n">
-        <v>6978261</v>
+        <v>6978451</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9547,45 +9547,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129294276</v>
+        <v>129290229</v>
       </c>
       <c r="B88" t="n">
-        <v>91763</v>
+        <v>91848</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>628790</v>
+        <v>628436</v>
       </c>
       <c r="R88" t="n">
-        <v>6978034</v>
+        <v>6978498</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9644,32 +9644,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129292746</v>
+        <v>129296097</v>
       </c>
       <c r="B89" t="n">
-        <v>91848</v>
+        <v>80178</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628586</v>
+        <v>628959</v>
       </c>
       <c r="R89" t="n">
-        <v>6978451</v>
+        <v>6978530</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9741,10 +9741,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129290229</v>
+        <v>129293890</v>
       </c>
       <c r="B90" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9752,34 +9752,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628436</v>
+        <v>628691</v>
       </c>
       <c r="R90" t="n">
-        <v>6978498</v>
+        <v>6978242</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9812,6 +9817,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9838,45 +9848,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129289873</v>
+        <v>129293914</v>
       </c>
       <c r="B91" t="n">
-        <v>91514</v>
+        <v>57887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628447</v>
+        <v>628690</v>
       </c>
       <c r="R91" t="n">
-        <v>6978522</v>
+        <v>6978221</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9935,50 +9950,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129293890</v>
+        <v>129289873</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628691</v>
+        <v>628447</v>
       </c>
       <c r="R92" t="n">
-        <v>6978242</v>
+        <v>6978522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10011,11 +10021,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10042,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129293914</v>
+        <v>129302267</v>
       </c>
       <c r="B93" t="n">
-        <v>57887</v>
+        <v>91848</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10053,39 +10058,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>628690</v>
+        <v>628603</v>
       </c>
       <c r="R93" t="n">
-        <v>6978221</v>
+        <v>6978502</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10144,32 +10144,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129302260</v>
+        <v>129302264</v>
       </c>
       <c r="B94" t="n">
-        <v>92003</v>
+        <v>91848</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628641</v>
+        <v>628796</v>
       </c>
       <c r="R94" t="n">
-        <v>6978450</v>
+        <v>6978261</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10241,32 +10241,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129302258</v>
+        <v>129302232</v>
       </c>
       <c r="B95" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628851</v>
+        <v>628742</v>
       </c>
       <c r="R95" t="n">
-        <v>6978502</v>
+        <v>6978216</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10338,32 +10338,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129302232</v>
+        <v>129302258</v>
       </c>
       <c r="B96" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10373,10 +10373,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>628742</v>
+        <v>628851</v>
       </c>
       <c r="R96" t="n">
-        <v>6978216</v>
+        <v>6978502</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10532,10 +10532,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129295410</v>
+        <v>129302295</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10543,43 +10543,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628767</v>
+        <v>628463</v>
       </c>
       <c r="R98" t="n">
-        <v>6978383</v>
+        <v>6978635</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10638,49 +10629,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129293044</v>
+        <v>129295410</v>
       </c>
       <c r="B99" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>628662</v>
+        <v>628767</v>
       </c>
       <c r="R99" t="n">
-        <v>6978408</v>
+        <v>6978383</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10739,45 +10735,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129302295</v>
+        <v>129293044</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>628463</v>
+        <v>628662</v>
       </c>
       <c r="R100" t="n">
-        <v>6978635</v>
+        <v>6978408</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10836,7 +10836,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129302282</v>
+        <v>129295651</v>
       </c>
       <c r="B101" t="n">
         <v>98724</v>
@@ -10864,17 +10864,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628654</v>
+        <v>628796</v>
       </c>
       <c r="R101" t="n">
-        <v>6978418</v>
+        <v>6978373</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10907,11 +10911,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10938,32 +10937,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129302287</v>
+        <v>129302268</v>
       </c>
       <c r="B102" t="n">
-        <v>98724</v>
+        <v>97595</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10973,10 +10972,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628649</v>
+        <v>628719</v>
       </c>
       <c r="R102" t="n">
-        <v>6978449</v>
+        <v>6978594</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11009,11 +11008,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11040,45 +11034,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129302263</v>
+        <v>129295020</v>
       </c>
       <c r="B103" t="n">
-        <v>91848</v>
+        <v>80184</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628810</v>
+        <v>628826</v>
       </c>
       <c r="R103" t="n">
-        <v>6978299</v>
+        <v>6978150</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11137,45 +11131,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129295020</v>
+        <v>129302263</v>
       </c>
       <c r="B104" t="n">
-        <v>80184</v>
+        <v>91848</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628826</v>
+        <v>628810</v>
       </c>
       <c r="R104" t="n">
-        <v>6978150</v>
+        <v>6978299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11234,7 +11228,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129295651</v>
+        <v>129302282</v>
       </c>
       <c r="B105" t="n">
         <v>98724</v>
@@ -11262,21 +11256,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628796</v>
+        <v>628654</v>
       </c>
       <c r="R105" t="n">
-        <v>6978373</v>
+        <v>6978418</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11309,6 +11299,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>70 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11335,32 +11330,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129302268</v>
+        <v>129302287</v>
       </c>
       <c r="B106" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11370,10 +11365,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>628719</v>
+        <v>628649</v>
       </c>
       <c r="R106" t="n">
-        <v>6978594</v>
+        <v>6978449</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11406,6 +11401,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ca 50 stycken kan finnas mer i mossan och under löv. 4 har blommat, gammla blomstänger kvar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11937,10 +11937,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129302225</v>
+        <v>129293475</v>
       </c>
       <c r="B112" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11948,21 +11948,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11972,10 +11972,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628856</v>
+        <v>628623</v>
       </c>
       <c r="R112" t="n">
-        <v>6978527</v>
+        <v>6978341</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12131,32 +12131,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129293475</v>
+        <v>129302289</v>
       </c>
       <c r="B114" t="n">
-        <v>91848</v>
+        <v>57719</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>100110</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12166,10 +12166,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628623</v>
+        <v>628493</v>
       </c>
       <c r="R114" t="n">
-        <v>6978341</v>
+        <v>6978648</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,6 +12202,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 individ. Sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12228,10 +12233,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129302290</v>
+        <v>129302225</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12239,21 +12244,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12263,10 +12268,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628712</v>
+        <v>628856</v>
       </c>
       <c r="R115" t="n">
-        <v>6978591</v>
+        <v>6978527</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12325,10 +12330,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129302247</v>
+        <v>129302290</v>
       </c>
       <c r="B116" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12336,21 +12341,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12360,10 +12365,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628749</v>
+        <v>628712</v>
       </c>
       <c r="R116" t="n">
-        <v>6978349</v>
+        <v>6978591</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12396,11 +12401,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12427,32 +12427,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129302289</v>
+        <v>129302247</v>
       </c>
       <c r="B117" t="n">
-        <v>57719</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12462,10 +12462,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628493</v>
+        <v>628749</v>
       </c>
       <c r="R117" t="n">
-        <v>6978648</v>
+        <v>6978349</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 individ. Sång</t>
+          <t>Färska spår, ringhack av tretåig hackspett på tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12631,32 +12631,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129294695</v>
+        <v>129295812</v>
       </c>
       <c r="B119" t="n">
-        <v>92003</v>
+        <v>91550</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12666,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628831</v>
+        <v>628900</v>
       </c>
       <c r="R119" t="n">
-        <v>6978180</v>
+        <v>6978416</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12728,7 +12728,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129297070</v>
+        <v>129294695</v>
       </c>
       <c r="B120" t="n">
         <v>92003</v>
@@ -12759,14 +12759,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>628764</v>
+        <v>628831</v>
       </c>
       <c r="R120" t="n">
-        <v>6978591</v>
+        <v>6978180</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12825,45 +12825,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129295812</v>
+        <v>129297070</v>
       </c>
       <c r="B121" t="n">
-        <v>91550</v>
+        <v>92003</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628900</v>
+        <v>628764</v>
       </c>
       <c r="R121" t="n">
-        <v>6978416</v>
+        <v>6978591</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13421,10 +13421,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129289677</v>
+        <v>129290523</v>
       </c>
       <c r="B127" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13432,16 +13432,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -13452,7 +13452,7 @@
       <c r="I127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -13461,10 +13461,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628484</v>
+        <v>628509</v>
       </c>
       <c r="R127" t="n">
-        <v>6978568</v>
+        <v>6978510</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13497,6 +13497,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13523,10 +13528,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129290523</v>
+        <v>129289677</v>
       </c>
       <c r="B128" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13534,16 +13539,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -13554,7 +13559,7 @@
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -13563,10 +13568,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628509</v>
+        <v>628484</v>
       </c>
       <c r="R128" t="n">
-        <v>6978510</v>
+        <v>6978568</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13599,11 +13604,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack på gran. Troligen årsfärska</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13925,32 +13925,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129302296</v>
+        <v>129302270</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13960,10 +13960,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628449</v>
+        <v>628812</v>
       </c>
       <c r="R132" t="n">
-        <v>6978612</v>
+        <v>6978062</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14022,10 +14022,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129302239</v>
+        <v>129302296</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14033,21 +14033,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14057,10 +14057,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628747</v>
+        <v>628449</v>
       </c>
       <c r="R133" t="n">
-        <v>6978218</v>
+        <v>6978612</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14093,11 +14093,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14124,32 +14119,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129302270</v>
+        <v>129302239</v>
       </c>
       <c r="B134" t="n">
-        <v>97595</v>
+        <v>57727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14159,10 +14154,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628812</v>
+        <v>628747</v>
       </c>
       <c r="R134" t="n">
-        <v>6978062</v>
+        <v>6978218</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14195,6 +14190,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre spår, ringhack av tretåig hackspett på tall. Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14221,10 +14221,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129302228</v>
+        <v>129294072</v>
       </c>
       <c r="B135" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14232,34 +14232,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Djupbäcken, Ång</t>
+          <t>Seselmyrhöjden, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628870</v>
+        <v>628731</v>
       </c>
       <c r="R135" t="n">
-        <v>6978469</v>
+        <v>6978165</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14318,10 +14318,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129295655</v>
+        <v>129302228</v>
       </c>
       <c r="B136" t="n">
-        <v>57724</v>
+        <v>91550</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14329,43 +14329,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Seselmyrhöjden, Ång</t>
+          <t>Djupbäcken, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628796</v>
+        <v>628870</v>
       </c>
       <c r="R136" t="n">
-        <v>6978373</v>
+        <v>6978469</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14424,10 +14415,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129294072</v>
+        <v>129293208</v>
       </c>
       <c r="B137" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14435,34 +14426,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+      